--- a/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52892A95-BBDD-42B6-A9C8-E869A5FA9CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE5807F-3B71-4A65-9DF2-E8A30E2FB156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -467,17 +467,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:P12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="20.625" customWidth="1"/>
-    <col min="5" max="6" width="12.25" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="5" max="6" width="12.21875" customWidth="1"/>
     <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="10.375" customWidth="1"/>
+    <col min="10" max="12" width="13.44140625" customWidth="1"/>
+    <col min="13" max="13" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -515,7 +515,7 @@
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,7 +541,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -569,6 +569,44 @@
       <c r="P3" s="2" t="s">
         <v>22</v>
       </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="L4" s="2"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J5" s="2"/>
+      <c r="L5" s="2"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J6" s="2"/>
+      <c r="L6" s="2"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J7" s="2"/>
+      <c r="L7" s="2"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J8" s="2"/>
+      <c r="L8" s="2"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J9" s="2"/>
+      <c r="L9" s="2"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J10" s="2"/>
+      <c r="L10" s="2"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J11" s="2"/>
+      <c r="L11" s="2"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J12" s="2"/>
+      <c r="L12" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE5807F-3B71-4A65-9DF2-E8A30E2FB156}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67E5318-0EC0-4EF3-AAAD-453B2BFC36FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
   <si>
     <t>##var</t>
   </si>
@@ -92,6 +92,66 @@
   </si>
   <si>
     <t>字段变体</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>value</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>y</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>z</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CueLogic</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GameplayCueLog</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GameplayCueLogFloat</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GameplayCueLogBool</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GameplayCueLogVector2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>GameplayCueVector3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CueLoging</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>duration</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -467,10 +527,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="4" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="6" width="12.21875" customWidth="1"/>
     <col min="7" max="9" width="15" customWidth="1"/>
     <col min="10" max="12" width="13.44140625" customWidth="1"/>
@@ -571,42 +633,137 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="E4" s="2"/>
       <c r="J4" s="2"/>
       <c r="L4" s="2"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J5" s="2"/>
-      <c r="L5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J6" s="2"/>
-      <c r="L6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J7" s="2"/>
-      <c r="L7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="J7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J8" s="2"/>
-      <c r="L8" s="2"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J9" s="2"/>
-      <c r="L9" s="2"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="J8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="J10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J11" s="2"/>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J12" s="2"/>
-      <c r="L12" s="2"/>
+      <c r="J11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="J12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J13" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E67E5318-0EC0-4EF3-AAAD-453B2BFC36FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA46240-587F-438B-822D-4F6CDF2122A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -152,6 +152,21 @@
   </si>
   <si>
     <t>duration</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MmcLogic</t>
+  </si>
+  <si>
+    <t>ScalableFloatMmc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>k</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>b</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -527,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.6640625" customWidth="1"/>
@@ -765,6 +780,33 @@
         <v>25</v>
       </c>
     </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17" t="s">
+        <v>38</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>

--- a/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA46240-587F-438B-822D-4F6CDF2122A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F155D18-E435-4AC3-8E91-61D561FA0BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -158,15 +158,15 @@
     <t>MmcLogic</t>
   </si>
   <si>
-    <t>ScalableFloatMmc</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>k</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>b</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MMCScalableFloat</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -787,13 +787,13 @@
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C17" t="s">
         <v>38</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -801,7 +801,7 @@
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="J18" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -813,6 +813,6 @@
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0344F1-3BA9-4A3C-B537-6AEB6B256C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0A8C6C-86C0-4DF8-9F2E-201F257CDEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="62">
   <si>
     <t>##var</t>
   </si>
@@ -236,6 +236,18 @@
     <t>overflowEffects</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>AbilityLogic</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALDebugLog</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALApplyEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -357,9 +369,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -377,6 +386,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -655,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:XFB35"/>
+  <dimension ref="A1:XFB45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="2" max="2" width="20.6640625" customWidth="1"/>
@@ -696,15 +708,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
     </row>
     <row r="2" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
       <c r="A2" s="1" t="s">
@@ -785,23 +797,23 @@
       </c>
       <c r="P5" s="2"/>
     </row>
-    <row r="6" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" s="5" customFormat="1">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
-      <c r="P6" s="7"/>
+    <row r="6" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" s="4" customFormat="1">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
     </row>
     <row r="7" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
       <c r="B7" s="2" t="s">
@@ -838,12 +850,12 @@
       </c>
       <c r="P9" s="2"/>
     </row>
-    <row r="10" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" s="8" customFormat="1">
-      <c r="B10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="6"/>
-      <c r="P10" s="6"/>
+    <row r="10" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" s="7" customFormat="1">
+      <c r="B10" s="5"/>
+      <c r="J10" s="5"/>
+      <c r="K10" s="5"/>
+      <c r="L10" s="5"/>
+      <c r="P10" s="5"/>
     </row>
     <row r="11" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
       <c r="B11" s="2" t="s">
@@ -4951,7 +4963,7 @@
       <c r="XFB11" s="2"/>
     </row>
     <row r="12" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
-      <c r="B12" s="4"/>
+      <c r="B12" s="3"/>
       <c r="F12" s="2"/>
       <c r="J12" s="2" t="s">
         <v>51</v>
@@ -9054,7 +9066,7 @@
       <c r="XFB12" s="2"/>
     </row>
     <row r="13" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
-      <c r="B13" s="4"/>
+      <c r="B13" s="3"/>
       <c r="F13" s="2"/>
       <c r="J13" s="2" t="s">
         <v>52</v>
@@ -13157,7 +13169,7 @@
       <c r="XFB13" s="2"/>
     </row>
     <row r="14" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
-      <c r="B14" s="4"/>
+      <c r="B14" s="3"/>
       <c r="F14" s="2"/>
       <c r="J14" s="2" t="s">
         <v>53</v>
@@ -17260,7 +17272,7 @@
       <c r="XFB14" s="2"/>
     </row>
     <row r="15" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
-      <c r="B15" s="4"/>
+      <c r="B15" s="3"/>
       <c r="F15" s="2"/>
       <c r="J15" s="2" t="s">
         <v>54</v>
@@ -21363,7 +21375,7 @@
       <c r="XFB15" s="2"/>
     </row>
     <row r="16" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
-      <c r="B16" s="4"/>
+      <c r="B16" s="3"/>
       <c r="F16" s="2"/>
       <c r="J16" s="2" t="s">
         <v>55</v>
@@ -25466,7 +25478,7 @@
       <c r="XFB16" s="2"/>
     </row>
     <row r="17" spans="2:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
-      <c r="B17" s="4"/>
+      <c r="B17" s="3"/>
       <c r="F17" s="2"/>
       <c r="J17" s="2" t="s">
         <v>56</v>
@@ -29569,7 +29581,7 @@
       <c r="XFB17" s="2"/>
     </row>
     <row r="18" spans="2:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
-      <c r="B18" s="4"/>
+      <c r="B18" s="3"/>
       <c r="F18" s="2"/>
       <c r="J18" s="2" t="s">
         <v>57</v>
@@ -33672,7 +33684,7 @@
       <c r="XFB18" s="2"/>
     </row>
     <row r="19" spans="2:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
-      <c r="B19" s="4"/>
+      <c r="B19" s="3"/>
       <c r="F19" s="2"/>
       <c r="J19" s="2" t="s">
         <v>58</v>
@@ -37774,4104 +37786,4104 @@
       <c r="XEX19" s="2"/>
       <c r="XFB19" s="2"/>
     </row>
-    <row r="20" spans="2:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" s="8" customFormat="1">
-      <c r="B20" s="9"/>
-      <c r="F20" s="6"/>
-      <c r="J20" s="9"/>
-      <c r="L20" s="6"/>
-      <c r="N20" s="6"/>
-      <c r="R20" s="6"/>
-      <c r="V20" s="6"/>
-      <c r="Z20" s="6"/>
-      <c r="AD20" s="6"/>
-      <c r="AH20" s="6"/>
-      <c r="AL20" s="6"/>
-      <c r="AP20" s="6"/>
-      <c r="AT20" s="6"/>
-      <c r="AX20" s="6"/>
-      <c r="BB20" s="6"/>
-      <c r="BF20" s="6"/>
-      <c r="BJ20" s="6"/>
-      <c r="BN20" s="6"/>
-      <c r="BR20" s="6"/>
-      <c r="BV20" s="6"/>
-      <c r="BZ20" s="6"/>
-      <c r="CD20" s="6"/>
-      <c r="CH20" s="6"/>
-      <c r="CL20" s="6"/>
-      <c r="CP20" s="6"/>
-      <c r="CT20" s="6"/>
-      <c r="CX20" s="6"/>
-      <c r="DB20" s="6"/>
-      <c r="DF20" s="6"/>
-      <c r="DJ20" s="6"/>
-      <c r="DN20" s="6"/>
-      <c r="DR20" s="6"/>
-      <c r="DV20" s="6"/>
-      <c r="DZ20" s="6"/>
-      <c r="ED20" s="6"/>
-      <c r="EH20" s="6"/>
-      <c r="EL20" s="6"/>
-      <c r="EP20" s="6"/>
-      <c r="ET20" s="6"/>
-      <c r="EX20" s="6"/>
-      <c r="FB20" s="6"/>
-      <c r="FF20" s="6"/>
-      <c r="FJ20" s="6"/>
-      <c r="FN20" s="6"/>
-      <c r="FR20" s="6"/>
-      <c r="FV20" s="6"/>
-      <c r="FZ20" s="6"/>
-      <c r="GD20" s="6"/>
-      <c r="GH20" s="6"/>
-      <c r="GL20" s="6"/>
-      <c r="GP20" s="6"/>
-      <c r="GT20" s="6"/>
-      <c r="GX20" s="6"/>
-      <c r="HB20" s="6"/>
-      <c r="HF20" s="6"/>
-      <c r="HJ20" s="6"/>
-      <c r="HN20" s="6"/>
-      <c r="HR20" s="6"/>
-      <c r="HV20" s="6"/>
-      <c r="HZ20" s="6"/>
-      <c r="ID20" s="6"/>
-      <c r="IH20" s="6"/>
-      <c r="IL20" s="6"/>
-      <c r="IP20" s="6"/>
-      <c r="IT20" s="6"/>
-      <c r="IX20" s="6"/>
-      <c r="JB20" s="6"/>
-      <c r="JF20" s="6"/>
-      <c r="JJ20" s="6"/>
-      <c r="JN20" s="6"/>
-      <c r="JR20" s="6"/>
-      <c r="JV20" s="6"/>
-      <c r="JZ20" s="6"/>
-      <c r="KD20" s="6"/>
-      <c r="KH20" s="6"/>
-      <c r="KL20" s="6"/>
-      <c r="KP20" s="6"/>
-      <c r="KT20" s="6"/>
-      <c r="KX20" s="6"/>
-      <c r="LB20" s="6"/>
-      <c r="LF20" s="6"/>
-      <c r="LJ20" s="6"/>
-      <c r="LN20" s="6"/>
-      <c r="LR20" s="6"/>
-      <c r="LV20" s="6"/>
-      <c r="LZ20" s="6"/>
-      <c r="MD20" s="6"/>
-      <c r="MH20" s="6"/>
-      <c r="ML20" s="6"/>
-      <c r="MP20" s="6"/>
-      <c r="MT20" s="6"/>
-      <c r="MX20" s="6"/>
-      <c r="NB20" s="6"/>
-      <c r="NF20" s="6"/>
-      <c r="NJ20" s="6"/>
-      <c r="NN20" s="6"/>
-      <c r="NR20" s="6"/>
-      <c r="NV20" s="6"/>
-      <c r="NZ20" s="6"/>
-      <c r="OD20" s="6"/>
-      <c r="OH20" s="6"/>
-      <c r="OL20" s="6"/>
-      <c r="OP20" s="6"/>
-      <c r="OT20" s="6"/>
-      <c r="OX20" s="6"/>
-      <c r="PB20" s="6"/>
-      <c r="PF20" s="6"/>
-      <c r="PJ20" s="6"/>
-      <c r="PN20" s="6"/>
-      <c r="PR20" s="6"/>
-      <c r="PV20" s="6"/>
-      <c r="PZ20" s="6"/>
-      <c r="QD20" s="6"/>
-      <c r="QH20" s="6"/>
-      <c r="QL20" s="6"/>
-      <c r="QP20" s="6"/>
-      <c r="QT20" s="6"/>
-      <c r="QX20" s="6"/>
-      <c r="RB20" s="6"/>
-      <c r="RF20" s="6"/>
-      <c r="RJ20" s="6"/>
-      <c r="RN20" s="6"/>
-      <c r="RR20" s="6"/>
-      <c r="RV20" s="6"/>
-      <c r="RZ20" s="6"/>
-      <c r="SD20" s="6"/>
-      <c r="SH20" s="6"/>
-      <c r="SL20" s="6"/>
-      <c r="SP20" s="6"/>
-      <c r="ST20" s="6"/>
-      <c r="SX20" s="6"/>
-      <c r="TB20" s="6"/>
-      <c r="TF20" s="6"/>
-      <c r="TJ20" s="6"/>
-      <c r="TN20" s="6"/>
-      <c r="TR20" s="6"/>
-      <c r="TV20" s="6"/>
-      <c r="TZ20" s="6"/>
-      <c r="UD20" s="6"/>
-      <c r="UH20" s="6"/>
-      <c r="UL20" s="6"/>
-      <c r="UP20" s="6"/>
-      <c r="UT20" s="6"/>
-      <c r="UX20" s="6"/>
-      <c r="VB20" s="6"/>
-      <c r="VF20" s="6"/>
-      <c r="VJ20" s="6"/>
-      <c r="VN20" s="6"/>
-      <c r="VR20" s="6"/>
-      <c r="VV20" s="6"/>
-      <c r="VZ20" s="6"/>
-      <c r="WD20" s="6"/>
-      <c r="WH20" s="6"/>
-      <c r="WL20" s="6"/>
-      <c r="WP20" s="6"/>
-      <c r="WT20" s="6"/>
-      <c r="WX20" s="6"/>
-      <c r="XB20" s="6"/>
-      <c r="XF20" s="6"/>
-      <c r="XJ20" s="6"/>
-      <c r="XN20" s="6"/>
-      <c r="XR20" s="6"/>
-      <c r="XV20" s="6"/>
-      <c r="XZ20" s="6"/>
-      <c r="YD20" s="6"/>
-      <c r="YH20" s="6"/>
-      <c r="YL20" s="6"/>
-      <c r="YP20" s="6"/>
-      <c r="YT20" s="6"/>
-      <c r="YX20" s="6"/>
-      <c r="ZB20" s="6"/>
-      <c r="ZF20" s="6"/>
-      <c r="ZJ20" s="6"/>
-      <c r="ZN20" s="6"/>
-      <c r="ZR20" s="6"/>
-      <c r="ZV20" s="6"/>
-      <c r="ZZ20" s="6"/>
-      <c r="AAD20" s="6"/>
-      <c r="AAH20" s="6"/>
-      <c r="AAL20" s="6"/>
-      <c r="AAP20" s="6"/>
-      <c r="AAT20" s="6"/>
-      <c r="AAX20" s="6"/>
-      <c r="ABB20" s="6"/>
-      <c r="ABF20" s="6"/>
-      <c r="ABJ20" s="6"/>
-      <c r="ABN20" s="6"/>
-      <c r="ABR20" s="6"/>
-      <c r="ABV20" s="6"/>
-      <c r="ABZ20" s="6"/>
-      <c r="ACD20" s="6"/>
-      <c r="ACH20" s="6"/>
-      <c r="ACL20" s="6"/>
-      <c r="ACP20" s="6"/>
-      <c r="ACT20" s="6"/>
-      <c r="ACX20" s="6"/>
-      <c r="ADB20" s="6"/>
-      <c r="ADF20" s="6"/>
-      <c r="ADJ20" s="6"/>
-      <c r="ADN20" s="6"/>
-      <c r="ADR20" s="6"/>
-      <c r="ADV20" s="6"/>
-      <c r="ADZ20" s="6"/>
-      <c r="AED20" s="6"/>
-      <c r="AEH20" s="6"/>
-      <c r="AEL20" s="6"/>
-      <c r="AEP20" s="6"/>
-      <c r="AET20" s="6"/>
-      <c r="AEX20" s="6"/>
-      <c r="AFB20" s="6"/>
-      <c r="AFF20" s="6"/>
-      <c r="AFJ20" s="6"/>
-      <c r="AFN20" s="6"/>
-      <c r="AFR20" s="6"/>
-      <c r="AFV20" s="6"/>
-      <c r="AFZ20" s="6"/>
-      <c r="AGD20" s="6"/>
-      <c r="AGH20" s="6"/>
-      <c r="AGL20" s="6"/>
-      <c r="AGP20" s="6"/>
-      <c r="AGT20" s="6"/>
-      <c r="AGX20" s="6"/>
-      <c r="AHB20" s="6"/>
-      <c r="AHF20" s="6"/>
-      <c r="AHJ20" s="6"/>
-      <c r="AHN20" s="6"/>
-      <c r="AHR20" s="6"/>
-      <c r="AHV20" s="6"/>
-      <c r="AHZ20" s="6"/>
-      <c r="AID20" s="6"/>
-      <c r="AIH20" s="6"/>
-      <c r="AIL20" s="6"/>
-      <c r="AIP20" s="6"/>
-      <c r="AIT20" s="6"/>
-      <c r="AIX20" s="6"/>
-      <c r="AJB20" s="6"/>
-      <c r="AJF20" s="6"/>
-      <c r="AJJ20" s="6"/>
-      <c r="AJN20" s="6"/>
-      <c r="AJR20" s="6"/>
-      <c r="AJV20" s="6"/>
-      <c r="AJZ20" s="6"/>
-      <c r="AKD20" s="6"/>
-      <c r="AKH20" s="6"/>
-      <c r="AKL20" s="6"/>
-      <c r="AKP20" s="6"/>
-      <c r="AKT20" s="6"/>
-      <c r="AKX20" s="6"/>
-      <c r="ALB20" s="6"/>
-      <c r="ALF20" s="6"/>
-      <c r="ALJ20" s="6"/>
-      <c r="ALN20" s="6"/>
-      <c r="ALR20" s="6"/>
-      <c r="ALV20" s="6"/>
-      <c r="ALZ20" s="6"/>
-      <c r="AMD20" s="6"/>
-      <c r="AMH20" s="6"/>
-      <c r="AML20" s="6"/>
-      <c r="AMP20" s="6"/>
-      <c r="AMT20" s="6"/>
-      <c r="AMX20" s="6"/>
-      <c r="ANB20" s="6"/>
-      <c r="ANF20" s="6"/>
-      <c r="ANJ20" s="6"/>
-      <c r="ANN20" s="6"/>
-      <c r="ANR20" s="6"/>
-      <c r="ANV20" s="6"/>
-      <c r="ANZ20" s="6"/>
-      <c r="AOD20" s="6"/>
-      <c r="AOH20" s="6"/>
-      <c r="AOL20" s="6"/>
-      <c r="AOP20" s="6"/>
-      <c r="AOT20" s="6"/>
-      <c r="AOX20" s="6"/>
-      <c r="APB20" s="6"/>
-      <c r="APF20" s="6"/>
-      <c r="APJ20" s="6"/>
-      <c r="APN20" s="6"/>
-      <c r="APR20" s="6"/>
-      <c r="APV20" s="6"/>
-      <c r="APZ20" s="6"/>
-      <c r="AQD20" s="6"/>
-      <c r="AQH20" s="6"/>
-      <c r="AQL20" s="6"/>
-      <c r="AQP20" s="6"/>
-      <c r="AQT20" s="6"/>
-      <c r="AQX20" s="6"/>
-      <c r="ARB20" s="6"/>
-      <c r="ARF20" s="6"/>
-      <c r="ARJ20" s="6"/>
-      <c r="ARN20" s="6"/>
-      <c r="ARR20" s="6"/>
-      <c r="ARV20" s="6"/>
-      <c r="ARZ20" s="6"/>
-      <c r="ASD20" s="6"/>
-      <c r="ASH20" s="6"/>
-      <c r="ASL20" s="6"/>
-      <c r="ASP20" s="6"/>
-      <c r="AST20" s="6"/>
-      <c r="ASX20" s="6"/>
-      <c r="ATB20" s="6"/>
-      <c r="ATF20" s="6"/>
-      <c r="ATJ20" s="6"/>
-      <c r="ATN20" s="6"/>
-      <c r="ATR20" s="6"/>
-      <c r="ATV20" s="6"/>
-      <c r="ATZ20" s="6"/>
-      <c r="AUD20" s="6"/>
-      <c r="AUH20" s="6"/>
-      <c r="AUL20" s="6"/>
-      <c r="AUP20" s="6"/>
-      <c r="AUT20" s="6"/>
-      <c r="AUX20" s="6"/>
-      <c r="AVB20" s="6"/>
-      <c r="AVF20" s="6"/>
-      <c r="AVJ20" s="6"/>
-      <c r="AVN20" s="6"/>
-      <c r="AVR20" s="6"/>
-      <c r="AVV20" s="6"/>
-      <c r="AVZ20" s="6"/>
-      <c r="AWD20" s="6"/>
-      <c r="AWH20" s="6"/>
-      <c r="AWL20" s="6"/>
-      <c r="AWP20" s="6"/>
-      <c r="AWT20" s="6"/>
-      <c r="AWX20" s="6"/>
-      <c r="AXB20" s="6"/>
-      <c r="AXF20" s="6"/>
-      <c r="AXJ20" s="6"/>
-      <c r="AXN20" s="6"/>
-      <c r="AXR20" s="6"/>
-      <c r="AXV20" s="6"/>
-      <c r="AXZ20" s="6"/>
-      <c r="AYD20" s="6"/>
-      <c r="AYH20" s="6"/>
-      <c r="AYL20" s="6"/>
-      <c r="AYP20" s="6"/>
-      <c r="AYT20" s="6"/>
-      <c r="AYX20" s="6"/>
-      <c r="AZB20" s="6"/>
-      <c r="AZF20" s="6"/>
-      <c r="AZJ20" s="6"/>
-      <c r="AZN20" s="6"/>
-      <c r="AZR20" s="6"/>
-      <c r="AZV20" s="6"/>
-      <c r="AZZ20" s="6"/>
-      <c r="BAD20" s="6"/>
-      <c r="BAH20" s="6"/>
-      <c r="BAL20" s="6"/>
-      <c r="BAP20" s="6"/>
-      <c r="BAT20" s="6"/>
-      <c r="BAX20" s="6"/>
-      <c r="BBB20" s="6"/>
-      <c r="BBF20" s="6"/>
-      <c r="BBJ20" s="6"/>
-      <c r="BBN20" s="6"/>
-      <c r="BBR20" s="6"/>
-      <c r="BBV20" s="6"/>
-      <c r="BBZ20" s="6"/>
-      <c r="BCD20" s="6"/>
-      <c r="BCH20" s="6"/>
-      <c r="BCL20" s="6"/>
-      <c r="BCP20" s="6"/>
-      <c r="BCT20" s="6"/>
-      <c r="BCX20" s="6"/>
-      <c r="BDB20" s="6"/>
-      <c r="BDF20" s="6"/>
-      <c r="BDJ20" s="6"/>
-      <c r="BDN20" s="6"/>
-      <c r="BDR20" s="6"/>
-      <c r="BDV20" s="6"/>
-      <c r="BDZ20" s="6"/>
-      <c r="BED20" s="6"/>
-      <c r="BEH20" s="6"/>
-      <c r="BEL20" s="6"/>
-      <c r="BEP20" s="6"/>
-      <c r="BET20" s="6"/>
-      <c r="BEX20" s="6"/>
-      <c r="BFB20" s="6"/>
-      <c r="BFF20" s="6"/>
-      <c r="BFJ20" s="6"/>
-      <c r="BFN20" s="6"/>
-      <c r="BFR20" s="6"/>
-      <c r="BFV20" s="6"/>
-      <c r="BFZ20" s="6"/>
-      <c r="BGD20" s="6"/>
-      <c r="BGH20" s="6"/>
-      <c r="BGL20" s="6"/>
-      <c r="BGP20" s="6"/>
-      <c r="BGT20" s="6"/>
-      <c r="BGX20" s="6"/>
-      <c r="BHB20" s="6"/>
-      <c r="BHF20" s="6"/>
-      <c r="BHJ20" s="6"/>
-      <c r="BHN20" s="6"/>
-      <c r="BHR20" s="6"/>
-      <c r="BHV20" s="6"/>
-      <c r="BHZ20" s="6"/>
-      <c r="BID20" s="6"/>
-      <c r="BIH20" s="6"/>
-      <c r="BIL20" s="6"/>
-      <c r="BIP20" s="6"/>
-      <c r="BIT20" s="6"/>
-      <c r="BIX20" s="6"/>
-      <c r="BJB20" s="6"/>
-      <c r="BJF20" s="6"/>
-      <c r="BJJ20" s="6"/>
-      <c r="BJN20" s="6"/>
-      <c r="BJR20" s="6"/>
-      <c r="BJV20" s="6"/>
-      <c r="BJZ20" s="6"/>
-      <c r="BKD20" s="6"/>
-      <c r="BKH20" s="6"/>
-      <c r="BKL20" s="6"/>
-      <c r="BKP20" s="6"/>
-      <c r="BKT20" s="6"/>
-      <c r="BKX20" s="6"/>
-      <c r="BLB20" s="6"/>
-      <c r="BLF20" s="6"/>
-      <c r="BLJ20" s="6"/>
-      <c r="BLN20" s="6"/>
-      <c r="BLR20" s="6"/>
-      <c r="BLV20" s="6"/>
-      <c r="BLZ20" s="6"/>
-      <c r="BMD20" s="6"/>
-      <c r="BMH20" s="6"/>
-      <c r="BML20" s="6"/>
-      <c r="BMP20" s="6"/>
-      <c r="BMT20" s="6"/>
-      <c r="BMX20" s="6"/>
-      <c r="BNB20" s="6"/>
-      <c r="BNF20" s="6"/>
-      <c r="BNJ20" s="6"/>
-      <c r="BNN20" s="6"/>
-      <c r="BNR20" s="6"/>
-      <c r="BNV20" s="6"/>
-      <c r="BNZ20" s="6"/>
-      <c r="BOD20" s="6"/>
-      <c r="BOH20" s="6"/>
-      <c r="BOL20" s="6"/>
-      <c r="BOP20" s="6"/>
-      <c r="BOT20" s="6"/>
-      <c r="BOX20" s="6"/>
-      <c r="BPB20" s="6"/>
-      <c r="BPF20" s="6"/>
-      <c r="BPJ20" s="6"/>
-      <c r="BPN20" s="6"/>
-      <c r="BPR20" s="6"/>
-      <c r="BPV20" s="6"/>
-      <c r="BPZ20" s="6"/>
-      <c r="BQD20" s="6"/>
-      <c r="BQH20" s="6"/>
-      <c r="BQL20" s="6"/>
-      <c r="BQP20" s="6"/>
-      <c r="BQT20" s="6"/>
-      <c r="BQX20" s="6"/>
-      <c r="BRB20" s="6"/>
-      <c r="BRF20" s="6"/>
-      <c r="BRJ20" s="6"/>
-      <c r="BRN20" s="6"/>
-      <c r="BRR20" s="6"/>
-      <c r="BRV20" s="6"/>
-      <c r="BRZ20" s="6"/>
-      <c r="BSD20" s="6"/>
-      <c r="BSH20" s="6"/>
-      <c r="BSL20" s="6"/>
-      <c r="BSP20" s="6"/>
-      <c r="BST20" s="6"/>
-      <c r="BSX20" s="6"/>
-      <c r="BTB20" s="6"/>
-      <c r="BTF20" s="6"/>
-      <c r="BTJ20" s="6"/>
-      <c r="BTN20" s="6"/>
-      <c r="BTR20" s="6"/>
-      <c r="BTV20" s="6"/>
-      <c r="BTZ20" s="6"/>
-      <c r="BUD20" s="6"/>
-      <c r="BUH20" s="6"/>
-      <c r="BUL20" s="6"/>
-      <c r="BUP20" s="6"/>
-      <c r="BUT20" s="6"/>
-      <c r="BUX20" s="6"/>
-      <c r="BVB20" s="6"/>
-      <c r="BVF20" s="6"/>
-      <c r="BVJ20" s="6"/>
-      <c r="BVN20" s="6"/>
-      <c r="BVR20" s="6"/>
-      <c r="BVV20" s="6"/>
-      <c r="BVZ20" s="6"/>
-      <c r="BWD20" s="6"/>
-      <c r="BWH20" s="6"/>
-      <c r="BWL20" s="6"/>
-      <c r="BWP20" s="6"/>
-      <c r="BWT20" s="6"/>
-      <c r="BWX20" s="6"/>
-      <c r="BXB20" s="6"/>
-      <c r="BXF20" s="6"/>
-      <c r="BXJ20" s="6"/>
-      <c r="BXN20" s="6"/>
-      <c r="BXR20" s="6"/>
-      <c r="BXV20" s="6"/>
-      <c r="BXZ20" s="6"/>
-      <c r="BYD20" s="6"/>
-      <c r="BYH20" s="6"/>
-      <c r="BYL20" s="6"/>
-      <c r="BYP20" s="6"/>
-      <c r="BYT20" s="6"/>
-      <c r="BYX20" s="6"/>
-      <c r="BZB20" s="6"/>
-      <c r="BZF20" s="6"/>
-      <c r="BZJ20" s="6"/>
-      <c r="BZN20" s="6"/>
-      <c r="BZR20" s="6"/>
-      <c r="BZV20" s="6"/>
-      <c r="BZZ20" s="6"/>
-      <c r="CAD20" s="6"/>
-      <c r="CAH20" s="6"/>
-      <c r="CAL20" s="6"/>
-      <c r="CAP20" s="6"/>
-      <c r="CAT20" s="6"/>
-      <c r="CAX20" s="6"/>
-      <c r="CBB20" s="6"/>
-      <c r="CBF20" s="6"/>
-      <c r="CBJ20" s="6"/>
-      <c r="CBN20" s="6"/>
-      <c r="CBR20" s="6"/>
-      <c r="CBV20" s="6"/>
-      <c r="CBZ20" s="6"/>
-      <c r="CCD20" s="6"/>
-      <c r="CCH20" s="6"/>
-      <c r="CCL20" s="6"/>
-      <c r="CCP20" s="6"/>
-      <c r="CCT20" s="6"/>
-      <c r="CCX20" s="6"/>
-      <c r="CDB20" s="6"/>
-      <c r="CDF20" s="6"/>
-      <c r="CDJ20" s="6"/>
-      <c r="CDN20" s="6"/>
-      <c r="CDR20" s="6"/>
-      <c r="CDV20" s="6"/>
-      <c r="CDZ20" s="6"/>
-      <c r="CED20" s="6"/>
-      <c r="CEH20" s="6"/>
-      <c r="CEL20" s="6"/>
-      <c r="CEP20" s="6"/>
-      <c r="CET20" s="6"/>
-      <c r="CEX20" s="6"/>
-      <c r="CFB20" s="6"/>
-      <c r="CFF20" s="6"/>
-      <c r="CFJ20" s="6"/>
-      <c r="CFN20" s="6"/>
-      <c r="CFR20" s="6"/>
-      <c r="CFV20" s="6"/>
-      <c r="CFZ20" s="6"/>
-      <c r="CGD20" s="6"/>
-      <c r="CGH20" s="6"/>
-      <c r="CGL20" s="6"/>
-      <c r="CGP20" s="6"/>
-      <c r="CGT20" s="6"/>
-      <c r="CGX20" s="6"/>
-      <c r="CHB20" s="6"/>
-      <c r="CHF20" s="6"/>
-      <c r="CHJ20" s="6"/>
-      <c r="CHN20" s="6"/>
-      <c r="CHR20" s="6"/>
-      <c r="CHV20" s="6"/>
-      <c r="CHZ20" s="6"/>
-      <c r="CID20" s="6"/>
-      <c r="CIH20" s="6"/>
-      <c r="CIL20" s="6"/>
-      <c r="CIP20" s="6"/>
-      <c r="CIT20" s="6"/>
-      <c r="CIX20" s="6"/>
-      <c r="CJB20" s="6"/>
-      <c r="CJF20" s="6"/>
-      <c r="CJJ20" s="6"/>
-      <c r="CJN20" s="6"/>
-      <c r="CJR20" s="6"/>
-      <c r="CJV20" s="6"/>
-      <c r="CJZ20" s="6"/>
-      <c r="CKD20" s="6"/>
-      <c r="CKH20" s="6"/>
-      <c r="CKL20" s="6"/>
-      <c r="CKP20" s="6"/>
-      <c r="CKT20" s="6"/>
-      <c r="CKX20" s="6"/>
-      <c r="CLB20" s="6"/>
-      <c r="CLF20" s="6"/>
-      <c r="CLJ20" s="6"/>
-      <c r="CLN20" s="6"/>
-      <c r="CLR20" s="6"/>
-      <c r="CLV20" s="6"/>
-      <c r="CLZ20" s="6"/>
-      <c r="CMD20" s="6"/>
-      <c r="CMH20" s="6"/>
-      <c r="CML20" s="6"/>
-      <c r="CMP20" s="6"/>
-      <c r="CMT20" s="6"/>
-      <c r="CMX20" s="6"/>
-      <c r="CNB20" s="6"/>
-      <c r="CNF20" s="6"/>
-      <c r="CNJ20" s="6"/>
-      <c r="CNN20" s="6"/>
-      <c r="CNR20" s="6"/>
-      <c r="CNV20" s="6"/>
-      <c r="CNZ20" s="6"/>
-      <c r="COD20" s="6"/>
-      <c r="COH20" s="6"/>
-      <c r="COL20" s="6"/>
-      <c r="COP20" s="6"/>
-      <c r="COT20" s="6"/>
-      <c r="COX20" s="6"/>
-      <c r="CPB20" s="6"/>
-      <c r="CPF20" s="6"/>
-      <c r="CPJ20" s="6"/>
-      <c r="CPN20" s="6"/>
-      <c r="CPR20" s="6"/>
-      <c r="CPV20" s="6"/>
-      <c r="CPZ20" s="6"/>
-      <c r="CQD20" s="6"/>
-      <c r="CQH20" s="6"/>
-      <c r="CQL20" s="6"/>
-      <c r="CQP20" s="6"/>
-      <c r="CQT20" s="6"/>
-      <c r="CQX20" s="6"/>
-      <c r="CRB20" s="6"/>
-      <c r="CRF20" s="6"/>
-      <c r="CRJ20" s="6"/>
-      <c r="CRN20" s="6"/>
-      <c r="CRR20" s="6"/>
-      <c r="CRV20" s="6"/>
-      <c r="CRZ20" s="6"/>
-      <c r="CSD20" s="6"/>
-      <c r="CSH20" s="6"/>
-      <c r="CSL20" s="6"/>
-      <c r="CSP20" s="6"/>
-      <c r="CST20" s="6"/>
-      <c r="CSX20" s="6"/>
-      <c r="CTB20" s="6"/>
-      <c r="CTF20" s="6"/>
-      <c r="CTJ20" s="6"/>
-      <c r="CTN20" s="6"/>
-      <c r="CTR20" s="6"/>
-      <c r="CTV20" s="6"/>
-      <c r="CTZ20" s="6"/>
-      <c r="CUD20" s="6"/>
-      <c r="CUH20" s="6"/>
-      <c r="CUL20" s="6"/>
-      <c r="CUP20" s="6"/>
-      <c r="CUT20" s="6"/>
-      <c r="CUX20" s="6"/>
-      <c r="CVB20" s="6"/>
-      <c r="CVF20" s="6"/>
-      <c r="CVJ20" s="6"/>
-      <c r="CVN20" s="6"/>
-      <c r="CVR20" s="6"/>
-      <c r="CVV20" s="6"/>
-      <c r="CVZ20" s="6"/>
-      <c r="CWD20" s="6"/>
-      <c r="CWH20" s="6"/>
-      <c r="CWL20" s="6"/>
-      <c r="CWP20" s="6"/>
-      <c r="CWT20" s="6"/>
-      <c r="CWX20" s="6"/>
-      <c r="CXB20" s="6"/>
-      <c r="CXF20" s="6"/>
-      <c r="CXJ20" s="6"/>
-      <c r="CXN20" s="6"/>
-      <c r="CXR20" s="6"/>
-      <c r="CXV20" s="6"/>
-      <c r="CXZ20" s="6"/>
-      <c r="CYD20" s="6"/>
-      <c r="CYH20" s="6"/>
-      <c r="CYL20" s="6"/>
-      <c r="CYP20" s="6"/>
-      <c r="CYT20" s="6"/>
-      <c r="CYX20" s="6"/>
-      <c r="CZB20" s="6"/>
-      <c r="CZF20" s="6"/>
-      <c r="CZJ20" s="6"/>
-      <c r="CZN20" s="6"/>
-      <c r="CZR20" s="6"/>
-      <c r="CZV20" s="6"/>
-      <c r="CZZ20" s="6"/>
-      <c r="DAD20" s="6"/>
-      <c r="DAH20" s="6"/>
-      <c r="DAL20" s="6"/>
-      <c r="DAP20" s="6"/>
-      <c r="DAT20" s="6"/>
-      <c r="DAX20" s="6"/>
-      <c r="DBB20" s="6"/>
-      <c r="DBF20" s="6"/>
-      <c r="DBJ20" s="6"/>
-      <c r="DBN20" s="6"/>
-      <c r="DBR20" s="6"/>
-      <c r="DBV20" s="6"/>
-      <c r="DBZ20" s="6"/>
-      <c r="DCD20" s="6"/>
-      <c r="DCH20" s="6"/>
-      <c r="DCL20" s="6"/>
-      <c r="DCP20" s="6"/>
-      <c r="DCT20" s="6"/>
-      <c r="DCX20" s="6"/>
-      <c r="DDB20" s="6"/>
-      <c r="DDF20" s="6"/>
-      <c r="DDJ20" s="6"/>
-      <c r="DDN20" s="6"/>
-      <c r="DDR20" s="6"/>
-      <c r="DDV20" s="6"/>
-      <c r="DDZ20" s="6"/>
-      <c r="DED20" s="6"/>
-      <c r="DEH20" s="6"/>
-      <c r="DEL20" s="6"/>
-      <c r="DEP20" s="6"/>
-      <c r="DET20" s="6"/>
-      <c r="DEX20" s="6"/>
-      <c r="DFB20" s="6"/>
-      <c r="DFF20" s="6"/>
-      <c r="DFJ20" s="6"/>
-      <c r="DFN20" s="6"/>
-      <c r="DFR20" s="6"/>
-      <c r="DFV20" s="6"/>
-      <c r="DFZ20" s="6"/>
-      <c r="DGD20" s="6"/>
-      <c r="DGH20" s="6"/>
-      <c r="DGL20" s="6"/>
-      <c r="DGP20" s="6"/>
-      <c r="DGT20" s="6"/>
-      <c r="DGX20" s="6"/>
-      <c r="DHB20" s="6"/>
-      <c r="DHF20" s="6"/>
-      <c r="DHJ20" s="6"/>
-      <c r="DHN20" s="6"/>
-      <c r="DHR20" s="6"/>
-      <c r="DHV20" s="6"/>
-      <c r="DHZ20" s="6"/>
-      <c r="DID20" s="6"/>
-      <c r="DIH20" s="6"/>
-      <c r="DIL20" s="6"/>
-      <c r="DIP20" s="6"/>
-      <c r="DIT20" s="6"/>
-      <c r="DIX20" s="6"/>
-      <c r="DJB20" s="6"/>
-      <c r="DJF20" s="6"/>
-      <c r="DJJ20" s="6"/>
-      <c r="DJN20" s="6"/>
-      <c r="DJR20" s="6"/>
-      <c r="DJV20" s="6"/>
-      <c r="DJZ20" s="6"/>
-      <c r="DKD20" s="6"/>
-      <c r="DKH20" s="6"/>
-      <c r="DKL20" s="6"/>
-      <c r="DKP20" s="6"/>
-      <c r="DKT20" s="6"/>
-      <c r="DKX20" s="6"/>
-      <c r="DLB20" s="6"/>
-      <c r="DLF20" s="6"/>
-      <c r="DLJ20" s="6"/>
-      <c r="DLN20" s="6"/>
-      <c r="DLR20" s="6"/>
-      <c r="DLV20" s="6"/>
-      <c r="DLZ20" s="6"/>
-      <c r="DMD20" s="6"/>
-      <c r="DMH20" s="6"/>
-      <c r="DML20" s="6"/>
-      <c r="DMP20" s="6"/>
-      <c r="DMT20" s="6"/>
-      <c r="DMX20" s="6"/>
-      <c r="DNB20" s="6"/>
-      <c r="DNF20" s="6"/>
-      <c r="DNJ20" s="6"/>
-      <c r="DNN20" s="6"/>
-      <c r="DNR20" s="6"/>
-      <c r="DNV20" s="6"/>
-      <c r="DNZ20" s="6"/>
-      <c r="DOD20" s="6"/>
-      <c r="DOH20" s="6"/>
-      <c r="DOL20" s="6"/>
-      <c r="DOP20" s="6"/>
-      <c r="DOT20" s="6"/>
-      <c r="DOX20" s="6"/>
-      <c r="DPB20" s="6"/>
-      <c r="DPF20" s="6"/>
-      <c r="DPJ20" s="6"/>
-      <c r="DPN20" s="6"/>
-      <c r="DPR20" s="6"/>
-      <c r="DPV20" s="6"/>
-      <c r="DPZ20" s="6"/>
-      <c r="DQD20" s="6"/>
-      <c r="DQH20" s="6"/>
-      <c r="DQL20" s="6"/>
-      <c r="DQP20" s="6"/>
-      <c r="DQT20" s="6"/>
-      <c r="DQX20" s="6"/>
-      <c r="DRB20" s="6"/>
-      <c r="DRF20" s="6"/>
-      <c r="DRJ20" s="6"/>
-      <c r="DRN20" s="6"/>
-      <c r="DRR20" s="6"/>
-      <c r="DRV20" s="6"/>
-      <c r="DRZ20" s="6"/>
-      <c r="DSD20" s="6"/>
-      <c r="DSH20" s="6"/>
-      <c r="DSL20" s="6"/>
-      <c r="DSP20" s="6"/>
-      <c r="DST20" s="6"/>
-      <c r="DSX20" s="6"/>
-      <c r="DTB20" s="6"/>
-      <c r="DTF20" s="6"/>
-      <c r="DTJ20" s="6"/>
-      <c r="DTN20" s="6"/>
-      <c r="DTR20" s="6"/>
-      <c r="DTV20" s="6"/>
-      <c r="DTZ20" s="6"/>
-      <c r="DUD20" s="6"/>
-      <c r="DUH20" s="6"/>
-      <c r="DUL20" s="6"/>
-      <c r="DUP20" s="6"/>
-      <c r="DUT20" s="6"/>
-      <c r="DUX20" s="6"/>
-      <c r="DVB20" s="6"/>
-      <c r="DVF20" s="6"/>
-      <c r="DVJ20" s="6"/>
-      <c r="DVN20" s="6"/>
-      <c r="DVR20" s="6"/>
-      <c r="DVV20" s="6"/>
-      <c r="DVZ20" s="6"/>
-      <c r="DWD20" s="6"/>
-      <c r="DWH20" s="6"/>
-      <c r="DWL20" s="6"/>
-      <c r="DWP20" s="6"/>
-      <c r="DWT20" s="6"/>
-      <c r="DWX20" s="6"/>
-      <c r="DXB20" s="6"/>
-      <c r="DXF20" s="6"/>
-      <c r="DXJ20" s="6"/>
-      <c r="DXN20" s="6"/>
-      <c r="DXR20" s="6"/>
-      <c r="DXV20" s="6"/>
-      <c r="DXZ20" s="6"/>
-      <c r="DYD20" s="6"/>
-      <c r="DYH20" s="6"/>
-      <c r="DYL20" s="6"/>
-      <c r="DYP20" s="6"/>
-      <c r="DYT20" s="6"/>
-      <c r="DYX20" s="6"/>
-      <c r="DZB20" s="6"/>
-      <c r="DZF20" s="6"/>
-      <c r="DZJ20" s="6"/>
-      <c r="DZN20" s="6"/>
-      <c r="DZR20" s="6"/>
-      <c r="DZV20" s="6"/>
-      <c r="DZZ20" s="6"/>
-      <c r="EAD20" s="6"/>
-      <c r="EAH20" s="6"/>
-      <c r="EAL20" s="6"/>
-      <c r="EAP20" s="6"/>
-      <c r="EAT20" s="6"/>
-      <c r="EAX20" s="6"/>
-      <c r="EBB20" s="6"/>
-      <c r="EBF20" s="6"/>
-      <c r="EBJ20" s="6"/>
-      <c r="EBN20" s="6"/>
-      <c r="EBR20" s="6"/>
-      <c r="EBV20" s="6"/>
-      <c r="EBZ20" s="6"/>
-      <c r="ECD20" s="6"/>
-      <c r="ECH20" s="6"/>
-      <c r="ECL20" s="6"/>
-      <c r="ECP20" s="6"/>
-      <c r="ECT20" s="6"/>
-      <c r="ECX20" s="6"/>
-      <c r="EDB20" s="6"/>
-      <c r="EDF20" s="6"/>
-      <c r="EDJ20" s="6"/>
-      <c r="EDN20" s="6"/>
-      <c r="EDR20" s="6"/>
-      <c r="EDV20" s="6"/>
-      <c r="EDZ20" s="6"/>
-      <c r="EED20" s="6"/>
-      <c r="EEH20" s="6"/>
-      <c r="EEL20" s="6"/>
-      <c r="EEP20" s="6"/>
-      <c r="EET20" s="6"/>
-      <c r="EEX20" s="6"/>
-      <c r="EFB20" s="6"/>
-      <c r="EFF20" s="6"/>
-      <c r="EFJ20" s="6"/>
-      <c r="EFN20" s="6"/>
-      <c r="EFR20" s="6"/>
-      <c r="EFV20" s="6"/>
-      <c r="EFZ20" s="6"/>
-      <c r="EGD20" s="6"/>
-      <c r="EGH20" s="6"/>
-      <c r="EGL20" s="6"/>
-      <c r="EGP20" s="6"/>
-      <c r="EGT20" s="6"/>
-      <c r="EGX20" s="6"/>
-      <c r="EHB20" s="6"/>
-      <c r="EHF20" s="6"/>
-      <c r="EHJ20" s="6"/>
-      <c r="EHN20" s="6"/>
-      <c r="EHR20" s="6"/>
-      <c r="EHV20" s="6"/>
-      <c r="EHZ20" s="6"/>
-      <c r="EID20" s="6"/>
-      <c r="EIH20" s="6"/>
-      <c r="EIL20" s="6"/>
-      <c r="EIP20" s="6"/>
-      <c r="EIT20" s="6"/>
-      <c r="EIX20" s="6"/>
-      <c r="EJB20" s="6"/>
-      <c r="EJF20" s="6"/>
-      <c r="EJJ20" s="6"/>
-      <c r="EJN20" s="6"/>
-      <c r="EJR20" s="6"/>
-      <c r="EJV20" s="6"/>
-      <c r="EJZ20" s="6"/>
-      <c r="EKD20" s="6"/>
-      <c r="EKH20" s="6"/>
-      <c r="EKL20" s="6"/>
-      <c r="EKP20" s="6"/>
-      <c r="EKT20" s="6"/>
-      <c r="EKX20" s="6"/>
-      <c r="ELB20" s="6"/>
-      <c r="ELF20" s="6"/>
-      <c r="ELJ20" s="6"/>
-      <c r="ELN20" s="6"/>
-      <c r="ELR20" s="6"/>
-      <c r="ELV20" s="6"/>
-      <c r="ELZ20" s="6"/>
-      <c r="EMD20" s="6"/>
-      <c r="EMH20" s="6"/>
-      <c r="EML20" s="6"/>
-      <c r="EMP20" s="6"/>
-      <c r="EMT20" s="6"/>
-      <c r="EMX20" s="6"/>
-      <c r="ENB20" s="6"/>
-      <c r="ENF20" s="6"/>
-      <c r="ENJ20" s="6"/>
-      <c r="ENN20" s="6"/>
-      <c r="ENR20" s="6"/>
-      <c r="ENV20" s="6"/>
-      <c r="ENZ20" s="6"/>
-      <c r="EOD20" s="6"/>
-      <c r="EOH20" s="6"/>
-      <c r="EOL20" s="6"/>
-      <c r="EOP20" s="6"/>
-      <c r="EOT20" s="6"/>
-      <c r="EOX20" s="6"/>
-      <c r="EPB20" s="6"/>
-      <c r="EPF20" s="6"/>
-      <c r="EPJ20" s="6"/>
-      <c r="EPN20" s="6"/>
-      <c r="EPR20" s="6"/>
-      <c r="EPV20" s="6"/>
-      <c r="EPZ20" s="6"/>
-      <c r="EQD20" s="6"/>
-      <c r="EQH20" s="6"/>
-      <c r="EQL20" s="6"/>
-      <c r="EQP20" s="6"/>
-      <c r="EQT20" s="6"/>
-      <c r="EQX20" s="6"/>
-      <c r="ERB20" s="6"/>
-      <c r="ERF20" s="6"/>
-      <c r="ERJ20" s="6"/>
-      <c r="ERN20" s="6"/>
-      <c r="ERR20" s="6"/>
-      <c r="ERV20" s="6"/>
-      <c r="ERZ20" s="6"/>
-      <c r="ESD20" s="6"/>
-      <c r="ESH20" s="6"/>
-      <c r="ESL20" s="6"/>
-      <c r="ESP20" s="6"/>
-      <c r="EST20" s="6"/>
-      <c r="ESX20" s="6"/>
-      <c r="ETB20" s="6"/>
-      <c r="ETF20" s="6"/>
-      <c r="ETJ20" s="6"/>
-      <c r="ETN20" s="6"/>
-      <c r="ETR20" s="6"/>
-      <c r="ETV20" s="6"/>
-      <c r="ETZ20" s="6"/>
-      <c r="EUD20" s="6"/>
-      <c r="EUH20" s="6"/>
-      <c r="EUL20" s="6"/>
-      <c r="EUP20" s="6"/>
-      <c r="EUT20" s="6"/>
-      <c r="EUX20" s="6"/>
-      <c r="EVB20" s="6"/>
-      <c r="EVF20" s="6"/>
-      <c r="EVJ20" s="6"/>
-      <c r="EVN20" s="6"/>
-      <c r="EVR20" s="6"/>
-      <c r="EVV20" s="6"/>
-      <c r="EVZ20" s="6"/>
-      <c r="EWD20" s="6"/>
-      <c r="EWH20" s="6"/>
-      <c r="EWL20" s="6"/>
-      <c r="EWP20" s="6"/>
-      <c r="EWT20" s="6"/>
-      <c r="EWX20" s="6"/>
-      <c r="EXB20" s="6"/>
-      <c r="EXF20" s="6"/>
-      <c r="EXJ20" s="6"/>
-      <c r="EXN20" s="6"/>
-      <c r="EXR20" s="6"/>
-      <c r="EXV20" s="6"/>
-      <c r="EXZ20" s="6"/>
-      <c r="EYD20" s="6"/>
-      <c r="EYH20" s="6"/>
-      <c r="EYL20" s="6"/>
-      <c r="EYP20" s="6"/>
-      <c r="EYT20" s="6"/>
-      <c r="EYX20" s="6"/>
-      <c r="EZB20" s="6"/>
-      <c r="EZF20" s="6"/>
-      <c r="EZJ20" s="6"/>
-      <c r="EZN20" s="6"/>
-      <c r="EZR20" s="6"/>
-      <c r="EZV20" s="6"/>
-      <c r="EZZ20" s="6"/>
-      <c r="FAD20" s="6"/>
-      <c r="FAH20" s="6"/>
-      <c r="FAL20" s="6"/>
-      <c r="FAP20" s="6"/>
-      <c r="FAT20" s="6"/>
-      <c r="FAX20" s="6"/>
-      <c r="FBB20" s="6"/>
-      <c r="FBF20" s="6"/>
-      <c r="FBJ20" s="6"/>
-      <c r="FBN20" s="6"/>
-      <c r="FBR20" s="6"/>
-      <c r="FBV20" s="6"/>
-      <c r="FBZ20" s="6"/>
-      <c r="FCD20" s="6"/>
-      <c r="FCH20" s="6"/>
-      <c r="FCL20" s="6"/>
-      <c r="FCP20" s="6"/>
-      <c r="FCT20" s="6"/>
-      <c r="FCX20" s="6"/>
-      <c r="FDB20" s="6"/>
-      <c r="FDF20" s="6"/>
-      <c r="FDJ20" s="6"/>
-      <c r="FDN20" s="6"/>
-      <c r="FDR20" s="6"/>
-      <c r="FDV20" s="6"/>
-      <c r="FDZ20" s="6"/>
-      <c r="FED20" s="6"/>
-      <c r="FEH20" s="6"/>
-      <c r="FEL20" s="6"/>
-      <c r="FEP20" s="6"/>
-      <c r="FET20" s="6"/>
-      <c r="FEX20" s="6"/>
-      <c r="FFB20" s="6"/>
-      <c r="FFF20" s="6"/>
-      <c r="FFJ20" s="6"/>
-      <c r="FFN20" s="6"/>
-      <c r="FFR20" s="6"/>
-      <c r="FFV20" s="6"/>
-      <c r="FFZ20" s="6"/>
-      <c r="FGD20" s="6"/>
-      <c r="FGH20" s="6"/>
-      <c r="FGL20" s="6"/>
-      <c r="FGP20" s="6"/>
-      <c r="FGT20" s="6"/>
-      <c r="FGX20" s="6"/>
-      <c r="FHB20" s="6"/>
-      <c r="FHF20" s="6"/>
-      <c r="FHJ20" s="6"/>
-      <c r="FHN20" s="6"/>
-      <c r="FHR20" s="6"/>
-      <c r="FHV20" s="6"/>
-      <c r="FHZ20" s="6"/>
-      <c r="FID20" s="6"/>
-      <c r="FIH20" s="6"/>
-      <c r="FIL20" s="6"/>
-      <c r="FIP20" s="6"/>
-      <c r="FIT20" s="6"/>
-      <c r="FIX20" s="6"/>
-      <c r="FJB20" s="6"/>
-      <c r="FJF20" s="6"/>
-      <c r="FJJ20" s="6"/>
-      <c r="FJN20" s="6"/>
-      <c r="FJR20" s="6"/>
-      <c r="FJV20" s="6"/>
-      <c r="FJZ20" s="6"/>
-      <c r="FKD20" s="6"/>
-      <c r="FKH20" s="6"/>
-      <c r="FKL20" s="6"/>
-      <c r="FKP20" s="6"/>
-      <c r="FKT20" s="6"/>
-      <c r="FKX20" s="6"/>
-      <c r="FLB20" s="6"/>
-      <c r="FLF20" s="6"/>
-      <c r="FLJ20" s="6"/>
-      <c r="FLN20" s="6"/>
-      <c r="FLR20" s="6"/>
-      <c r="FLV20" s="6"/>
-      <c r="FLZ20" s="6"/>
-      <c r="FMD20" s="6"/>
-      <c r="FMH20" s="6"/>
-      <c r="FML20" s="6"/>
-      <c r="FMP20" s="6"/>
-      <c r="FMT20" s="6"/>
-      <c r="FMX20" s="6"/>
-      <c r="FNB20" s="6"/>
-      <c r="FNF20" s="6"/>
-      <c r="FNJ20" s="6"/>
-      <c r="FNN20" s="6"/>
-      <c r="FNR20" s="6"/>
-      <c r="FNV20" s="6"/>
-      <c r="FNZ20" s="6"/>
-      <c r="FOD20" s="6"/>
-      <c r="FOH20" s="6"/>
-      <c r="FOL20" s="6"/>
-      <c r="FOP20" s="6"/>
-      <c r="FOT20" s="6"/>
-      <c r="FOX20" s="6"/>
-      <c r="FPB20" s="6"/>
-      <c r="FPF20" s="6"/>
-      <c r="FPJ20" s="6"/>
-      <c r="FPN20" s="6"/>
-      <c r="FPR20" s="6"/>
-      <c r="FPV20" s="6"/>
-      <c r="FPZ20" s="6"/>
-      <c r="FQD20" s="6"/>
-      <c r="FQH20" s="6"/>
-      <c r="FQL20" s="6"/>
-      <c r="FQP20" s="6"/>
-      <c r="FQT20" s="6"/>
-      <c r="FQX20" s="6"/>
-      <c r="FRB20" s="6"/>
-      <c r="FRF20" s="6"/>
-      <c r="FRJ20" s="6"/>
-      <c r="FRN20" s="6"/>
-      <c r="FRR20" s="6"/>
-      <c r="FRV20" s="6"/>
-      <c r="FRZ20" s="6"/>
-      <c r="FSD20" s="6"/>
-      <c r="FSH20" s="6"/>
-      <c r="FSL20" s="6"/>
-      <c r="FSP20" s="6"/>
-      <c r="FST20" s="6"/>
-      <c r="FSX20" s="6"/>
-      <c r="FTB20" s="6"/>
-      <c r="FTF20" s="6"/>
-      <c r="FTJ20" s="6"/>
-      <c r="FTN20" s="6"/>
-      <c r="FTR20" s="6"/>
-      <c r="FTV20" s="6"/>
-      <c r="FTZ20" s="6"/>
-      <c r="FUD20" s="6"/>
-      <c r="FUH20" s="6"/>
-      <c r="FUL20" s="6"/>
-      <c r="FUP20" s="6"/>
-      <c r="FUT20" s="6"/>
-      <c r="FUX20" s="6"/>
-      <c r="FVB20" s="6"/>
-      <c r="FVF20" s="6"/>
-      <c r="FVJ20" s="6"/>
-      <c r="FVN20" s="6"/>
-      <c r="FVR20" s="6"/>
-      <c r="FVV20" s="6"/>
-      <c r="FVZ20" s="6"/>
-      <c r="FWD20" s="6"/>
-      <c r="FWH20" s="6"/>
-      <c r="FWL20" s="6"/>
-      <c r="FWP20" s="6"/>
-      <c r="FWT20" s="6"/>
-      <c r="FWX20" s="6"/>
-      <c r="FXB20" s="6"/>
-      <c r="FXF20" s="6"/>
-      <c r="FXJ20" s="6"/>
-      <c r="FXN20" s="6"/>
-      <c r="FXR20" s="6"/>
-      <c r="FXV20" s="6"/>
-      <c r="FXZ20" s="6"/>
-      <c r="FYD20" s="6"/>
-      <c r="FYH20" s="6"/>
-      <c r="FYL20" s="6"/>
-      <c r="FYP20" s="6"/>
-      <c r="FYT20" s="6"/>
-      <c r="FYX20" s="6"/>
-      <c r="FZB20" s="6"/>
-      <c r="FZF20" s="6"/>
-      <c r="FZJ20" s="6"/>
-      <c r="FZN20" s="6"/>
-      <c r="FZR20" s="6"/>
-      <c r="FZV20" s="6"/>
-      <c r="FZZ20" s="6"/>
-      <c r="GAD20" s="6"/>
-      <c r="GAH20" s="6"/>
-      <c r="GAL20" s="6"/>
-      <c r="GAP20" s="6"/>
-      <c r="GAT20" s="6"/>
-      <c r="GAX20" s="6"/>
-      <c r="GBB20" s="6"/>
-      <c r="GBF20" s="6"/>
-      <c r="GBJ20" s="6"/>
-      <c r="GBN20" s="6"/>
-      <c r="GBR20" s="6"/>
-      <c r="GBV20" s="6"/>
-      <c r="GBZ20" s="6"/>
-      <c r="GCD20" s="6"/>
-      <c r="GCH20" s="6"/>
-      <c r="GCL20" s="6"/>
-      <c r="GCP20" s="6"/>
-      <c r="GCT20" s="6"/>
-      <c r="GCX20" s="6"/>
-      <c r="GDB20" s="6"/>
-      <c r="GDF20" s="6"/>
-      <c r="GDJ20" s="6"/>
-      <c r="GDN20" s="6"/>
-      <c r="GDR20" s="6"/>
-      <c r="GDV20" s="6"/>
-      <c r="GDZ20" s="6"/>
-      <c r="GED20" s="6"/>
-      <c r="GEH20" s="6"/>
-      <c r="GEL20" s="6"/>
-      <c r="GEP20" s="6"/>
-      <c r="GET20" s="6"/>
-      <c r="GEX20" s="6"/>
-      <c r="GFB20" s="6"/>
-      <c r="GFF20" s="6"/>
-      <c r="GFJ20" s="6"/>
-      <c r="GFN20" s="6"/>
-      <c r="GFR20" s="6"/>
-      <c r="GFV20" s="6"/>
-      <c r="GFZ20" s="6"/>
-      <c r="GGD20" s="6"/>
-      <c r="GGH20" s="6"/>
-      <c r="GGL20" s="6"/>
-      <c r="GGP20" s="6"/>
-      <c r="GGT20" s="6"/>
-      <c r="GGX20" s="6"/>
-      <c r="GHB20" s="6"/>
-      <c r="GHF20" s="6"/>
-      <c r="GHJ20" s="6"/>
-      <c r="GHN20" s="6"/>
-      <c r="GHR20" s="6"/>
-      <c r="GHV20" s="6"/>
-      <c r="GHZ20" s="6"/>
-      <c r="GID20" s="6"/>
-      <c r="GIH20" s="6"/>
-      <c r="GIL20" s="6"/>
-      <c r="GIP20" s="6"/>
-      <c r="GIT20" s="6"/>
-      <c r="GIX20" s="6"/>
-      <c r="GJB20" s="6"/>
-      <c r="GJF20" s="6"/>
-      <c r="GJJ20" s="6"/>
-      <c r="GJN20" s="6"/>
-      <c r="GJR20" s="6"/>
-      <c r="GJV20" s="6"/>
-      <c r="GJZ20" s="6"/>
-      <c r="GKD20" s="6"/>
-      <c r="GKH20" s="6"/>
-      <c r="GKL20" s="6"/>
-      <c r="GKP20" s="6"/>
-      <c r="GKT20" s="6"/>
-      <c r="GKX20" s="6"/>
-      <c r="GLB20" s="6"/>
-      <c r="GLF20" s="6"/>
-      <c r="GLJ20" s="6"/>
-      <c r="GLN20" s="6"/>
-      <c r="GLR20" s="6"/>
-      <c r="GLV20" s="6"/>
-      <c r="GLZ20" s="6"/>
-      <c r="GMD20" s="6"/>
-      <c r="GMH20" s="6"/>
-      <c r="GML20" s="6"/>
-      <c r="GMP20" s="6"/>
-      <c r="GMT20" s="6"/>
-      <c r="GMX20" s="6"/>
-      <c r="GNB20" s="6"/>
-      <c r="GNF20" s="6"/>
-      <c r="GNJ20" s="6"/>
-      <c r="GNN20" s="6"/>
-      <c r="GNR20" s="6"/>
-      <c r="GNV20" s="6"/>
-      <c r="GNZ20" s="6"/>
-      <c r="GOD20" s="6"/>
-      <c r="GOH20" s="6"/>
-      <c r="GOL20" s="6"/>
-      <c r="GOP20" s="6"/>
-      <c r="GOT20" s="6"/>
-      <c r="GOX20" s="6"/>
-      <c r="GPB20" s="6"/>
-      <c r="GPF20" s="6"/>
-      <c r="GPJ20" s="6"/>
-      <c r="GPN20" s="6"/>
-      <c r="GPR20" s="6"/>
-      <c r="GPV20" s="6"/>
-      <c r="GPZ20" s="6"/>
-      <c r="GQD20" s="6"/>
-      <c r="GQH20" s="6"/>
-      <c r="GQL20" s="6"/>
-      <c r="GQP20" s="6"/>
-      <c r="GQT20" s="6"/>
-      <c r="GQX20" s="6"/>
-      <c r="GRB20" s="6"/>
-      <c r="GRF20" s="6"/>
-      <c r="GRJ20" s="6"/>
-      <c r="GRN20" s="6"/>
-      <c r="GRR20" s="6"/>
-      <c r="GRV20" s="6"/>
-      <c r="GRZ20" s="6"/>
-      <c r="GSD20" s="6"/>
-      <c r="GSH20" s="6"/>
-      <c r="GSL20" s="6"/>
-      <c r="GSP20" s="6"/>
-      <c r="GST20" s="6"/>
-      <c r="GSX20" s="6"/>
-      <c r="GTB20" s="6"/>
-      <c r="GTF20" s="6"/>
-      <c r="GTJ20" s="6"/>
-      <c r="GTN20" s="6"/>
-      <c r="GTR20" s="6"/>
-      <c r="GTV20" s="6"/>
-      <c r="GTZ20" s="6"/>
-      <c r="GUD20" s="6"/>
-      <c r="GUH20" s="6"/>
-      <c r="GUL20" s="6"/>
-      <c r="GUP20" s="6"/>
-      <c r="GUT20" s="6"/>
-      <c r="GUX20" s="6"/>
-      <c r="GVB20" s="6"/>
-      <c r="GVF20" s="6"/>
-      <c r="GVJ20" s="6"/>
-      <c r="GVN20" s="6"/>
-      <c r="GVR20" s="6"/>
-      <c r="GVV20" s="6"/>
-      <c r="GVZ20" s="6"/>
-      <c r="GWD20" s="6"/>
-      <c r="GWH20" s="6"/>
-      <c r="GWL20" s="6"/>
-      <c r="GWP20" s="6"/>
-      <c r="GWT20" s="6"/>
-      <c r="GWX20" s="6"/>
-      <c r="GXB20" s="6"/>
-      <c r="GXF20" s="6"/>
-      <c r="GXJ20" s="6"/>
-      <c r="GXN20" s="6"/>
-      <c r="GXR20" s="6"/>
-      <c r="GXV20" s="6"/>
-      <c r="GXZ20" s="6"/>
-      <c r="GYD20" s="6"/>
-      <c r="GYH20" s="6"/>
-      <c r="GYL20" s="6"/>
-      <c r="GYP20" s="6"/>
-      <c r="GYT20" s="6"/>
-      <c r="GYX20" s="6"/>
-      <c r="GZB20" s="6"/>
-      <c r="GZF20" s="6"/>
-      <c r="GZJ20" s="6"/>
-      <c r="GZN20" s="6"/>
-      <c r="GZR20" s="6"/>
-      <c r="GZV20" s="6"/>
-      <c r="GZZ20" s="6"/>
-      <c r="HAD20" s="6"/>
-      <c r="HAH20" s="6"/>
-      <c r="HAL20" s="6"/>
-      <c r="HAP20" s="6"/>
-      <c r="HAT20" s="6"/>
-      <c r="HAX20" s="6"/>
-      <c r="HBB20" s="6"/>
-      <c r="HBF20" s="6"/>
-      <c r="HBJ20" s="6"/>
-      <c r="HBN20" s="6"/>
-      <c r="HBR20" s="6"/>
-      <c r="HBV20" s="6"/>
-      <c r="HBZ20" s="6"/>
-      <c r="HCD20" s="6"/>
-      <c r="HCH20" s="6"/>
-      <c r="HCL20" s="6"/>
-      <c r="HCP20" s="6"/>
-      <c r="HCT20" s="6"/>
-      <c r="HCX20" s="6"/>
-      <c r="HDB20" s="6"/>
-      <c r="HDF20" s="6"/>
-      <c r="HDJ20" s="6"/>
-      <c r="HDN20" s="6"/>
-      <c r="HDR20" s="6"/>
-      <c r="HDV20" s="6"/>
-      <c r="HDZ20" s="6"/>
-      <c r="HED20" s="6"/>
-      <c r="HEH20" s="6"/>
-      <c r="HEL20" s="6"/>
-      <c r="HEP20" s="6"/>
-      <c r="HET20" s="6"/>
-      <c r="HEX20" s="6"/>
-      <c r="HFB20" s="6"/>
-      <c r="HFF20" s="6"/>
-      <c r="HFJ20" s="6"/>
-      <c r="HFN20" s="6"/>
-      <c r="HFR20" s="6"/>
-      <c r="HFV20" s="6"/>
-      <c r="HFZ20" s="6"/>
-      <c r="HGD20" s="6"/>
-      <c r="HGH20" s="6"/>
-      <c r="HGL20" s="6"/>
-      <c r="HGP20" s="6"/>
-      <c r="HGT20" s="6"/>
-      <c r="HGX20" s="6"/>
-      <c r="HHB20" s="6"/>
-      <c r="HHF20" s="6"/>
-      <c r="HHJ20" s="6"/>
-      <c r="HHN20" s="6"/>
-      <c r="HHR20" s="6"/>
-      <c r="HHV20" s="6"/>
-      <c r="HHZ20" s="6"/>
-      <c r="HID20" s="6"/>
-      <c r="HIH20" s="6"/>
-      <c r="HIL20" s="6"/>
-      <c r="HIP20" s="6"/>
-      <c r="HIT20" s="6"/>
-      <c r="HIX20" s="6"/>
-      <c r="HJB20" s="6"/>
-      <c r="HJF20" s="6"/>
-      <c r="HJJ20" s="6"/>
-      <c r="HJN20" s="6"/>
-      <c r="HJR20" s="6"/>
-      <c r="HJV20" s="6"/>
-      <c r="HJZ20" s="6"/>
-      <c r="HKD20" s="6"/>
-      <c r="HKH20" s="6"/>
-      <c r="HKL20" s="6"/>
-      <c r="HKP20" s="6"/>
-      <c r="HKT20" s="6"/>
-      <c r="HKX20" s="6"/>
-      <c r="HLB20" s="6"/>
-      <c r="HLF20" s="6"/>
-      <c r="HLJ20" s="6"/>
-      <c r="HLN20" s="6"/>
-      <c r="HLR20" s="6"/>
-      <c r="HLV20" s="6"/>
-      <c r="HLZ20" s="6"/>
-      <c r="HMD20" s="6"/>
-      <c r="HMH20" s="6"/>
-      <c r="HML20" s="6"/>
-      <c r="HMP20" s="6"/>
-      <c r="HMT20" s="6"/>
-      <c r="HMX20" s="6"/>
-      <c r="HNB20" s="6"/>
-      <c r="HNF20" s="6"/>
-      <c r="HNJ20" s="6"/>
-      <c r="HNN20" s="6"/>
-      <c r="HNR20" s="6"/>
-      <c r="HNV20" s="6"/>
-      <c r="HNZ20" s="6"/>
-      <c r="HOD20" s="6"/>
-      <c r="HOH20" s="6"/>
-      <c r="HOL20" s="6"/>
-      <c r="HOP20" s="6"/>
-      <c r="HOT20" s="6"/>
-      <c r="HOX20" s="6"/>
-      <c r="HPB20" s="6"/>
-      <c r="HPF20" s="6"/>
-      <c r="HPJ20" s="6"/>
-      <c r="HPN20" s="6"/>
-      <c r="HPR20" s="6"/>
-      <c r="HPV20" s="6"/>
-      <c r="HPZ20" s="6"/>
-      <c r="HQD20" s="6"/>
-      <c r="HQH20" s="6"/>
-      <c r="HQL20" s="6"/>
-      <c r="HQP20" s="6"/>
-      <c r="HQT20" s="6"/>
-      <c r="HQX20" s="6"/>
-      <c r="HRB20" s="6"/>
-      <c r="HRF20" s="6"/>
-      <c r="HRJ20" s="6"/>
-      <c r="HRN20" s="6"/>
-      <c r="HRR20" s="6"/>
-      <c r="HRV20" s="6"/>
-      <c r="HRZ20" s="6"/>
-      <c r="HSD20" s="6"/>
-      <c r="HSH20" s="6"/>
-      <c r="HSL20" s="6"/>
-      <c r="HSP20" s="6"/>
-      <c r="HST20" s="6"/>
-      <c r="HSX20" s="6"/>
-      <c r="HTB20" s="6"/>
-      <c r="HTF20" s="6"/>
-      <c r="HTJ20" s="6"/>
-      <c r="HTN20" s="6"/>
-      <c r="HTR20" s="6"/>
-      <c r="HTV20" s="6"/>
-      <c r="HTZ20" s="6"/>
-      <c r="HUD20" s="6"/>
-      <c r="HUH20" s="6"/>
-      <c r="HUL20" s="6"/>
-      <c r="HUP20" s="6"/>
-      <c r="HUT20" s="6"/>
-      <c r="HUX20" s="6"/>
-      <c r="HVB20" s="6"/>
-      <c r="HVF20" s="6"/>
-      <c r="HVJ20" s="6"/>
-      <c r="HVN20" s="6"/>
-      <c r="HVR20" s="6"/>
-      <c r="HVV20" s="6"/>
-      <c r="HVZ20" s="6"/>
-      <c r="HWD20" s="6"/>
-      <c r="HWH20" s="6"/>
-      <c r="HWL20" s="6"/>
-      <c r="HWP20" s="6"/>
-      <c r="HWT20" s="6"/>
-      <c r="HWX20" s="6"/>
-      <c r="HXB20" s="6"/>
-      <c r="HXF20" s="6"/>
-      <c r="HXJ20" s="6"/>
-      <c r="HXN20" s="6"/>
-      <c r="HXR20" s="6"/>
-      <c r="HXV20" s="6"/>
-      <c r="HXZ20" s="6"/>
-      <c r="HYD20" s="6"/>
-      <c r="HYH20" s="6"/>
-      <c r="HYL20" s="6"/>
-      <c r="HYP20" s="6"/>
-      <c r="HYT20" s="6"/>
-      <c r="HYX20" s="6"/>
-      <c r="HZB20" s="6"/>
-      <c r="HZF20" s="6"/>
-      <c r="HZJ20" s="6"/>
-      <c r="HZN20" s="6"/>
-      <c r="HZR20" s="6"/>
-      <c r="HZV20" s="6"/>
-      <c r="HZZ20" s="6"/>
-      <c r="IAD20" s="6"/>
-      <c r="IAH20" s="6"/>
-      <c r="IAL20" s="6"/>
-      <c r="IAP20" s="6"/>
-      <c r="IAT20" s="6"/>
-      <c r="IAX20" s="6"/>
-      <c r="IBB20" s="6"/>
-      <c r="IBF20" s="6"/>
-      <c r="IBJ20" s="6"/>
-      <c r="IBN20" s="6"/>
-      <c r="IBR20" s="6"/>
-      <c r="IBV20" s="6"/>
-      <c r="IBZ20" s="6"/>
-      <c r="ICD20" s="6"/>
-      <c r="ICH20" s="6"/>
-      <c r="ICL20" s="6"/>
-      <c r="ICP20" s="6"/>
-      <c r="ICT20" s="6"/>
-      <c r="ICX20" s="6"/>
-      <c r="IDB20" s="6"/>
-      <c r="IDF20" s="6"/>
-      <c r="IDJ20" s="6"/>
-      <c r="IDN20" s="6"/>
-      <c r="IDR20" s="6"/>
-      <c r="IDV20" s="6"/>
-      <c r="IDZ20" s="6"/>
-      <c r="IED20" s="6"/>
-      <c r="IEH20" s="6"/>
-      <c r="IEL20" s="6"/>
-      <c r="IEP20" s="6"/>
-      <c r="IET20" s="6"/>
-      <c r="IEX20" s="6"/>
-      <c r="IFB20" s="6"/>
-      <c r="IFF20" s="6"/>
-      <c r="IFJ20" s="6"/>
-      <c r="IFN20" s="6"/>
-      <c r="IFR20" s="6"/>
-      <c r="IFV20" s="6"/>
-      <c r="IFZ20" s="6"/>
-      <c r="IGD20" s="6"/>
-      <c r="IGH20" s="6"/>
-      <c r="IGL20" s="6"/>
-      <c r="IGP20" s="6"/>
-      <c r="IGT20" s="6"/>
-      <c r="IGX20" s="6"/>
-      <c r="IHB20" s="6"/>
-      <c r="IHF20" s="6"/>
-      <c r="IHJ20" s="6"/>
-      <c r="IHN20" s="6"/>
-      <c r="IHR20" s="6"/>
-      <c r="IHV20" s="6"/>
-      <c r="IHZ20" s="6"/>
-      <c r="IID20" s="6"/>
-      <c r="IIH20" s="6"/>
-      <c r="IIL20" s="6"/>
-      <c r="IIP20" s="6"/>
-      <c r="IIT20" s="6"/>
-      <c r="IIX20" s="6"/>
-      <c r="IJB20" s="6"/>
-      <c r="IJF20" s="6"/>
-      <c r="IJJ20" s="6"/>
-      <c r="IJN20" s="6"/>
-      <c r="IJR20" s="6"/>
-      <c r="IJV20" s="6"/>
-      <c r="IJZ20" s="6"/>
-      <c r="IKD20" s="6"/>
-      <c r="IKH20" s="6"/>
-      <c r="IKL20" s="6"/>
-      <c r="IKP20" s="6"/>
-      <c r="IKT20" s="6"/>
-      <c r="IKX20" s="6"/>
-      <c r="ILB20" s="6"/>
-      <c r="ILF20" s="6"/>
-      <c r="ILJ20" s="6"/>
-      <c r="ILN20" s="6"/>
-      <c r="ILR20" s="6"/>
-      <c r="ILV20" s="6"/>
-      <c r="ILZ20" s="6"/>
-      <c r="IMD20" s="6"/>
-      <c r="IMH20" s="6"/>
-      <c r="IML20" s="6"/>
-      <c r="IMP20" s="6"/>
-      <c r="IMT20" s="6"/>
-      <c r="IMX20" s="6"/>
-      <c r="INB20" s="6"/>
-      <c r="INF20" s="6"/>
-      <c r="INJ20" s="6"/>
-      <c r="INN20" s="6"/>
-      <c r="INR20" s="6"/>
-      <c r="INV20" s="6"/>
-      <c r="INZ20" s="6"/>
-      <c r="IOD20" s="6"/>
-      <c r="IOH20" s="6"/>
-      <c r="IOL20" s="6"/>
-      <c r="IOP20" s="6"/>
-      <c r="IOT20" s="6"/>
-      <c r="IOX20" s="6"/>
-      <c r="IPB20" s="6"/>
-      <c r="IPF20" s="6"/>
-      <c r="IPJ20" s="6"/>
-      <c r="IPN20" s="6"/>
-      <c r="IPR20" s="6"/>
-      <c r="IPV20" s="6"/>
-      <c r="IPZ20" s="6"/>
-      <c r="IQD20" s="6"/>
-      <c r="IQH20" s="6"/>
-      <c r="IQL20" s="6"/>
-      <c r="IQP20" s="6"/>
-      <c r="IQT20" s="6"/>
-      <c r="IQX20" s="6"/>
-      <c r="IRB20" s="6"/>
-      <c r="IRF20" s="6"/>
-      <c r="IRJ20" s="6"/>
-      <c r="IRN20" s="6"/>
-      <c r="IRR20" s="6"/>
-      <c r="IRV20" s="6"/>
-      <c r="IRZ20" s="6"/>
-      <c r="ISD20" s="6"/>
-      <c r="ISH20" s="6"/>
-      <c r="ISL20" s="6"/>
-      <c r="ISP20" s="6"/>
-      <c r="IST20" s="6"/>
-      <c r="ISX20" s="6"/>
-      <c r="ITB20" s="6"/>
-      <c r="ITF20" s="6"/>
-      <c r="ITJ20" s="6"/>
-      <c r="ITN20" s="6"/>
-      <c r="ITR20" s="6"/>
-      <c r="ITV20" s="6"/>
-      <c r="ITZ20" s="6"/>
-      <c r="IUD20" s="6"/>
-      <c r="IUH20" s="6"/>
-      <c r="IUL20" s="6"/>
-      <c r="IUP20" s="6"/>
-      <c r="IUT20" s="6"/>
-      <c r="IUX20" s="6"/>
-      <c r="IVB20" s="6"/>
-      <c r="IVF20" s="6"/>
-      <c r="IVJ20" s="6"/>
-      <c r="IVN20" s="6"/>
-      <c r="IVR20" s="6"/>
-      <c r="IVV20" s="6"/>
-      <c r="IVZ20" s="6"/>
-      <c r="IWD20" s="6"/>
-      <c r="IWH20" s="6"/>
-      <c r="IWL20" s="6"/>
-      <c r="IWP20" s="6"/>
-      <c r="IWT20" s="6"/>
-      <c r="IWX20" s="6"/>
-      <c r="IXB20" s="6"/>
-      <c r="IXF20" s="6"/>
-      <c r="IXJ20" s="6"/>
-      <c r="IXN20" s="6"/>
-      <c r="IXR20" s="6"/>
-      <c r="IXV20" s="6"/>
-      <c r="IXZ20" s="6"/>
-      <c r="IYD20" s="6"/>
-      <c r="IYH20" s="6"/>
-      <c r="IYL20" s="6"/>
-      <c r="IYP20" s="6"/>
-      <c r="IYT20" s="6"/>
-      <c r="IYX20" s="6"/>
-      <c r="IZB20" s="6"/>
-      <c r="IZF20" s="6"/>
-      <c r="IZJ20" s="6"/>
-      <c r="IZN20" s="6"/>
-      <c r="IZR20" s="6"/>
-      <c r="IZV20" s="6"/>
-      <c r="IZZ20" s="6"/>
-      <c r="JAD20" s="6"/>
-      <c r="JAH20" s="6"/>
-      <c r="JAL20" s="6"/>
-      <c r="JAP20" s="6"/>
-      <c r="JAT20" s="6"/>
-      <c r="JAX20" s="6"/>
-      <c r="JBB20" s="6"/>
-      <c r="JBF20" s="6"/>
-      <c r="JBJ20" s="6"/>
-      <c r="JBN20" s="6"/>
-      <c r="JBR20" s="6"/>
-      <c r="JBV20" s="6"/>
-      <c r="JBZ20" s="6"/>
-      <c r="JCD20" s="6"/>
-      <c r="JCH20" s="6"/>
-      <c r="JCL20" s="6"/>
-      <c r="JCP20" s="6"/>
-      <c r="JCT20" s="6"/>
-      <c r="JCX20" s="6"/>
-      <c r="JDB20" s="6"/>
-      <c r="JDF20" s="6"/>
-      <c r="JDJ20" s="6"/>
-      <c r="JDN20" s="6"/>
-      <c r="JDR20" s="6"/>
-      <c r="JDV20" s="6"/>
-      <c r="JDZ20" s="6"/>
-      <c r="JED20" s="6"/>
-      <c r="JEH20" s="6"/>
-      <c r="JEL20" s="6"/>
-      <c r="JEP20" s="6"/>
-      <c r="JET20" s="6"/>
-      <c r="JEX20" s="6"/>
-      <c r="JFB20" s="6"/>
-      <c r="JFF20" s="6"/>
-      <c r="JFJ20" s="6"/>
-      <c r="JFN20" s="6"/>
-      <c r="JFR20" s="6"/>
-      <c r="JFV20" s="6"/>
-      <c r="JFZ20" s="6"/>
-      <c r="JGD20" s="6"/>
-      <c r="JGH20" s="6"/>
-      <c r="JGL20" s="6"/>
-      <c r="JGP20" s="6"/>
-      <c r="JGT20" s="6"/>
-      <c r="JGX20" s="6"/>
-      <c r="JHB20" s="6"/>
-      <c r="JHF20" s="6"/>
-      <c r="JHJ20" s="6"/>
-      <c r="JHN20" s="6"/>
-      <c r="JHR20" s="6"/>
-      <c r="JHV20" s="6"/>
-      <c r="JHZ20" s="6"/>
-      <c r="JID20" s="6"/>
-      <c r="JIH20" s="6"/>
-      <c r="JIL20" s="6"/>
-      <c r="JIP20" s="6"/>
-      <c r="JIT20" s="6"/>
-      <c r="JIX20" s="6"/>
-      <c r="JJB20" s="6"/>
-      <c r="JJF20" s="6"/>
-      <c r="JJJ20" s="6"/>
-      <c r="JJN20" s="6"/>
-      <c r="JJR20" s="6"/>
-      <c r="JJV20" s="6"/>
-      <c r="JJZ20" s="6"/>
-      <c r="JKD20" s="6"/>
-      <c r="JKH20" s="6"/>
-      <c r="JKL20" s="6"/>
-      <c r="JKP20" s="6"/>
-      <c r="JKT20" s="6"/>
-      <c r="JKX20" s="6"/>
-      <c r="JLB20" s="6"/>
-      <c r="JLF20" s="6"/>
-      <c r="JLJ20" s="6"/>
-      <c r="JLN20" s="6"/>
-      <c r="JLR20" s="6"/>
-      <c r="JLV20" s="6"/>
-      <c r="JLZ20" s="6"/>
-      <c r="JMD20" s="6"/>
-      <c r="JMH20" s="6"/>
-      <c r="JML20" s="6"/>
-      <c r="JMP20" s="6"/>
-      <c r="JMT20" s="6"/>
-      <c r="JMX20" s="6"/>
-      <c r="JNB20" s="6"/>
-      <c r="JNF20" s="6"/>
-      <c r="JNJ20" s="6"/>
-      <c r="JNN20" s="6"/>
-      <c r="JNR20" s="6"/>
-      <c r="JNV20" s="6"/>
-      <c r="JNZ20" s="6"/>
-      <c r="JOD20" s="6"/>
-      <c r="JOH20" s="6"/>
-      <c r="JOL20" s="6"/>
-      <c r="JOP20" s="6"/>
-      <c r="JOT20" s="6"/>
-      <c r="JOX20" s="6"/>
-      <c r="JPB20" s="6"/>
-      <c r="JPF20" s="6"/>
-      <c r="JPJ20" s="6"/>
-      <c r="JPN20" s="6"/>
-      <c r="JPR20" s="6"/>
-      <c r="JPV20" s="6"/>
-      <c r="JPZ20" s="6"/>
-      <c r="JQD20" s="6"/>
-      <c r="JQH20" s="6"/>
-      <c r="JQL20" s="6"/>
-      <c r="JQP20" s="6"/>
-      <c r="JQT20" s="6"/>
-      <c r="JQX20" s="6"/>
-      <c r="JRB20" s="6"/>
-      <c r="JRF20" s="6"/>
-      <c r="JRJ20" s="6"/>
-      <c r="JRN20" s="6"/>
-      <c r="JRR20" s="6"/>
-      <c r="JRV20" s="6"/>
-      <c r="JRZ20" s="6"/>
-      <c r="JSD20" s="6"/>
-      <c r="JSH20" s="6"/>
-      <c r="JSL20" s="6"/>
-      <c r="JSP20" s="6"/>
-      <c r="JST20" s="6"/>
-      <c r="JSX20" s="6"/>
-      <c r="JTB20" s="6"/>
-      <c r="JTF20" s="6"/>
-      <c r="JTJ20" s="6"/>
-      <c r="JTN20" s="6"/>
-      <c r="JTR20" s="6"/>
-      <c r="JTV20" s="6"/>
-      <c r="JTZ20" s="6"/>
-      <c r="JUD20" s="6"/>
-      <c r="JUH20" s="6"/>
-      <c r="JUL20" s="6"/>
-      <c r="JUP20" s="6"/>
-      <c r="JUT20" s="6"/>
-      <c r="JUX20" s="6"/>
-      <c r="JVB20" s="6"/>
-      <c r="JVF20" s="6"/>
-      <c r="JVJ20" s="6"/>
-      <c r="JVN20" s="6"/>
-      <c r="JVR20" s="6"/>
-      <c r="JVV20" s="6"/>
-      <c r="JVZ20" s="6"/>
-      <c r="JWD20" s="6"/>
-      <c r="JWH20" s="6"/>
-      <c r="JWL20" s="6"/>
-      <c r="JWP20" s="6"/>
-      <c r="JWT20" s="6"/>
-      <c r="JWX20" s="6"/>
-      <c r="JXB20" s="6"/>
-      <c r="JXF20" s="6"/>
-      <c r="JXJ20" s="6"/>
-      <c r="JXN20" s="6"/>
-      <c r="JXR20" s="6"/>
-      <c r="JXV20" s="6"/>
-      <c r="JXZ20" s="6"/>
-      <c r="JYD20" s="6"/>
-      <c r="JYH20" s="6"/>
-      <c r="JYL20" s="6"/>
-      <c r="JYP20" s="6"/>
-      <c r="JYT20" s="6"/>
-      <c r="JYX20" s="6"/>
-      <c r="JZB20" s="6"/>
-      <c r="JZF20" s="6"/>
-      <c r="JZJ20" s="6"/>
-      <c r="JZN20" s="6"/>
-      <c r="JZR20" s="6"/>
-      <c r="JZV20" s="6"/>
-      <c r="JZZ20" s="6"/>
-      <c r="KAD20" s="6"/>
-      <c r="KAH20" s="6"/>
-      <c r="KAL20" s="6"/>
-      <c r="KAP20" s="6"/>
-      <c r="KAT20" s="6"/>
-      <c r="KAX20" s="6"/>
-      <c r="KBB20" s="6"/>
-      <c r="KBF20" s="6"/>
-      <c r="KBJ20" s="6"/>
-      <c r="KBN20" s="6"/>
-      <c r="KBR20" s="6"/>
-      <c r="KBV20" s="6"/>
-      <c r="KBZ20" s="6"/>
-      <c r="KCD20" s="6"/>
-      <c r="KCH20" s="6"/>
-      <c r="KCL20" s="6"/>
-      <c r="KCP20" s="6"/>
-      <c r="KCT20" s="6"/>
-      <c r="KCX20" s="6"/>
-      <c r="KDB20" s="6"/>
-      <c r="KDF20" s="6"/>
-      <c r="KDJ20" s="6"/>
-      <c r="KDN20" s="6"/>
-      <c r="KDR20" s="6"/>
-      <c r="KDV20" s="6"/>
-      <c r="KDZ20" s="6"/>
-      <c r="KED20" s="6"/>
-      <c r="KEH20" s="6"/>
-      <c r="KEL20" s="6"/>
-      <c r="KEP20" s="6"/>
-      <c r="KET20" s="6"/>
-      <c r="KEX20" s="6"/>
-      <c r="KFB20" s="6"/>
-      <c r="KFF20" s="6"/>
-      <c r="KFJ20" s="6"/>
-      <c r="KFN20" s="6"/>
-      <c r="KFR20" s="6"/>
-      <c r="KFV20" s="6"/>
-      <c r="KFZ20" s="6"/>
-      <c r="KGD20" s="6"/>
-      <c r="KGH20" s="6"/>
-      <c r="KGL20" s="6"/>
-      <c r="KGP20" s="6"/>
-      <c r="KGT20" s="6"/>
-      <c r="KGX20" s="6"/>
-      <c r="KHB20" s="6"/>
-      <c r="KHF20" s="6"/>
-      <c r="KHJ20" s="6"/>
-      <c r="KHN20" s="6"/>
-      <c r="KHR20" s="6"/>
-      <c r="KHV20" s="6"/>
-      <c r="KHZ20" s="6"/>
-      <c r="KID20" s="6"/>
-      <c r="KIH20" s="6"/>
-      <c r="KIL20" s="6"/>
-      <c r="KIP20" s="6"/>
-      <c r="KIT20" s="6"/>
-      <c r="KIX20" s="6"/>
-      <c r="KJB20" s="6"/>
-      <c r="KJF20" s="6"/>
-      <c r="KJJ20" s="6"/>
-      <c r="KJN20" s="6"/>
-      <c r="KJR20" s="6"/>
-      <c r="KJV20" s="6"/>
-      <c r="KJZ20" s="6"/>
-      <c r="KKD20" s="6"/>
-      <c r="KKH20" s="6"/>
-      <c r="KKL20" s="6"/>
-      <c r="KKP20" s="6"/>
-      <c r="KKT20" s="6"/>
-      <c r="KKX20" s="6"/>
-      <c r="KLB20" s="6"/>
-      <c r="KLF20" s="6"/>
-      <c r="KLJ20" s="6"/>
-      <c r="KLN20" s="6"/>
-      <c r="KLR20" s="6"/>
-      <c r="KLV20" s="6"/>
-      <c r="KLZ20" s="6"/>
-      <c r="KMD20" s="6"/>
-      <c r="KMH20" s="6"/>
-      <c r="KML20" s="6"/>
-      <c r="KMP20" s="6"/>
-      <c r="KMT20" s="6"/>
-      <c r="KMX20" s="6"/>
-      <c r="KNB20" s="6"/>
-      <c r="KNF20" s="6"/>
-      <c r="KNJ20" s="6"/>
-      <c r="KNN20" s="6"/>
-      <c r="KNR20" s="6"/>
-      <c r="KNV20" s="6"/>
-      <c r="KNZ20" s="6"/>
-      <c r="KOD20" s="6"/>
-      <c r="KOH20" s="6"/>
-      <c r="KOL20" s="6"/>
-      <c r="KOP20" s="6"/>
-      <c r="KOT20" s="6"/>
-      <c r="KOX20" s="6"/>
-      <c r="KPB20" s="6"/>
-      <c r="KPF20" s="6"/>
-      <c r="KPJ20" s="6"/>
-      <c r="KPN20" s="6"/>
-      <c r="KPR20" s="6"/>
-      <c r="KPV20" s="6"/>
-      <c r="KPZ20" s="6"/>
-      <c r="KQD20" s="6"/>
-      <c r="KQH20" s="6"/>
-      <c r="KQL20" s="6"/>
-      <c r="KQP20" s="6"/>
-      <c r="KQT20" s="6"/>
-      <c r="KQX20" s="6"/>
-      <c r="KRB20" s="6"/>
-      <c r="KRF20" s="6"/>
-      <c r="KRJ20" s="6"/>
-      <c r="KRN20" s="6"/>
-      <c r="KRR20" s="6"/>
-      <c r="KRV20" s="6"/>
-      <c r="KRZ20" s="6"/>
-      <c r="KSD20" s="6"/>
-      <c r="KSH20" s="6"/>
-      <c r="KSL20" s="6"/>
-      <c r="KSP20" s="6"/>
-      <c r="KST20" s="6"/>
-      <c r="KSX20" s="6"/>
-      <c r="KTB20" s="6"/>
-      <c r="KTF20" s="6"/>
-      <c r="KTJ20" s="6"/>
-      <c r="KTN20" s="6"/>
-      <c r="KTR20" s="6"/>
-      <c r="KTV20" s="6"/>
-      <c r="KTZ20" s="6"/>
-      <c r="KUD20" s="6"/>
-      <c r="KUH20" s="6"/>
-      <c r="KUL20" s="6"/>
-      <c r="KUP20" s="6"/>
-      <c r="KUT20" s="6"/>
-      <c r="KUX20" s="6"/>
-      <c r="KVB20" s="6"/>
-      <c r="KVF20" s="6"/>
-      <c r="KVJ20" s="6"/>
-      <c r="KVN20" s="6"/>
-      <c r="KVR20" s="6"/>
-      <c r="KVV20" s="6"/>
-      <c r="KVZ20" s="6"/>
-      <c r="KWD20" s="6"/>
-      <c r="KWH20" s="6"/>
-      <c r="KWL20" s="6"/>
-      <c r="KWP20" s="6"/>
-      <c r="KWT20" s="6"/>
-      <c r="KWX20" s="6"/>
-      <c r="KXB20" s="6"/>
-      <c r="KXF20" s="6"/>
-      <c r="KXJ20" s="6"/>
-      <c r="KXN20" s="6"/>
-      <c r="KXR20" s="6"/>
-      <c r="KXV20" s="6"/>
-      <c r="KXZ20" s="6"/>
-      <c r="KYD20" s="6"/>
-      <c r="KYH20" s="6"/>
-      <c r="KYL20" s="6"/>
-      <c r="KYP20" s="6"/>
-      <c r="KYT20" s="6"/>
-      <c r="KYX20" s="6"/>
-      <c r="KZB20" s="6"/>
-      <c r="KZF20" s="6"/>
-      <c r="KZJ20" s="6"/>
-      <c r="KZN20" s="6"/>
-      <c r="KZR20" s="6"/>
-      <c r="KZV20" s="6"/>
-      <c r="KZZ20" s="6"/>
-      <c r="LAD20" s="6"/>
-      <c r="LAH20" s="6"/>
-      <c r="LAL20" s="6"/>
-      <c r="LAP20" s="6"/>
-      <c r="LAT20" s="6"/>
-      <c r="LAX20" s="6"/>
-      <c r="LBB20" s="6"/>
-      <c r="LBF20" s="6"/>
-      <c r="LBJ20" s="6"/>
-      <c r="LBN20" s="6"/>
-      <c r="LBR20" s="6"/>
-      <c r="LBV20" s="6"/>
-      <c r="LBZ20" s="6"/>
-      <c r="LCD20" s="6"/>
-      <c r="LCH20" s="6"/>
-      <c r="LCL20" s="6"/>
-      <c r="LCP20" s="6"/>
-      <c r="LCT20" s="6"/>
-      <c r="LCX20" s="6"/>
-      <c r="LDB20" s="6"/>
-      <c r="LDF20" s="6"/>
-      <c r="LDJ20" s="6"/>
-      <c r="LDN20" s="6"/>
-      <c r="LDR20" s="6"/>
-      <c r="LDV20" s="6"/>
-      <c r="LDZ20" s="6"/>
-      <c r="LED20" s="6"/>
-      <c r="LEH20" s="6"/>
-      <c r="LEL20" s="6"/>
-      <c r="LEP20" s="6"/>
-      <c r="LET20" s="6"/>
-      <c r="LEX20" s="6"/>
-      <c r="LFB20" s="6"/>
-      <c r="LFF20" s="6"/>
-      <c r="LFJ20" s="6"/>
-      <c r="LFN20" s="6"/>
-      <c r="LFR20" s="6"/>
-      <c r="LFV20" s="6"/>
-      <c r="LFZ20" s="6"/>
-      <c r="LGD20" s="6"/>
-      <c r="LGH20" s="6"/>
-      <c r="LGL20" s="6"/>
-      <c r="LGP20" s="6"/>
-      <c r="LGT20" s="6"/>
-      <c r="LGX20" s="6"/>
-      <c r="LHB20" s="6"/>
-      <c r="LHF20" s="6"/>
-      <c r="LHJ20" s="6"/>
-      <c r="LHN20" s="6"/>
-      <c r="LHR20" s="6"/>
-      <c r="LHV20" s="6"/>
-      <c r="LHZ20" s="6"/>
-      <c r="LID20" s="6"/>
-      <c r="LIH20" s="6"/>
-      <c r="LIL20" s="6"/>
-      <c r="LIP20" s="6"/>
-      <c r="LIT20" s="6"/>
-      <c r="LIX20" s="6"/>
-      <c r="LJB20" s="6"/>
-      <c r="LJF20" s="6"/>
-      <c r="LJJ20" s="6"/>
-      <c r="LJN20" s="6"/>
-      <c r="LJR20" s="6"/>
-      <c r="LJV20" s="6"/>
-      <c r="LJZ20" s="6"/>
-      <c r="LKD20" s="6"/>
-      <c r="LKH20" s="6"/>
-      <c r="LKL20" s="6"/>
-      <c r="LKP20" s="6"/>
-      <c r="LKT20" s="6"/>
-      <c r="LKX20" s="6"/>
-      <c r="LLB20" s="6"/>
-      <c r="LLF20" s="6"/>
-      <c r="LLJ20" s="6"/>
-      <c r="LLN20" s="6"/>
-      <c r="LLR20" s="6"/>
-      <c r="LLV20" s="6"/>
-      <c r="LLZ20" s="6"/>
-      <c r="LMD20" s="6"/>
-      <c r="LMH20" s="6"/>
-      <c r="LML20" s="6"/>
-      <c r="LMP20" s="6"/>
-      <c r="LMT20" s="6"/>
-      <c r="LMX20" s="6"/>
-      <c r="LNB20" s="6"/>
-      <c r="LNF20" s="6"/>
-      <c r="LNJ20" s="6"/>
-      <c r="LNN20" s="6"/>
-      <c r="LNR20" s="6"/>
-      <c r="LNV20" s="6"/>
-      <c r="LNZ20" s="6"/>
-      <c r="LOD20" s="6"/>
-      <c r="LOH20" s="6"/>
-      <c r="LOL20" s="6"/>
-      <c r="LOP20" s="6"/>
-      <c r="LOT20" s="6"/>
-      <c r="LOX20" s="6"/>
-      <c r="LPB20" s="6"/>
-      <c r="LPF20" s="6"/>
-      <c r="LPJ20" s="6"/>
-      <c r="LPN20" s="6"/>
-      <c r="LPR20" s="6"/>
-      <c r="LPV20" s="6"/>
-      <c r="LPZ20" s="6"/>
-      <c r="LQD20" s="6"/>
-      <c r="LQH20" s="6"/>
-      <c r="LQL20" s="6"/>
-      <c r="LQP20" s="6"/>
-      <c r="LQT20" s="6"/>
-      <c r="LQX20" s="6"/>
-      <c r="LRB20" s="6"/>
-      <c r="LRF20" s="6"/>
-      <c r="LRJ20" s="6"/>
-      <c r="LRN20" s="6"/>
-      <c r="LRR20" s="6"/>
-      <c r="LRV20" s="6"/>
-      <c r="LRZ20" s="6"/>
-      <c r="LSD20" s="6"/>
-      <c r="LSH20" s="6"/>
-      <c r="LSL20" s="6"/>
-      <c r="LSP20" s="6"/>
-      <c r="LST20" s="6"/>
-      <c r="LSX20" s="6"/>
-      <c r="LTB20" s="6"/>
-      <c r="LTF20" s="6"/>
-      <c r="LTJ20" s="6"/>
-      <c r="LTN20" s="6"/>
-      <c r="LTR20" s="6"/>
-      <c r="LTV20" s="6"/>
-      <c r="LTZ20" s="6"/>
-      <c r="LUD20" s="6"/>
-      <c r="LUH20" s="6"/>
-      <c r="LUL20" s="6"/>
-      <c r="LUP20" s="6"/>
-      <c r="LUT20" s="6"/>
-      <c r="LUX20" s="6"/>
-      <c r="LVB20" s="6"/>
-      <c r="LVF20" s="6"/>
-      <c r="LVJ20" s="6"/>
-      <c r="LVN20" s="6"/>
-      <c r="LVR20" s="6"/>
-      <c r="LVV20" s="6"/>
-      <c r="LVZ20" s="6"/>
-      <c r="LWD20" s="6"/>
-      <c r="LWH20" s="6"/>
-      <c r="LWL20" s="6"/>
-      <c r="LWP20" s="6"/>
-      <c r="LWT20" s="6"/>
-      <c r="LWX20" s="6"/>
-      <c r="LXB20" s="6"/>
-      <c r="LXF20" s="6"/>
-      <c r="LXJ20" s="6"/>
-      <c r="LXN20" s="6"/>
-      <c r="LXR20" s="6"/>
-      <c r="LXV20" s="6"/>
-      <c r="LXZ20" s="6"/>
-      <c r="LYD20" s="6"/>
-      <c r="LYH20" s="6"/>
-      <c r="LYL20" s="6"/>
-      <c r="LYP20" s="6"/>
-      <c r="LYT20" s="6"/>
-      <c r="LYX20" s="6"/>
-      <c r="LZB20" s="6"/>
-      <c r="LZF20" s="6"/>
-      <c r="LZJ20" s="6"/>
-      <c r="LZN20" s="6"/>
-      <c r="LZR20" s="6"/>
-      <c r="LZV20" s="6"/>
-      <c r="LZZ20" s="6"/>
-      <c r="MAD20" s="6"/>
-      <c r="MAH20" s="6"/>
-      <c r="MAL20" s="6"/>
-      <c r="MAP20" s="6"/>
-      <c r="MAT20" s="6"/>
-      <c r="MAX20" s="6"/>
-      <c r="MBB20" s="6"/>
-      <c r="MBF20" s="6"/>
-      <c r="MBJ20" s="6"/>
-      <c r="MBN20" s="6"/>
-      <c r="MBR20" s="6"/>
-      <c r="MBV20" s="6"/>
-      <c r="MBZ20" s="6"/>
-      <c r="MCD20" s="6"/>
-      <c r="MCH20" s="6"/>
-      <c r="MCL20" s="6"/>
-      <c r="MCP20" s="6"/>
-      <c r="MCT20" s="6"/>
-      <c r="MCX20" s="6"/>
-      <c r="MDB20" s="6"/>
-      <c r="MDF20" s="6"/>
-      <c r="MDJ20" s="6"/>
-      <c r="MDN20" s="6"/>
-      <c r="MDR20" s="6"/>
-      <c r="MDV20" s="6"/>
-      <c r="MDZ20" s="6"/>
-      <c r="MED20" s="6"/>
-      <c r="MEH20" s="6"/>
-      <c r="MEL20" s="6"/>
-      <c r="MEP20" s="6"/>
-      <c r="MET20" s="6"/>
-      <c r="MEX20" s="6"/>
-      <c r="MFB20" s="6"/>
-      <c r="MFF20" s="6"/>
-      <c r="MFJ20" s="6"/>
-      <c r="MFN20" s="6"/>
-      <c r="MFR20" s="6"/>
-      <c r="MFV20" s="6"/>
-      <c r="MFZ20" s="6"/>
-      <c r="MGD20" s="6"/>
-      <c r="MGH20" s="6"/>
-      <c r="MGL20" s="6"/>
-      <c r="MGP20" s="6"/>
-      <c r="MGT20" s="6"/>
-      <c r="MGX20" s="6"/>
-      <c r="MHB20" s="6"/>
-      <c r="MHF20" s="6"/>
-      <c r="MHJ20" s="6"/>
-      <c r="MHN20" s="6"/>
-      <c r="MHR20" s="6"/>
-      <c r="MHV20" s="6"/>
-      <c r="MHZ20" s="6"/>
-      <c r="MID20" s="6"/>
-      <c r="MIH20" s="6"/>
-      <c r="MIL20" s="6"/>
-      <c r="MIP20" s="6"/>
-      <c r="MIT20" s="6"/>
-      <c r="MIX20" s="6"/>
-      <c r="MJB20" s="6"/>
-      <c r="MJF20" s="6"/>
-      <c r="MJJ20" s="6"/>
-      <c r="MJN20" s="6"/>
-      <c r="MJR20" s="6"/>
-      <c r="MJV20" s="6"/>
-      <c r="MJZ20" s="6"/>
-      <c r="MKD20" s="6"/>
-      <c r="MKH20" s="6"/>
-      <c r="MKL20" s="6"/>
-      <c r="MKP20" s="6"/>
-      <c r="MKT20" s="6"/>
-      <c r="MKX20" s="6"/>
-      <c r="MLB20" s="6"/>
-      <c r="MLF20" s="6"/>
-      <c r="MLJ20" s="6"/>
-      <c r="MLN20" s="6"/>
-      <c r="MLR20" s="6"/>
-      <c r="MLV20" s="6"/>
-      <c r="MLZ20" s="6"/>
-      <c r="MMD20" s="6"/>
-      <c r="MMH20" s="6"/>
-      <c r="MML20" s="6"/>
-      <c r="MMP20" s="6"/>
-      <c r="MMT20" s="6"/>
-      <c r="MMX20" s="6"/>
-      <c r="MNB20" s="6"/>
-      <c r="MNF20" s="6"/>
-      <c r="MNJ20" s="6"/>
-      <c r="MNN20" s="6"/>
-      <c r="MNR20" s="6"/>
-      <c r="MNV20" s="6"/>
-      <c r="MNZ20" s="6"/>
-      <c r="MOD20" s="6"/>
-      <c r="MOH20" s="6"/>
-      <c r="MOL20" s="6"/>
-      <c r="MOP20" s="6"/>
-      <c r="MOT20" s="6"/>
-      <c r="MOX20" s="6"/>
-      <c r="MPB20" s="6"/>
-      <c r="MPF20" s="6"/>
-      <c r="MPJ20" s="6"/>
-      <c r="MPN20" s="6"/>
-      <c r="MPR20" s="6"/>
-      <c r="MPV20" s="6"/>
-      <c r="MPZ20" s="6"/>
-      <c r="MQD20" s="6"/>
-      <c r="MQH20" s="6"/>
-      <c r="MQL20" s="6"/>
-      <c r="MQP20" s="6"/>
-      <c r="MQT20" s="6"/>
-      <c r="MQX20" s="6"/>
-      <c r="MRB20" s="6"/>
-      <c r="MRF20" s="6"/>
-      <c r="MRJ20" s="6"/>
-      <c r="MRN20" s="6"/>
-      <c r="MRR20" s="6"/>
-      <c r="MRV20" s="6"/>
-      <c r="MRZ20" s="6"/>
-      <c r="MSD20" s="6"/>
-      <c r="MSH20" s="6"/>
-      <c r="MSL20" s="6"/>
-      <c r="MSP20" s="6"/>
-      <c r="MST20" s="6"/>
-      <c r="MSX20" s="6"/>
-      <c r="MTB20" s="6"/>
-      <c r="MTF20" s="6"/>
-      <c r="MTJ20" s="6"/>
-      <c r="MTN20" s="6"/>
-      <c r="MTR20" s="6"/>
-      <c r="MTV20" s="6"/>
-      <c r="MTZ20" s="6"/>
-      <c r="MUD20" s="6"/>
-      <c r="MUH20" s="6"/>
-      <c r="MUL20" s="6"/>
-      <c r="MUP20" s="6"/>
-      <c r="MUT20" s="6"/>
-      <c r="MUX20" s="6"/>
-      <c r="MVB20" s="6"/>
-      <c r="MVF20" s="6"/>
-      <c r="MVJ20" s="6"/>
-      <c r="MVN20" s="6"/>
-      <c r="MVR20" s="6"/>
-      <c r="MVV20" s="6"/>
-      <c r="MVZ20" s="6"/>
-      <c r="MWD20" s="6"/>
-      <c r="MWH20" s="6"/>
-      <c r="MWL20" s="6"/>
-      <c r="MWP20" s="6"/>
-      <c r="MWT20" s="6"/>
-      <c r="MWX20" s="6"/>
-      <c r="MXB20" s="6"/>
-      <c r="MXF20" s="6"/>
-      <c r="MXJ20" s="6"/>
-      <c r="MXN20" s="6"/>
-      <c r="MXR20" s="6"/>
-      <c r="MXV20" s="6"/>
-      <c r="MXZ20" s="6"/>
-      <c r="MYD20" s="6"/>
-      <c r="MYH20" s="6"/>
-      <c r="MYL20" s="6"/>
-      <c r="MYP20" s="6"/>
-      <c r="MYT20" s="6"/>
-      <c r="MYX20" s="6"/>
-      <c r="MZB20" s="6"/>
-      <c r="MZF20" s="6"/>
-      <c r="MZJ20" s="6"/>
-      <c r="MZN20" s="6"/>
-      <c r="MZR20" s="6"/>
-      <c r="MZV20" s="6"/>
-      <c r="MZZ20" s="6"/>
-      <c r="NAD20" s="6"/>
-      <c r="NAH20" s="6"/>
-      <c r="NAL20" s="6"/>
-      <c r="NAP20" s="6"/>
-      <c r="NAT20" s="6"/>
-      <c r="NAX20" s="6"/>
-      <c r="NBB20" s="6"/>
-      <c r="NBF20" s="6"/>
-      <c r="NBJ20" s="6"/>
-      <c r="NBN20" s="6"/>
-      <c r="NBR20" s="6"/>
-      <c r="NBV20" s="6"/>
-      <c r="NBZ20" s="6"/>
-      <c r="NCD20" s="6"/>
-      <c r="NCH20" s="6"/>
-      <c r="NCL20" s="6"/>
-      <c r="NCP20" s="6"/>
-      <c r="NCT20" s="6"/>
-      <c r="NCX20" s="6"/>
-      <c r="NDB20" s="6"/>
-      <c r="NDF20" s="6"/>
-      <c r="NDJ20" s="6"/>
-      <c r="NDN20" s="6"/>
-      <c r="NDR20" s="6"/>
-      <c r="NDV20" s="6"/>
-      <c r="NDZ20" s="6"/>
-      <c r="NED20" s="6"/>
-      <c r="NEH20" s="6"/>
-      <c r="NEL20" s="6"/>
-      <c r="NEP20" s="6"/>
-      <c r="NET20" s="6"/>
-      <c r="NEX20" s="6"/>
-      <c r="NFB20" s="6"/>
-      <c r="NFF20" s="6"/>
-      <c r="NFJ20" s="6"/>
-      <c r="NFN20" s="6"/>
-      <c r="NFR20" s="6"/>
-      <c r="NFV20" s="6"/>
-      <c r="NFZ20" s="6"/>
-      <c r="NGD20" s="6"/>
-      <c r="NGH20" s="6"/>
-      <c r="NGL20" s="6"/>
-      <c r="NGP20" s="6"/>
-      <c r="NGT20" s="6"/>
-      <c r="NGX20" s="6"/>
-      <c r="NHB20" s="6"/>
-      <c r="NHF20" s="6"/>
-      <c r="NHJ20" s="6"/>
-      <c r="NHN20" s="6"/>
-      <c r="NHR20" s="6"/>
-      <c r="NHV20" s="6"/>
-      <c r="NHZ20" s="6"/>
-      <c r="NID20" s="6"/>
-      <c r="NIH20" s="6"/>
-      <c r="NIL20" s="6"/>
-      <c r="NIP20" s="6"/>
-      <c r="NIT20" s="6"/>
-      <c r="NIX20" s="6"/>
-      <c r="NJB20" s="6"/>
-      <c r="NJF20" s="6"/>
-      <c r="NJJ20" s="6"/>
-      <c r="NJN20" s="6"/>
-      <c r="NJR20" s="6"/>
-      <c r="NJV20" s="6"/>
-      <c r="NJZ20" s="6"/>
-      <c r="NKD20" s="6"/>
-      <c r="NKH20" s="6"/>
-      <c r="NKL20" s="6"/>
-      <c r="NKP20" s="6"/>
-      <c r="NKT20" s="6"/>
-      <c r="NKX20" s="6"/>
-      <c r="NLB20" s="6"/>
-      <c r="NLF20" s="6"/>
-      <c r="NLJ20" s="6"/>
-      <c r="NLN20" s="6"/>
-      <c r="NLR20" s="6"/>
-      <c r="NLV20" s="6"/>
-      <c r="NLZ20" s="6"/>
-      <c r="NMD20" s="6"/>
-      <c r="NMH20" s="6"/>
-      <c r="NML20" s="6"/>
-      <c r="NMP20" s="6"/>
-      <c r="NMT20" s="6"/>
-      <c r="NMX20" s="6"/>
-      <c r="NNB20" s="6"/>
-      <c r="NNF20" s="6"/>
-      <c r="NNJ20" s="6"/>
-      <c r="NNN20" s="6"/>
-      <c r="NNR20" s="6"/>
-      <c r="NNV20" s="6"/>
-      <c r="NNZ20" s="6"/>
-      <c r="NOD20" s="6"/>
-      <c r="NOH20" s="6"/>
-      <c r="NOL20" s="6"/>
-      <c r="NOP20" s="6"/>
-      <c r="NOT20" s="6"/>
-      <c r="NOX20" s="6"/>
-      <c r="NPB20" s="6"/>
-      <c r="NPF20" s="6"/>
-      <c r="NPJ20" s="6"/>
-      <c r="NPN20" s="6"/>
-      <c r="NPR20" s="6"/>
-      <c r="NPV20" s="6"/>
-      <c r="NPZ20" s="6"/>
-      <c r="NQD20" s="6"/>
-      <c r="NQH20" s="6"/>
-      <c r="NQL20" s="6"/>
-      <c r="NQP20" s="6"/>
-      <c r="NQT20" s="6"/>
-      <c r="NQX20" s="6"/>
-      <c r="NRB20" s="6"/>
-      <c r="NRF20" s="6"/>
-      <c r="NRJ20" s="6"/>
-      <c r="NRN20" s="6"/>
-      <c r="NRR20" s="6"/>
-      <c r="NRV20" s="6"/>
-      <c r="NRZ20" s="6"/>
-      <c r="NSD20" s="6"/>
-      <c r="NSH20" s="6"/>
-      <c r="NSL20" s="6"/>
-      <c r="NSP20" s="6"/>
-      <c r="NST20" s="6"/>
-      <c r="NSX20" s="6"/>
-      <c r="NTB20" s="6"/>
-      <c r="NTF20" s="6"/>
-      <c r="NTJ20" s="6"/>
-      <c r="NTN20" s="6"/>
-      <c r="NTR20" s="6"/>
-      <c r="NTV20" s="6"/>
-      <c r="NTZ20" s="6"/>
-      <c r="NUD20" s="6"/>
-      <c r="NUH20" s="6"/>
-      <c r="NUL20" s="6"/>
-      <c r="NUP20" s="6"/>
-      <c r="NUT20" s="6"/>
-      <c r="NUX20" s="6"/>
-      <c r="NVB20" s="6"/>
-      <c r="NVF20" s="6"/>
-      <c r="NVJ20" s="6"/>
-      <c r="NVN20" s="6"/>
-      <c r="NVR20" s="6"/>
-      <c r="NVV20" s="6"/>
-      <c r="NVZ20" s="6"/>
-      <c r="NWD20" s="6"/>
-      <c r="NWH20" s="6"/>
-      <c r="NWL20" s="6"/>
-      <c r="NWP20" s="6"/>
-      <c r="NWT20" s="6"/>
-      <c r="NWX20" s="6"/>
-      <c r="NXB20" s="6"/>
-      <c r="NXF20" s="6"/>
-      <c r="NXJ20" s="6"/>
-      <c r="NXN20" s="6"/>
-      <c r="NXR20" s="6"/>
-      <c r="NXV20" s="6"/>
-      <c r="NXZ20" s="6"/>
-      <c r="NYD20" s="6"/>
-      <c r="NYH20" s="6"/>
-      <c r="NYL20" s="6"/>
-      <c r="NYP20" s="6"/>
-      <c r="NYT20" s="6"/>
-      <c r="NYX20" s="6"/>
-      <c r="NZB20" s="6"/>
-      <c r="NZF20" s="6"/>
-      <c r="NZJ20" s="6"/>
-      <c r="NZN20" s="6"/>
-      <c r="NZR20" s="6"/>
-      <c r="NZV20" s="6"/>
-      <c r="NZZ20" s="6"/>
-      <c r="OAD20" s="6"/>
-      <c r="OAH20" s="6"/>
-      <c r="OAL20" s="6"/>
-      <c r="OAP20" s="6"/>
-      <c r="OAT20" s="6"/>
-      <c r="OAX20" s="6"/>
-      <c r="OBB20" s="6"/>
-      <c r="OBF20" s="6"/>
-      <c r="OBJ20" s="6"/>
-      <c r="OBN20" s="6"/>
-      <c r="OBR20" s="6"/>
-      <c r="OBV20" s="6"/>
-      <c r="OBZ20" s="6"/>
-      <c r="OCD20" s="6"/>
-      <c r="OCH20" s="6"/>
-      <c r="OCL20" s="6"/>
-      <c r="OCP20" s="6"/>
-      <c r="OCT20" s="6"/>
-      <c r="OCX20" s="6"/>
-      <c r="ODB20" s="6"/>
-      <c r="ODF20" s="6"/>
-      <c r="ODJ20" s="6"/>
-      <c r="ODN20" s="6"/>
-      <c r="ODR20" s="6"/>
-      <c r="ODV20" s="6"/>
-      <c r="ODZ20" s="6"/>
-      <c r="OED20" s="6"/>
-      <c r="OEH20" s="6"/>
-      <c r="OEL20" s="6"/>
-      <c r="OEP20" s="6"/>
-      <c r="OET20" s="6"/>
-      <c r="OEX20" s="6"/>
-      <c r="OFB20" s="6"/>
-      <c r="OFF20" s="6"/>
-      <c r="OFJ20" s="6"/>
-      <c r="OFN20" s="6"/>
-      <c r="OFR20" s="6"/>
-      <c r="OFV20" s="6"/>
-      <c r="OFZ20" s="6"/>
-      <c r="OGD20" s="6"/>
-      <c r="OGH20" s="6"/>
-      <c r="OGL20" s="6"/>
-      <c r="OGP20" s="6"/>
-      <c r="OGT20" s="6"/>
-      <c r="OGX20" s="6"/>
-      <c r="OHB20" s="6"/>
-      <c r="OHF20" s="6"/>
-      <c r="OHJ20" s="6"/>
-      <c r="OHN20" s="6"/>
-      <c r="OHR20" s="6"/>
-      <c r="OHV20" s="6"/>
-      <c r="OHZ20" s="6"/>
-      <c r="OID20" s="6"/>
-      <c r="OIH20" s="6"/>
-      <c r="OIL20" s="6"/>
-      <c r="OIP20" s="6"/>
-      <c r="OIT20" s="6"/>
-      <c r="OIX20" s="6"/>
-      <c r="OJB20" s="6"/>
-      <c r="OJF20" s="6"/>
-      <c r="OJJ20" s="6"/>
-      <c r="OJN20" s="6"/>
-      <c r="OJR20" s="6"/>
-      <c r="OJV20" s="6"/>
-      <c r="OJZ20" s="6"/>
-      <c r="OKD20" s="6"/>
-      <c r="OKH20" s="6"/>
-      <c r="OKL20" s="6"/>
-      <c r="OKP20" s="6"/>
-      <c r="OKT20" s="6"/>
-      <c r="OKX20" s="6"/>
-      <c r="OLB20" s="6"/>
-      <c r="OLF20" s="6"/>
-      <c r="OLJ20" s="6"/>
-      <c r="OLN20" s="6"/>
-      <c r="OLR20" s="6"/>
-      <c r="OLV20" s="6"/>
-      <c r="OLZ20" s="6"/>
-      <c r="OMD20" s="6"/>
-      <c r="OMH20" s="6"/>
-      <c r="OML20" s="6"/>
-      <c r="OMP20" s="6"/>
-      <c r="OMT20" s="6"/>
-      <c r="OMX20" s="6"/>
-      <c r="ONB20" s="6"/>
-      <c r="ONF20" s="6"/>
-      <c r="ONJ20" s="6"/>
-      <c r="ONN20" s="6"/>
-      <c r="ONR20" s="6"/>
-      <c r="ONV20" s="6"/>
-      <c r="ONZ20" s="6"/>
-      <c r="OOD20" s="6"/>
-      <c r="OOH20" s="6"/>
-      <c r="OOL20" s="6"/>
-      <c r="OOP20" s="6"/>
-      <c r="OOT20" s="6"/>
-      <c r="OOX20" s="6"/>
-      <c r="OPB20" s="6"/>
-      <c r="OPF20" s="6"/>
-      <c r="OPJ20" s="6"/>
-      <c r="OPN20" s="6"/>
-      <c r="OPR20" s="6"/>
-      <c r="OPV20" s="6"/>
-      <c r="OPZ20" s="6"/>
-      <c r="OQD20" s="6"/>
-      <c r="OQH20" s="6"/>
-      <c r="OQL20" s="6"/>
-      <c r="OQP20" s="6"/>
-      <c r="OQT20" s="6"/>
-      <c r="OQX20" s="6"/>
-      <c r="ORB20" s="6"/>
-      <c r="ORF20" s="6"/>
-      <c r="ORJ20" s="6"/>
-      <c r="ORN20" s="6"/>
-      <c r="ORR20" s="6"/>
-      <c r="ORV20" s="6"/>
-      <c r="ORZ20" s="6"/>
-      <c r="OSD20" s="6"/>
-      <c r="OSH20" s="6"/>
-      <c r="OSL20" s="6"/>
-      <c r="OSP20" s="6"/>
-      <c r="OST20" s="6"/>
-      <c r="OSX20" s="6"/>
-      <c r="OTB20" s="6"/>
-      <c r="OTF20" s="6"/>
-      <c r="OTJ20" s="6"/>
-      <c r="OTN20" s="6"/>
-      <c r="OTR20" s="6"/>
-      <c r="OTV20" s="6"/>
-      <c r="OTZ20" s="6"/>
-      <c r="OUD20" s="6"/>
-      <c r="OUH20" s="6"/>
-      <c r="OUL20" s="6"/>
-      <c r="OUP20" s="6"/>
-      <c r="OUT20" s="6"/>
-      <c r="OUX20" s="6"/>
-      <c r="OVB20" s="6"/>
-      <c r="OVF20" s="6"/>
-      <c r="OVJ20" s="6"/>
-      <c r="OVN20" s="6"/>
-      <c r="OVR20" s="6"/>
-      <c r="OVV20" s="6"/>
-      <c r="OVZ20" s="6"/>
-      <c r="OWD20" s="6"/>
-      <c r="OWH20" s="6"/>
-      <c r="OWL20" s="6"/>
-      <c r="OWP20" s="6"/>
-      <c r="OWT20" s="6"/>
-      <c r="OWX20" s="6"/>
-      <c r="OXB20" s="6"/>
-      <c r="OXF20" s="6"/>
-      <c r="OXJ20" s="6"/>
-      <c r="OXN20" s="6"/>
-      <c r="OXR20" s="6"/>
-      <c r="OXV20" s="6"/>
-      <c r="OXZ20" s="6"/>
-      <c r="OYD20" s="6"/>
-      <c r="OYH20" s="6"/>
-      <c r="OYL20" s="6"/>
-      <c r="OYP20" s="6"/>
-      <c r="OYT20" s="6"/>
-      <c r="OYX20" s="6"/>
-      <c r="OZB20" s="6"/>
-      <c r="OZF20" s="6"/>
-      <c r="OZJ20" s="6"/>
-      <c r="OZN20" s="6"/>
-      <c r="OZR20" s="6"/>
-      <c r="OZV20" s="6"/>
-      <c r="OZZ20" s="6"/>
-      <c r="PAD20" s="6"/>
-      <c r="PAH20" s="6"/>
-      <c r="PAL20" s="6"/>
-      <c r="PAP20" s="6"/>
-      <c r="PAT20" s="6"/>
-      <c r="PAX20" s="6"/>
-      <c r="PBB20" s="6"/>
-      <c r="PBF20" s="6"/>
-      <c r="PBJ20" s="6"/>
-      <c r="PBN20" s="6"/>
-      <c r="PBR20" s="6"/>
-      <c r="PBV20" s="6"/>
-      <c r="PBZ20" s="6"/>
-      <c r="PCD20" s="6"/>
-      <c r="PCH20" s="6"/>
-      <c r="PCL20" s="6"/>
-      <c r="PCP20" s="6"/>
-      <c r="PCT20" s="6"/>
-      <c r="PCX20" s="6"/>
-      <c r="PDB20" s="6"/>
-      <c r="PDF20" s="6"/>
-      <c r="PDJ20" s="6"/>
-      <c r="PDN20" s="6"/>
-      <c r="PDR20" s="6"/>
-      <c r="PDV20" s="6"/>
-      <c r="PDZ20" s="6"/>
-      <c r="PED20" s="6"/>
-      <c r="PEH20" s="6"/>
-      <c r="PEL20" s="6"/>
-      <c r="PEP20" s="6"/>
-      <c r="PET20" s="6"/>
-      <c r="PEX20" s="6"/>
-      <c r="PFB20" s="6"/>
-      <c r="PFF20" s="6"/>
-      <c r="PFJ20" s="6"/>
-      <c r="PFN20" s="6"/>
-      <c r="PFR20" s="6"/>
-      <c r="PFV20" s="6"/>
-      <c r="PFZ20" s="6"/>
-      <c r="PGD20" s="6"/>
-      <c r="PGH20" s="6"/>
-      <c r="PGL20" s="6"/>
-      <c r="PGP20" s="6"/>
-      <c r="PGT20" s="6"/>
-      <c r="PGX20" s="6"/>
-      <c r="PHB20" s="6"/>
-      <c r="PHF20" s="6"/>
-      <c r="PHJ20" s="6"/>
-      <c r="PHN20" s="6"/>
-      <c r="PHR20" s="6"/>
-      <c r="PHV20" s="6"/>
-      <c r="PHZ20" s="6"/>
-      <c r="PID20" s="6"/>
-      <c r="PIH20" s="6"/>
-      <c r="PIL20" s="6"/>
-      <c r="PIP20" s="6"/>
-      <c r="PIT20" s="6"/>
-      <c r="PIX20" s="6"/>
-      <c r="PJB20" s="6"/>
-      <c r="PJF20" s="6"/>
-      <c r="PJJ20" s="6"/>
-      <c r="PJN20" s="6"/>
-      <c r="PJR20" s="6"/>
-      <c r="PJV20" s="6"/>
-      <c r="PJZ20" s="6"/>
-      <c r="PKD20" s="6"/>
-      <c r="PKH20" s="6"/>
-      <c r="PKL20" s="6"/>
-      <c r="PKP20" s="6"/>
-      <c r="PKT20" s="6"/>
-      <c r="PKX20" s="6"/>
-      <c r="PLB20" s="6"/>
-      <c r="PLF20" s="6"/>
-      <c r="PLJ20" s="6"/>
-      <c r="PLN20" s="6"/>
-      <c r="PLR20" s="6"/>
-      <c r="PLV20" s="6"/>
-      <c r="PLZ20" s="6"/>
-      <c r="PMD20" s="6"/>
-      <c r="PMH20" s="6"/>
-      <c r="PML20" s="6"/>
-      <c r="PMP20" s="6"/>
-      <c r="PMT20" s="6"/>
-      <c r="PMX20" s="6"/>
-      <c r="PNB20" s="6"/>
-      <c r="PNF20" s="6"/>
-      <c r="PNJ20" s="6"/>
-      <c r="PNN20" s="6"/>
-      <c r="PNR20" s="6"/>
-      <c r="PNV20" s="6"/>
-      <c r="PNZ20" s="6"/>
-      <c r="POD20" s="6"/>
-      <c r="POH20" s="6"/>
-      <c r="POL20" s="6"/>
-      <c r="POP20" s="6"/>
-      <c r="POT20" s="6"/>
-      <c r="POX20" s="6"/>
-      <c r="PPB20" s="6"/>
-      <c r="PPF20" s="6"/>
-      <c r="PPJ20" s="6"/>
-      <c r="PPN20" s="6"/>
-      <c r="PPR20" s="6"/>
-      <c r="PPV20" s="6"/>
-      <c r="PPZ20" s="6"/>
-      <c r="PQD20" s="6"/>
-      <c r="PQH20" s="6"/>
-      <c r="PQL20" s="6"/>
-      <c r="PQP20" s="6"/>
-      <c r="PQT20" s="6"/>
-      <c r="PQX20" s="6"/>
-      <c r="PRB20" s="6"/>
-      <c r="PRF20" s="6"/>
-      <c r="PRJ20" s="6"/>
-      <c r="PRN20" s="6"/>
-      <c r="PRR20" s="6"/>
-      <c r="PRV20" s="6"/>
-      <c r="PRZ20" s="6"/>
-      <c r="PSD20" s="6"/>
-      <c r="PSH20" s="6"/>
-      <c r="PSL20" s="6"/>
-      <c r="PSP20" s="6"/>
-      <c r="PST20" s="6"/>
-      <c r="PSX20" s="6"/>
-      <c r="PTB20" s="6"/>
-      <c r="PTF20" s="6"/>
-      <c r="PTJ20" s="6"/>
-      <c r="PTN20" s="6"/>
-      <c r="PTR20" s="6"/>
-      <c r="PTV20" s="6"/>
-      <c r="PTZ20" s="6"/>
-      <c r="PUD20" s="6"/>
-      <c r="PUH20" s="6"/>
-      <c r="PUL20" s="6"/>
-      <c r="PUP20" s="6"/>
-      <c r="PUT20" s="6"/>
-      <c r="PUX20" s="6"/>
-      <c r="PVB20" s="6"/>
-      <c r="PVF20" s="6"/>
-      <c r="PVJ20" s="6"/>
-      <c r="PVN20" s="6"/>
-      <c r="PVR20" s="6"/>
-      <c r="PVV20" s="6"/>
-      <c r="PVZ20" s="6"/>
-      <c r="PWD20" s="6"/>
-      <c r="PWH20" s="6"/>
-      <c r="PWL20" s="6"/>
-      <c r="PWP20" s="6"/>
-      <c r="PWT20" s="6"/>
-      <c r="PWX20" s="6"/>
-      <c r="PXB20" s="6"/>
-      <c r="PXF20" s="6"/>
-      <c r="PXJ20" s="6"/>
-      <c r="PXN20" s="6"/>
-      <c r="PXR20" s="6"/>
-      <c r="PXV20" s="6"/>
-      <c r="PXZ20" s="6"/>
-      <c r="PYD20" s="6"/>
-      <c r="PYH20" s="6"/>
-      <c r="PYL20" s="6"/>
-      <c r="PYP20" s="6"/>
-      <c r="PYT20" s="6"/>
-      <c r="PYX20" s="6"/>
-      <c r="PZB20" s="6"/>
-      <c r="PZF20" s="6"/>
-      <c r="PZJ20" s="6"/>
-      <c r="PZN20" s="6"/>
-      <c r="PZR20" s="6"/>
-      <c r="PZV20" s="6"/>
-      <c r="PZZ20" s="6"/>
-      <c r="QAD20" s="6"/>
-      <c r="QAH20" s="6"/>
-      <c r="QAL20" s="6"/>
-      <c r="QAP20" s="6"/>
-      <c r="QAT20" s="6"/>
-      <c r="QAX20" s="6"/>
-      <c r="QBB20" s="6"/>
-      <c r="QBF20" s="6"/>
-      <c r="QBJ20" s="6"/>
-      <c r="QBN20" s="6"/>
-      <c r="QBR20" s="6"/>
-      <c r="QBV20" s="6"/>
-      <c r="QBZ20" s="6"/>
-      <c r="QCD20" s="6"/>
-      <c r="QCH20" s="6"/>
-      <c r="QCL20" s="6"/>
-      <c r="QCP20" s="6"/>
-      <c r="QCT20" s="6"/>
-      <c r="QCX20" s="6"/>
-      <c r="QDB20" s="6"/>
-      <c r="QDF20" s="6"/>
-      <c r="QDJ20" s="6"/>
-      <c r="QDN20" s="6"/>
-      <c r="QDR20" s="6"/>
-      <c r="QDV20" s="6"/>
-      <c r="QDZ20" s="6"/>
-      <c r="QED20" s="6"/>
-      <c r="QEH20" s="6"/>
-      <c r="QEL20" s="6"/>
-      <c r="QEP20" s="6"/>
-      <c r="QET20" s="6"/>
-      <c r="QEX20" s="6"/>
-      <c r="QFB20" s="6"/>
-      <c r="QFF20" s="6"/>
-      <c r="QFJ20" s="6"/>
-      <c r="QFN20" s="6"/>
-      <c r="QFR20" s="6"/>
-      <c r="QFV20" s="6"/>
-      <c r="QFZ20" s="6"/>
-      <c r="QGD20" s="6"/>
-      <c r="QGH20" s="6"/>
-      <c r="QGL20" s="6"/>
-      <c r="QGP20" s="6"/>
-      <c r="QGT20" s="6"/>
-      <c r="QGX20" s="6"/>
-      <c r="QHB20" s="6"/>
-      <c r="QHF20" s="6"/>
-      <c r="QHJ20" s="6"/>
-      <c r="QHN20" s="6"/>
-      <c r="QHR20" s="6"/>
-      <c r="QHV20" s="6"/>
-      <c r="QHZ20" s="6"/>
-      <c r="QID20" s="6"/>
-      <c r="QIH20" s="6"/>
-      <c r="QIL20" s="6"/>
-      <c r="QIP20" s="6"/>
-      <c r="QIT20" s="6"/>
-      <c r="QIX20" s="6"/>
-      <c r="QJB20" s="6"/>
-      <c r="QJF20" s="6"/>
-      <c r="QJJ20" s="6"/>
-      <c r="QJN20" s="6"/>
-      <c r="QJR20" s="6"/>
-      <c r="QJV20" s="6"/>
-      <c r="QJZ20" s="6"/>
-      <c r="QKD20" s="6"/>
-      <c r="QKH20" s="6"/>
-      <c r="QKL20" s="6"/>
-      <c r="QKP20" s="6"/>
-      <c r="QKT20" s="6"/>
-      <c r="QKX20" s="6"/>
-      <c r="QLB20" s="6"/>
-      <c r="QLF20" s="6"/>
-      <c r="QLJ20" s="6"/>
-      <c r="QLN20" s="6"/>
-      <c r="QLR20" s="6"/>
-      <c r="QLV20" s="6"/>
-      <c r="QLZ20" s="6"/>
-      <c r="QMD20" s="6"/>
-      <c r="QMH20" s="6"/>
-      <c r="QML20" s="6"/>
-      <c r="QMP20" s="6"/>
-      <c r="QMT20" s="6"/>
-      <c r="QMX20" s="6"/>
-      <c r="QNB20" s="6"/>
-      <c r="QNF20" s="6"/>
-      <c r="QNJ20" s="6"/>
-      <c r="QNN20" s="6"/>
-      <c r="QNR20" s="6"/>
-      <c r="QNV20" s="6"/>
-      <c r="QNZ20" s="6"/>
-      <c r="QOD20" s="6"/>
-      <c r="QOH20" s="6"/>
-      <c r="QOL20" s="6"/>
-      <c r="QOP20" s="6"/>
-      <c r="QOT20" s="6"/>
-      <c r="QOX20" s="6"/>
-      <c r="QPB20" s="6"/>
-      <c r="QPF20" s="6"/>
-      <c r="QPJ20" s="6"/>
-      <c r="QPN20" s="6"/>
-      <c r="QPR20" s="6"/>
-      <c r="QPV20" s="6"/>
-      <c r="QPZ20" s="6"/>
-      <c r="QQD20" s="6"/>
-      <c r="QQH20" s="6"/>
-      <c r="QQL20" s="6"/>
-      <c r="QQP20" s="6"/>
-      <c r="QQT20" s="6"/>
-      <c r="QQX20" s="6"/>
-      <c r="QRB20" s="6"/>
-      <c r="QRF20" s="6"/>
-      <c r="QRJ20" s="6"/>
-      <c r="QRN20" s="6"/>
-      <c r="QRR20" s="6"/>
-      <c r="QRV20" s="6"/>
-      <c r="QRZ20" s="6"/>
-      <c r="QSD20" s="6"/>
-      <c r="QSH20" s="6"/>
-      <c r="QSL20" s="6"/>
-      <c r="QSP20" s="6"/>
-      <c r="QST20" s="6"/>
-      <c r="QSX20" s="6"/>
-      <c r="QTB20" s="6"/>
-      <c r="QTF20" s="6"/>
-      <c r="QTJ20" s="6"/>
-      <c r="QTN20" s="6"/>
-      <c r="QTR20" s="6"/>
-      <c r="QTV20" s="6"/>
-      <c r="QTZ20" s="6"/>
-      <c r="QUD20" s="6"/>
-      <c r="QUH20" s="6"/>
-      <c r="QUL20" s="6"/>
-      <c r="QUP20" s="6"/>
-      <c r="QUT20" s="6"/>
-      <c r="QUX20" s="6"/>
-      <c r="QVB20" s="6"/>
-      <c r="QVF20" s="6"/>
-      <c r="QVJ20" s="6"/>
-      <c r="QVN20" s="6"/>
-      <c r="QVR20" s="6"/>
-      <c r="QVV20" s="6"/>
-      <c r="QVZ20" s="6"/>
-      <c r="QWD20" s="6"/>
-      <c r="QWH20" s="6"/>
-      <c r="QWL20" s="6"/>
-      <c r="QWP20" s="6"/>
-      <c r="QWT20" s="6"/>
-      <c r="QWX20" s="6"/>
-      <c r="QXB20" s="6"/>
-      <c r="QXF20" s="6"/>
-      <c r="QXJ20" s="6"/>
-      <c r="QXN20" s="6"/>
-      <c r="QXR20" s="6"/>
-      <c r="QXV20" s="6"/>
-      <c r="QXZ20" s="6"/>
-      <c r="QYD20" s="6"/>
-      <c r="QYH20" s="6"/>
-      <c r="QYL20" s="6"/>
-      <c r="QYP20" s="6"/>
-      <c r="QYT20" s="6"/>
-      <c r="QYX20" s="6"/>
-      <c r="QZB20" s="6"/>
-      <c r="QZF20" s="6"/>
-      <c r="QZJ20" s="6"/>
-      <c r="QZN20" s="6"/>
-      <c r="QZR20" s="6"/>
-      <c r="QZV20" s="6"/>
-      <c r="QZZ20" s="6"/>
-      <c r="RAD20" s="6"/>
-      <c r="RAH20" s="6"/>
-      <c r="RAL20" s="6"/>
-      <c r="RAP20" s="6"/>
-      <c r="RAT20" s="6"/>
-      <c r="RAX20" s="6"/>
-      <c r="RBB20" s="6"/>
-      <c r="RBF20" s="6"/>
-      <c r="RBJ20" s="6"/>
-      <c r="RBN20" s="6"/>
-      <c r="RBR20" s="6"/>
-      <c r="RBV20" s="6"/>
-      <c r="RBZ20" s="6"/>
-      <c r="RCD20" s="6"/>
-      <c r="RCH20" s="6"/>
-      <c r="RCL20" s="6"/>
-      <c r="RCP20" s="6"/>
-      <c r="RCT20" s="6"/>
-      <c r="RCX20" s="6"/>
-      <c r="RDB20" s="6"/>
-      <c r="RDF20" s="6"/>
-      <c r="RDJ20" s="6"/>
-      <c r="RDN20" s="6"/>
-      <c r="RDR20" s="6"/>
-      <c r="RDV20" s="6"/>
-      <c r="RDZ20" s="6"/>
-      <c r="RED20" s="6"/>
-      <c r="REH20" s="6"/>
-      <c r="REL20" s="6"/>
-      <c r="REP20" s="6"/>
-      <c r="RET20" s="6"/>
-      <c r="REX20" s="6"/>
-      <c r="RFB20" s="6"/>
-      <c r="RFF20" s="6"/>
-      <c r="RFJ20" s="6"/>
-      <c r="RFN20" s="6"/>
-      <c r="RFR20" s="6"/>
-      <c r="RFV20" s="6"/>
-      <c r="RFZ20" s="6"/>
-      <c r="RGD20" s="6"/>
-      <c r="RGH20" s="6"/>
-      <c r="RGL20" s="6"/>
-      <c r="RGP20" s="6"/>
-      <c r="RGT20" s="6"/>
-      <c r="RGX20" s="6"/>
-      <c r="RHB20" s="6"/>
-      <c r="RHF20" s="6"/>
-      <c r="RHJ20" s="6"/>
-      <c r="RHN20" s="6"/>
-      <c r="RHR20" s="6"/>
-      <c r="RHV20" s="6"/>
-      <c r="RHZ20" s="6"/>
-      <c r="RID20" s="6"/>
-      <c r="RIH20" s="6"/>
-      <c r="RIL20" s="6"/>
-      <c r="RIP20" s="6"/>
-      <c r="RIT20" s="6"/>
-      <c r="RIX20" s="6"/>
-      <c r="RJB20" s="6"/>
-      <c r="RJF20" s="6"/>
-      <c r="RJJ20" s="6"/>
-      <c r="RJN20" s="6"/>
-      <c r="RJR20" s="6"/>
-      <c r="RJV20" s="6"/>
-      <c r="RJZ20" s="6"/>
-      <c r="RKD20" s="6"/>
-      <c r="RKH20" s="6"/>
-      <c r="RKL20" s="6"/>
-      <c r="RKP20" s="6"/>
-      <c r="RKT20" s="6"/>
-      <c r="RKX20" s="6"/>
-      <c r="RLB20" s="6"/>
-      <c r="RLF20" s="6"/>
-      <c r="RLJ20" s="6"/>
-      <c r="RLN20" s="6"/>
-      <c r="RLR20" s="6"/>
-      <c r="RLV20" s="6"/>
-      <c r="RLZ20" s="6"/>
-      <c r="RMD20" s="6"/>
-      <c r="RMH20" s="6"/>
-      <c r="RML20" s="6"/>
-      <c r="RMP20" s="6"/>
-      <c r="RMT20" s="6"/>
-      <c r="RMX20" s="6"/>
-      <c r="RNB20" s="6"/>
-      <c r="RNF20" s="6"/>
-      <c r="RNJ20" s="6"/>
-      <c r="RNN20" s="6"/>
-      <c r="RNR20" s="6"/>
-      <c r="RNV20" s="6"/>
-      <c r="RNZ20" s="6"/>
-      <c r="ROD20" s="6"/>
-      <c r="ROH20" s="6"/>
-      <c r="ROL20" s="6"/>
-      <c r="ROP20" s="6"/>
-      <c r="ROT20" s="6"/>
-      <c r="ROX20" s="6"/>
-      <c r="RPB20" s="6"/>
-      <c r="RPF20" s="6"/>
-      <c r="RPJ20" s="6"/>
-      <c r="RPN20" s="6"/>
-      <c r="RPR20" s="6"/>
-      <c r="RPV20" s="6"/>
-      <c r="RPZ20" s="6"/>
-      <c r="RQD20" s="6"/>
-      <c r="RQH20" s="6"/>
-      <c r="RQL20" s="6"/>
-      <c r="RQP20" s="6"/>
-      <c r="RQT20" s="6"/>
-      <c r="RQX20" s="6"/>
-      <c r="RRB20" s="6"/>
-      <c r="RRF20" s="6"/>
-      <c r="RRJ20" s="6"/>
-      <c r="RRN20" s="6"/>
-      <c r="RRR20" s="6"/>
-      <c r="RRV20" s="6"/>
-      <c r="RRZ20" s="6"/>
-      <c r="RSD20" s="6"/>
-      <c r="RSH20" s="6"/>
-      <c r="RSL20" s="6"/>
-      <c r="RSP20" s="6"/>
-      <c r="RST20" s="6"/>
-      <c r="RSX20" s="6"/>
-      <c r="RTB20" s="6"/>
-      <c r="RTF20" s="6"/>
-      <c r="RTJ20" s="6"/>
-      <c r="RTN20" s="6"/>
-      <c r="RTR20" s="6"/>
-      <c r="RTV20" s="6"/>
-      <c r="RTZ20" s="6"/>
-      <c r="RUD20" s="6"/>
-      <c r="RUH20" s="6"/>
-      <c r="RUL20" s="6"/>
-      <c r="RUP20" s="6"/>
-      <c r="RUT20" s="6"/>
-      <c r="RUX20" s="6"/>
-      <c r="RVB20" s="6"/>
-      <c r="RVF20" s="6"/>
-      <c r="RVJ20" s="6"/>
-      <c r="RVN20" s="6"/>
-      <c r="RVR20" s="6"/>
-      <c r="RVV20" s="6"/>
-      <c r="RVZ20" s="6"/>
-      <c r="RWD20" s="6"/>
-      <c r="RWH20" s="6"/>
-      <c r="RWL20" s="6"/>
-      <c r="RWP20" s="6"/>
-      <c r="RWT20" s="6"/>
-      <c r="RWX20" s="6"/>
-      <c r="RXB20" s="6"/>
-      <c r="RXF20" s="6"/>
-      <c r="RXJ20" s="6"/>
-      <c r="RXN20" s="6"/>
-      <c r="RXR20" s="6"/>
-      <c r="RXV20" s="6"/>
-      <c r="RXZ20" s="6"/>
-      <c r="RYD20" s="6"/>
-      <c r="RYH20" s="6"/>
-      <c r="RYL20" s="6"/>
-      <c r="RYP20" s="6"/>
-      <c r="RYT20" s="6"/>
-      <c r="RYX20" s="6"/>
-      <c r="RZB20" s="6"/>
-      <c r="RZF20" s="6"/>
-      <c r="RZJ20" s="6"/>
-      <c r="RZN20" s="6"/>
-      <c r="RZR20" s="6"/>
-      <c r="RZV20" s="6"/>
-      <c r="RZZ20" s="6"/>
-      <c r="SAD20" s="6"/>
-      <c r="SAH20" s="6"/>
-      <c r="SAL20" s="6"/>
-      <c r="SAP20" s="6"/>
-      <c r="SAT20" s="6"/>
-      <c r="SAX20" s="6"/>
-      <c r="SBB20" s="6"/>
-      <c r="SBF20" s="6"/>
-      <c r="SBJ20" s="6"/>
-      <c r="SBN20" s="6"/>
-      <c r="SBR20" s="6"/>
-      <c r="SBV20" s="6"/>
-      <c r="SBZ20" s="6"/>
-      <c r="SCD20" s="6"/>
-      <c r="SCH20" s="6"/>
-      <c r="SCL20" s="6"/>
-      <c r="SCP20" s="6"/>
-      <c r="SCT20" s="6"/>
-      <c r="SCX20" s="6"/>
-      <c r="SDB20" s="6"/>
-      <c r="SDF20" s="6"/>
-      <c r="SDJ20" s="6"/>
-      <c r="SDN20" s="6"/>
-      <c r="SDR20" s="6"/>
-      <c r="SDV20" s="6"/>
-      <c r="SDZ20" s="6"/>
-      <c r="SED20" s="6"/>
-      <c r="SEH20" s="6"/>
-      <c r="SEL20" s="6"/>
-      <c r="SEP20" s="6"/>
-      <c r="SET20" s="6"/>
-      <c r="SEX20" s="6"/>
-      <c r="SFB20" s="6"/>
-      <c r="SFF20" s="6"/>
-      <c r="SFJ20" s="6"/>
-      <c r="SFN20" s="6"/>
-      <c r="SFR20" s="6"/>
-      <c r="SFV20" s="6"/>
-      <c r="SFZ20" s="6"/>
-      <c r="SGD20" s="6"/>
-      <c r="SGH20" s="6"/>
-      <c r="SGL20" s="6"/>
-      <c r="SGP20" s="6"/>
-      <c r="SGT20" s="6"/>
-      <c r="SGX20" s="6"/>
-      <c r="SHB20" s="6"/>
-      <c r="SHF20" s="6"/>
-      <c r="SHJ20" s="6"/>
-      <c r="SHN20" s="6"/>
-      <c r="SHR20" s="6"/>
-      <c r="SHV20" s="6"/>
-      <c r="SHZ20" s="6"/>
-      <c r="SID20" s="6"/>
-      <c r="SIH20" s="6"/>
-      <c r="SIL20" s="6"/>
-      <c r="SIP20" s="6"/>
-      <c r="SIT20" s="6"/>
-      <c r="SIX20" s="6"/>
-      <c r="SJB20" s="6"/>
-      <c r="SJF20" s="6"/>
-      <c r="SJJ20" s="6"/>
-      <c r="SJN20" s="6"/>
-      <c r="SJR20" s="6"/>
-      <c r="SJV20" s="6"/>
-      <c r="SJZ20" s="6"/>
-      <c r="SKD20" s="6"/>
-      <c r="SKH20" s="6"/>
-      <c r="SKL20" s="6"/>
-      <c r="SKP20" s="6"/>
-      <c r="SKT20" s="6"/>
-      <c r="SKX20" s="6"/>
-      <c r="SLB20" s="6"/>
-      <c r="SLF20" s="6"/>
-      <c r="SLJ20" s="6"/>
-      <c r="SLN20" s="6"/>
-      <c r="SLR20" s="6"/>
-      <c r="SLV20" s="6"/>
-      <c r="SLZ20" s="6"/>
-      <c r="SMD20" s="6"/>
-      <c r="SMH20" s="6"/>
-      <c r="SML20" s="6"/>
-      <c r="SMP20" s="6"/>
-      <c r="SMT20" s="6"/>
-      <c r="SMX20" s="6"/>
-      <c r="SNB20" s="6"/>
-      <c r="SNF20" s="6"/>
-      <c r="SNJ20" s="6"/>
-      <c r="SNN20" s="6"/>
-      <c r="SNR20" s="6"/>
-      <c r="SNV20" s="6"/>
-      <c r="SNZ20" s="6"/>
-      <c r="SOD20" s="6"/>
-      <c r="SOH20" s="6"/>
-      <c r="SOL20" s="6"/>
-      <c r="SOP20" s="6"/>
-      <c r="SOT20" s="6"/>
-      <c r="SOX20" s="6"/>
-      <c r="SPB20" s="6"/>
-      <c r="SPF20" s="6"/>
-      <c r="SPJ20" s="6"/>
-      <c r="SPN20" s="6"/>
-      <c r="SPR20" s="6"/>
-      <c r="SPV20" s="6"/>
-      <c r="SPZ20" s="6"/>
-      <c r="SQD20" s="6"/>
-      <c r="SQH20" s="6"/>
-      <c r="SQL20" s="6"/>
-      <c r="SQP20" s="6"/>
-      <c r="SQT20" s="6"/>
-      <c r="SQX20" s="6"/>
-      <c r="SRB20" s="6"/>
-      <c r="SRF20" s="6"/>
-      <c r="SRJ20" s="6"/>
-      <c r="SRN20" s="6"/>
-      <c r="SRR20" s="6"/>
-      <c r="SRV20" s="6"/>
-      <c r="SRZ20" s="6"/>
-      <c r="SSD20" s="6"/>
-      <c r="SSH20" s="6"/>
-      <c r="SSL20" s="6"/>
-      <c r="SSP20" s="6"/>
-      <c r="SST20" s="6"/>
-      <c r="SSX20" s="6"/>
-      <c r="STB20" s="6"/>
-      <c r="STF20" s="6"/>
-      <c r="STJ20" s="6"/>
-      <c r="STN20" s="6"/>
-      <c r="STR20" s="6"/>
-      <c r="STV20" s="6"/>
-      <c r="STZ20" s="6"/>
-      <c r="SUD20" s="6"/>
-      <c r="SUH20" s="6"/>
-      <c r="SUL20" s="6"/>
-      <c r="SUP20" s="6"/>
-      <c r="SUT20" s="6"/>
-      <c r="SUX20" s="6"/>
-      <c r="SVB20" s="6"/>
-      <c r="SVF20" s="6"/>
-      <c r="SVJ20" s="6"/>
-      <c r="SVN20" s="6"/>
-      <c r="SVR20" s="6"/>
-      <c r="SVV20" s="6"/>
-      <c r="SVZ20" s="6"/>
-      <c r="SWD20" s="6"/>
-      <c r="SWH20" s="6"/>
-      <c r="SWL20" s="6"/>
-      <c r="SWP20" s="6"/>
-      <c r="SWT20" s="6"/>
-      <c r="SWX20" s="6"/>
-      <c r="SXB20" s="6"/>
-      <c r="SXF20" s="6"/>
-      <c r="SXJ20" s="6"/>
-      <c r="SXN20" s="6"/>
-      <c r="SXR20" s="6"/>
-      <c r="SXV20" s="6"/>
-      <c r="SXZ20" s="6"/>
-      <c r="SYD20" s="6"/>
-      <c r="SYH20" s="6"/>
-      <c r="SYL20" s="6"/>
-      <c r="SYP20" s="6"/>
-      <c r="SYT20" s="6"/>
-      <c r="SYX20" s="6"/>
-      <c r="SZB20" s="6"/>
-      <c r="SZF20" s="6"/>
-      <c r="SZJ20" s="6"/>
-      <c r="SZN20" s="6"/>
-      <c r="SZR20" s="6"/>
-      <c r="SZV20" s="6"/>
-      <c r="SZZ20" s="6"/>
-      <c r="TAD20" s="6"/>
-      <c r="TAH20" s="6"/>
-      <c r="TAL20" s="6"/>
-      <c r="TAP20" s="6"/>
-      <c r="TAT20" s="6"/>
-      <c r="TAX20" s="6"/>
-      <c r="TBB20" s="6"/>
-      <c r="TBF20" s="6"/>
-      <c r="TBJ20" s="6"/>
-      <c r="TBN20" s="6"/>
-      <c r="TBR20" s="6"/>
-      <c r="TBV20" s="6"/>
-      <c r="TBZ20" s="6"/>
-      <c r="TCD20" s="6"/>
-      <c r="TCH20" s="6"/>
-      <c r="TCL20" s="6"/>
-      <c r="TCP20" s="6"/>
-      <c r="TCT20" s="6"/>
-      <c r="TCX20" s="6"/>
-      <c r="TDB20" s="6"/>
-      <c r="TDF20" s="6"/>
-      <c r="TDJ20" s="6"/>
-      <c r="TDN20" s="6"/>
-      <c r="TDR20" s="6"/>
-      <c r="TDV20" s="6"/>
-      <c r="TDZ20" s="6"/>
-      <c r="TED20" s="6"/>
-      <c r="TEH20" s="6"/>
-      <c r="TEL20" s="6"/>
-      <c r="TEP20" s="6"/>
-      <c r="TET20" s="6"/>
-      <c r="TEX20" s="6"/>
-      <c r="TFB20" s="6"/>
-      <c r="TFF20" s="6"/>
-      <c r="TFJ20" s="6"/>
-      <c r="TFN20" s="6"/>
-      <c r="TFR20" s="6"/>
-      <c r="TFV20" s="6"/>
-      <c r="TFZ20" s="6"/>
-      <c r="TGD20" s="6"/>
-      <c r="TGH20" s="6"/>
-      <c r="TGL20" s="6"/>
-      <c r="TGP20" s="6"/>
-      <c r="TGT20" s="6"/>
-      <c r="TGX20" s="6"/>
-      <c r="THB20" s="6"/>
-      <c r="THF20" s="6"/>
-      <c r="THJ20" s="6"/>
-      <c r="THN20" s="6"/>
-      <c r="THR20" s="6"/>
-      <c r="THV20" s="6"/>
-      <c r="THZ20" s="6"/>
-      <c r="TID20" s="6"/>
-      <c r="TIH20" s="6"/>
-      <c r="TIL20" s="6"/>
-      <c r="TIP20" s="6"/>
-      <c r="TIT20" s="6"/>
-      <c r="TIX20" s="6"/>
-      <c r="TJB20" s="6"/>
-      <c r="TJF20" s="6"/>
-      <c r="TJJ20" s="6"/>
-      <c r="TJN20" s="6"/>
-      <c r="TJR20" s="6"/>
-      <c r="TJV20" s="6"/>
-      <c r="TJZ20" s="6"/>
-      <c r="TKD20" s="6"/>
-      <c r="TKH20" s="6"/>
-      <c r="TKL20" s="6"/>
-      <c r="TKP20" s="6"/>
-      <c r="TKT20" s="6"/>
-      <c r="TKX20" s="6"/>
-      <c r="TLB20" s="6"/>
-      <c r="TLF20" s="6"/>
-      <c r="TLJ20" s="6"/>
-      <c r="TLN20" s="6"/>
-      <c r="TLR20" s="6"/>
-      <c r="TLV20" s="6"/>
-      <c r="TLZ20" s="6"/>
-      <c r="TMD20" s="6"/>
-      <c r="TMH20" s="6"/>
-      <c r="TML20" s="6"/>
-      <c r="TMP20" s="6"/>
-      <c r="TMT20" s="6"/>
-      <c r="TMX20" s="6"/>
-      <c r="TNB20" s="6"/>
-      <c r="TNF20" s="6"/>
-      <c r="TNJ20" s="6"/>
-      <c r="TNN20" s="6"/>
-      <c r="TNR20" s="6"/>
-      <c r="TNV20" s="6"/>
-      <c r="TNZ20" s="6"/>
-      <c r="TOD20" s="6"/>
-      <c r="TOH20" s="6"/>
-      <c r="TOL20" s="6"/>
-      <c r="TOP20" s="6"/>
-      <c r="TOT20" s="6"/>
-      <c r="TOX20" s="6"/>
-      <c r="TPB20" s="6"/>
-      <c r="TPF20" s="6"/>
-      <c r="TPJ20" s="6"/>
-      <c r="TPN20" s="6"/>
-      <c r="TPR20" s="6"/>
-      <c r="TPV20" s="6"/>
-      <c r="TPZ20" s="6"/>
-      <c r="TQD20" s="6"/>
-      <c r="TQH20" s="6"/>
-      <c r="TQL20" s="6"/>
-      <c r="TQP20" s="6"/>
-      <c r="TQT20" s="6"/>
-      <c r="TQX20" s="6"/>
-      <c r="TRB20" s="6"/>
-      <c r="TRF20" s="6"/>
-      <c r="TRJ20" s="6"/>
-      <c r="TRN20" s="6"/>
-      <c r="TRR20" s="6"/>
-      <c r="TRV20" s="6"/>
-      <c r="TRZ20" s="6"/>
-      <c r="TSD20" s="6"/>
-      <c r="TSH20" s="6"/>
-      <c r="TSL20" s="6"/>
-      <c r="TSP20" s="6"/>
-      <c r="TST20" s="6"/>
-      <c r="TSX20" s="6"/>
-      <c r="TTB20" s="6"/>
-      <c r="TTF20" s="6"/>
-      <c r="TTJ20" s="6"/>
-      <c r="TTN20" s="6"/>
-      <c r="TTR20" s="6"/>
-      <c r="TTV20" s="6"/>
-      <c r="TTZ20" s="6"/>
-      <c r="TUD20" s="6"/>
-      <c r="TUH20" s="6"/>
-      <c r="TUL20" s="6"/>
-      <c r="TUP20" s="6"/>
-      <c r="TUT20" s="6"/>
-      <c r="TUX20" s="6"/>
-      <c r="TVB20" s="6"/>
-      <c r="TVF20" s="6"/>
-      <c r="TVJ20" s="6"/>
-      <c r="TVN20" s="6"/>
-      <c r="TVR20" s="6"/>
-      <c r="TVV20" s="6"/>
-      <c r="TVZ20" s="6"/>
-      <c r="TWD20" s="6"/>
-      <c r="TWH20" s="6"/>
-      <c r="TWL20" s="6"/>
-      <c r="TWP20" s="6"/>
-      <c r="TWT20" s="6"/>
-      <c r="TWX20" s="6"/>
-      <c r="TXB20" s="6"/>
-      <c r="TXF20" s="6"/>
-      <c r="TXJ20" s="6"/>
-      <c r="TXN20" s="6"/>
-      <c r="TXR20" s="6"/>
-      <c r="TXV20" s="6"/>
-      <c r="TXZ20" s="6"/>
-      <c r="TYD20" s="6"/>
-      <c r="TYH20" s="6"/>
-      <c r="TYL20" s="6"/>
-      <c r="TYP20" s="6"/>
-      <c r="TYT20" s="6"/>
-      <c r="TYX20" s="6"/>
-      <c r="TZB20" s="6"/>
-      <c r="TZF20" s="6"/>
-      <c r="TZJ20" s="6"/>
-      <c r="TZN20" s="6"/>
-      <c r="TZR20" s="6"/>
-      <c r="TZV20" s="6"/>
-      <c r="TZZ20" s="6"/>
-      <c r="UAD20" s="6"/>
-      <c r="UAH20" s="6"/>
-      <c r="UAL20" s="6"/>
-      <c r="UAP20" s="6"/>
-      <c r="UAT20" s="6"/>
-      <c r="UAX20" s="6"/>
-      <c r="UBB20" s="6"/>
-      <c r="UBF20" s="6"/>
-      <c r="UBJ20" s="6"/>
-      <c r="UBN20" s="6"/>
-      <c r="UBR20" s="6"/>
-      <c r="UBV20" s="6"/>
-      <c r="UBZ20" s="6"/>
-      <c r="UCD20" s="6"/>
-      <c r="UCH20" s="6"/>
-      <c r="UCL20" s="6"/>
-      <c r="UCP20" s="6"/>
-      <c r="UCT20" s="6"/>
-      <c r="UCX20" s="6"/>
-      <c r="UDB20" s="6"/>
-      <c r="UDF20" s="6"/>
-      <c r="UDJ20" s="6"/>
-      <c r="UDN20" s="6"/>
-      <c r="UDR20" s="6"/>
-      <c r="UDV20" s="6"/>
-      <c r="UDZ20" s="6"/>
-      <c r="UED20" s="6"/>
-      <c r="UEH20" s="6"/>
-      <c r="UEL20" s="6"/>
-      <c r="UEP20" s="6"/>
-      <c r="UET20" s="6"/>
-      <c r="UEX20" s="6"/>
-      <c r="UFB20" s="6"/>
-      <c r="UFF20" s="6"/>
-      <c r="UFJ20" s="6"/>
-      <c r="UFN20" s="6"/>
-      <c r="UFR20" s="6"/>
-      <c r="UFV20" s="6"/>
-      <c r="UFZ20" s="6"/>
-      <c r="UGD20" s="6"/>
-      <c r="UGH20" s="6"/>
-      <c r="UGL20" s="6"/>
-      <c r="UGP20" s="6"/>
-      <c r="UGT20" s="6"/>
-      <c r="UGX20" s="6"/>
-      <c r="UHB20" s="6"/>
-      <c r="UHF20" s="6"/>
-      <c r="UHJ20" s="6"/>
-      <c r="UHN20" s="6"/>
-      <c r="UHR20" s="6"/>
-      <c r="UHV20" s="6"/>
-      <c r="UHZ20" s="6"/>
-      <c r="UID20" s="6"/>
-      <c r="UIH20" s="6"/>
-      <c r="UIL20" s="6"/>
-      <c r="UIP20" s="6"/>
-      <c r="UIT20" s="6"/>
-      <c r="UIX20" s="6"/>
-      <c r="UJB20" s="6"/>
-      <c r="UJF20" s="6"/>
-      <c r="UJJ20" s="6"/>
-      <c r="UJN20" s="6"/>
-      <c r="UJR20" s="6"/>
-      <c r="UJV20" s="6"/>
-      <c r="UJZ20" s="6"/>
-      <c r="UKD20" s="6"/>
-      <c r="UKH20" s="6"/>
-      <c r="UKL20" s="6"/>
-      <c r="UKP20" s="6"/>
-      <c r="UKT20" s="6"/>
-      <c r="UKX20" s="6"/>
-      <c r="ULB20" s="6"/>
-      <c r="ULF20" s="6"/>
-      <c r="ULJ20" s="6"/>
-      <c r="ULN20" s="6"/>
-      <c r="ULR20" s="6"/>
-      <c r="ULV20" s="6"/>
-      <c r="ULZ20" s="6"/>
-      <c r="UMD20" s="6"/>
-      <c r="UMH20" s="6"/>
-      <c r="UML20" s="6"/>
-      <c r="UMP20" s="6"/>
-      <c r="UMT20" s="6"/>
-      <c r="UMX20" s="6"/>
-      <c r="UNB20" s="6"/>
-      <c r="UNF20" s="6"/>
-      <c r="UNJ20" s="6"/>
-      <c r="UNN20" s="6"/>
-      <c r="UNR20" s="6"/>
-      <c r="UNV20" s="6"/>
-      <c r="UNZ20" s="6"/>
-      <c r="UOD20" s="6"/>
-      <c r="UOH20" s="6"/>
-      <c r="UOL20" s="6"/>
-      <c r="UOP20" s="6"/>
-      <c r="UOT20" s="6"/>
-      <c r="UOX20" s="6"/>
-      <c r="UPB20" s="6"/>
-      <c r="UPF20" s="6"/>
-      <c r="UPJ20" s="6"/>
-      <c r="UPN20" s="6"/>
-      <c r="UPR20" s="6"/>
-      <c r="UPV20" s="6"/>
-      <c r="UPZ20" s="6"/>
-      <c r="UQD20" s="6"/>
-      <c r="UQH20" s="6"/>
-      <c r="UQL20" s="6"/>
-      <c r="UQP20" s="6"/>
-      <c r="UQT20" s="6"/>
-      <c r="UQX20" s="6"/>
-      <c r="URB20" s="6"/>
-      <c r="URF20" s="6"/>
-      <c r="URJ20" s="6"/>
-      <c r="URN20" s="6"/>
-      <c r="URR20" s="6"/>
-      <c r="URV20" s="6"/>
-      <c r="URZ20" s="6"/>
-      <c r="USD20" s="6"/>
-      <c r="USH20" s="6"/>
-      <c r="USL20" s="6"/>
-      <c r="USP20" s="6"/>
-      <c r="UST20" s="6"/>
-      <c r="USX20" s="6"/>
-      <c r="UTB20" s="6"/>
-      <c r="UTF20" s="6"/>
-      <c r="UTJ20" s="6"/>
-      <c r="UTN20" s="6"/>
-      <c r="UTR20" s="6"/>
-      <c r="UTV20" s="6"/>
-      <c r="UTZ20" s="6"/>
-      <c r="UUD20" s="6"/>
-      <c r="UUH20" s="6"/>
-      <c r="UUL20" s="6"/>
-      <c r="UUP20" s="6"/>
-      <c r="UUT20" s="6"/>
-      <c r="UUX20" s="6"/>
-      <c r="UVB20" s="6"/>
-      <c r="UVF20" s="6"/>
-      <c r="UVJ20" s="6"/>
-      <c r="UVN20" s="6"/>
-      <c r="UVR20" s="6"/>
-      <c r="UVV20" s="6"/>
-      <c r="UVZ20" s="6"/>
-      <c r="UWD20" s="6"/>
-      <c r="UWH20" s="6"/>
-      <c r="UWL20" s="6"/>
-      <c r="UWP20" s="6"/>
-      <c r="UWT20" s="6"/>
-      <c r="UWX20" s="6"/>
-      <c r="UXB20" s="6"/>
-      <c r="UXF20" s="6"/>
-      <c r="UXJ20" s="6"/>
-      <c r="UXN20" s="6"/>
-      <c r="UXR20" s="6"/>
-      <c r="UXV20" s="6"/>
-      <c r="UXZ20" s="6"/>
-      <c r="UYD20" s="6"/>
-      <c r="UYH20" s="6"/>
-      <c r="UYL20" s="6"/>
-      <c r="UYP20" s="6"/>
-      <c r="UYT20" s="6"/>
-      <c r="UYX20" s="6"/>
-      <c r="UZB20" s="6"/>
-      <c r="UZF20" s="6"/>
-      <c r="UZJ20" s="6"/>
-      <c r="UZN20" s="6"/>
-      <c r="UZR20" s="6"/>
-      <c r="UZV20" s="6"/>
-      <c r="UZZ20" s="6"/>
-      <c r="VAD20" s="6"/>
-      <c r="VAH20" s="6"/>
-      <c r="VAL20" s="6"/>
-      <c r="VAP20" s="6"/>
-      <c r="VAT20" s="6"/>
-      <c r="VAX20" s="6"/>
-      <c r="VBB20" s="6"/>
-      <c r="VBF20" s="6"/>
-      <c r="VBJ20" s="6"/>
-      <c r="VBN20" s="6"/>
-      <c r="VBR20" s="6"/>
-      <c r="VBV20" s="6"/>
-      <c r="VBZ20" s="6"/>
-      <c r="VCD20" s="6"/>
-      <c r="VCH20" s="6"/>
-      <c r="VCL20" s="6"/>
-      <c r="VCP20" s="6"/>
-      <c r="VCT20" s="6"/>
-      <c r="VCX20" s="6"/>
-      <c r="VDB20" s="6"/>
-      <c r="VDF20" s="6"/>
-      <c r="VDJ20" s="6"/>
-      <c r="VDN20" s="6"/>
-      <c r="VDR20" s="6"/>
-      <c r="VDV20" s="6"/>
-      <c r="VDZ20" s="6"/>
-      <c r="VED20" s="6"/>
-      <c r="VEH20" s="6"/>
-      <c r="VEL20" s="6"/>
-      <c r="VEP20" s="6"/>
-      <c r="VET20" s="6"/>
-      <c r="VEX20" s="6"/>
-      <c r="VFB20" s="6"/>
-      <c r="VFF20" s="6"/>
-      <c r="VFJ20" s="6"/>
-      <c r="VFN20" s="6"/>
-      <c r="VFR20" s="6"/>
-      <c r="VFV20" s="6"/>
-      <c r="VFZ20" s="6"/>
-      <c r="VGD20" s="6"/>
-      <c r="VGH20" s="6"/>
-      <c r="VGL20" s="6"/>
-      <c r="VGP20" s="6"/>
-      <c r="VGT20" s="6"/>
-      <c r="VGX20" s="6"/>
-      <c r="VHB20" s="6"/>
-      <c r="VHF20" s="6"/>
-      <c r="VHJ20" s="6"/>
-      <c r="VHN20" s="6"/>
-      <c r="VHR20" s="6"/>
-      <c r="VHV20" s="6"/>
-      <c r="VHZ20" s="6"/>
-      <c r="VID20" s="6"/>
-      <c r="VIH20" s="6"/>
-      <c r="VIL20" s="6"/>
-      <c r="VIP20" s="6"/>
-      <c r="VIT20" s="6"/>
-      <c r="VIX20" s="6"/>
-      <c r="VJB20" s="6"/>
-      <c r="VJF20" s="6"/>
-      <c r="VJJ20" s="6"/>
-      <c r="VJN20" s="6"/>
-      <c r="VJR20" s="6"/>
-      <c r="VJV20" s="6"/>
-      <c r="VJZ20" s="6"/>
-      <c r="VKD20" s="6"/>
-      <c r="VKH20" s="6"/>
-      <c r="VKL20" s="6"/>
-      <c r="VKP20" s="6"/>
-      <c r="VKT20" s="6"/>
-      <c r="VKX20" s="6"/>
-      <c r="VLB20" s="6"/>
-      <c r="VLF20" s="6"/>
-      <c r="VLJ20" s="6"/>
-      <c r="VLN20" s="6"/>
-      <c r="VLR20" s="6"/>
-      <c r="VLV20" s="6"/>
-      <c r="VLZ20" s="6"/>
-      <c r="VMD20" s="6"/>
-      <c r="VMH20" s="6"/>
-      <c r="VML20" s="6"/>
-      <c r="VMP20" s="6"/>
-      <c r="VMT20" s="6"/>
-      <c r="VMX20" s="6"/>
-      <c r="VNB20" s="6"/>
-      <c r="VNF20" s="6"/>
-      <c r="VNJ20" s="6"/>
-      <c r="VNN20" s="6"/>
-      <c r="VNR20" s="6"/>
-      <c r="VNV20" s="6"/>
-      <c r="VNZ20" s="6"/>
-      <c r="VOD20" s="6"/>
-      <c r="VOH20" s="6"/>
-      <c r="VOL20" s="6"/>
-      <c r="VOP20" s="6"/>
-      <c r="VOT20" s="6"/>
-      <c r="VOX20" s="6"/>
-      <c r="VPB20" s="6"/>
-      <c r="VPF20" s="6"/>
-      <c r="VPJ20" s="6"/>
-      <c r="VPN20" s="6"/>
-      <c r="VPR20" s="6"/>
-      <c r="VPV20" s="6"/>
-      <c r="VPZ20" s="6"/>
-      <c r="VQD20" s="6"/>
-      <c r="VQH20" s="6"/>
-      <c r="VQL20" s="6"/>
-      <c r="VQP20" s="6"/>
-      <c r="VQT20" s="6"/>
-      <c r="VQX20" s="6"/>
-      <c r="VRB20" s="6"/>
-      <c r="VRF20" s="6"/>
-      <c r="VRJ20" s="6"/>
-      <c r="VRN20" s="6"/>
-      <c r="VRR20" s="6"/>
-      <c r="VRV20" s="6"/>
-      <c r="VRZ20" s="6"/>
-      <c r="VSD20" s="6"/>
-      <c r="VSH20" s="6"/>
-      <c r="VSL20" s="6"/>
-      <c r="VSP20" s="6"/>
-      <c r="VST20" s="6"/>
-      <c r="VSX20" s="6"/>
-      <c r="VTB20" s="6"/>
-      <c r="VTF20" s="6"/>
-      <c r="VTJ20" s="6"/>
-      <c r="VTN20" s="6"/>
-      <c r="VTR20" s="6"/>
-      <c r="VTV20" s="6"/>
-      <c r="VTZ20" s="6"/>
-      <c r="VUD20" s="6"/>
-      <c r="VUH20" s="6"/>
-      <c r="VUL20" s="6"/>
-      <c r="VUP20" s="6"/>
-      <c r="VUT20" s="6"/>
-      <c r="VUX20" s="6"/>
-      <c r="VVB20" s="6"/>
-      <c r="VVF20" s="6"/>
-      <c r="VVJ20" s="6"/>
-      <c r="VVN20" s="6"/>
-      <c r="VVR20" s="6"/>
-      <c r="VVV20" s="6"/>
-      <c r="VVZ20" s="6"/>
-      <c r="VWD20" s="6"/>
-      <c r="VWH20" s="6"/>
-      <c r="VWL20" s="6"/>
-      <c r="VWP20" s="6"/>
-      <c r="VWT20" s="6"/>
-      <c r="VWX20" s="6"/>
-      <c r="VXB20" s="6"/>
-      <c r="VXF20" s="6"/>
-      <c r="VXJ20" s="6"/>
-      <c r="VXN20" s="6"/>
-      <c r="VXR20" s="6"/>
-      <c r="VXV20" s="6"/>
-      <c r="VXZ20" s="6"/>
-      <c r="VYD20" s="6"/>
-      <c r="VYH20" s="6"/>
-      <c r="VYL20" s="6"/>
-      <c r="VYP20" s="6"/>
-      <c r="VYT20" s="6"/>
-      <c r="VYX20" s="6"/>
-      <c r="VZB20" s="6"/>
-      <c r="VZF20" s="6"/>
-      <c r="VZJ20" s="6"/>
-      <c r="VZN20" s="6"/>
-      <c r="VZR20" s="6"/>
-      <c r="VZV20" s="6"/>
-      <c r="VZZ20" s="6"/>
-      <c r="WAD20" s="6"/>
-      <c r="WAH20" s="6"/>
-      <c r="WAL20" s="6"/>
-      <c r="WAP20" s="6"/>
-      <c r="WAT20" s="6"/>
-      <c r="WAX20" s="6"/>
-      <c r="WBB20" s="6"/>
-      <c r="WBF20" s="6"/>
-      <c r="WBJ20" s="6"/>
-      <c r="WBN20" s="6"/>
-      <c r="WBR20" s="6"/>
-      <c r="WBV20" s="6"/>
-      <c r="WBZ20" s="6"/>
-      <c r="WCD20" s="6"/>
-      <c r="WCH20" s="6"/>
-      <c r="WCL20" s="6"/>
-      <c r="WCP20" s="6"/>
-      <c r="WCT20" s="6"/>
-      <c r="WCX20" s="6"/>
-      <c r="WDB20" s="6"/>
-      <c r="WDF20" s="6"/>
-      <c r="WDJ20" s="6"/>
-      <c r="WDN20" s="6"/>
-      <c r="WDR20" s="6"/>
-      <c r="WDV20" s="6"/>
-      <c r="WDZ20" s="6"/>
-      <c r="WED20" s="6"/>
-      <c r="WEH20" s="6"/>
-      <c r="WEL20" s="6"/>
-      <c r="WEP20" s="6"/>
-      <c r="WET20" s="6"/>
-      <c r="WEX20" s="6"/>
-      <c r="WFB20" s="6"/>
-      <c r="WFF20" s="6"/>
-      <c r="WFJ20" s="6"/>
-      <c r="WFN20" s="6"/>
-      <c r="WFR20" s="6"/>
-      <c r="WFV20" s="6"/>
-      <c r="WFZ20" s="6"/>
-      <c r="WGD20" s="6"/>
-      <c r="WGH20" s="6"/>
-      <c r="WGL20" s="6"/>
-      <c r="WGP20" s="6"/>
-      <c r="WGT20" s="6"/>
-      <c r="WGX20" s="6"/>
-      <c r="WHB20" s="6"/>
-      <c r="WHF20" s="6"/>
-      <c r="WHJ20" s="6"/>
-      <c r="WHN20" s="6"/>
-      <c r="WHR20" s="6"/>
-      <c r="WHV20" s="6"/>
-      <c r="WHZ20" s="6"/>
-      <c r="WID20" s="6"/>
-      <c r="WIH20" s="6"/>
-      <c r="WIL20" s="6"/>
-      <c r="WIP20" s="6"/>
-      <c r="WIT20" s="6"/>
-      <c r="WIX20" s="6"/>
-      <c r="WJB20" s="6"/>
-      <c r="WJF20" s="6"/>
-      <c r="WJJ20" s="6"/>
-      <c r="WJN20" s="6"/>
-      <c r="WJR20" s="6"/>
-      <c r="WJV20" s="6"/>
-      <c r="WJZ20" s="6"/>
-      <c r="WKD20" s="6"/>
-      <c r="WKH20" s="6"/>
-      <c r="WKL20" s="6"/>
-      <c r="WKP20" s="6"/>
-      <c r="WKT20" s="6"/>
-      <c r="WKX20" s="6"/>
-      <c r="WLB20" s="6"/>
-      <c r="WLF20" s="6"/>
-      <c r="WLJ20" s="6"/>
-      <c r="WLN20" s="6"/>
-      <c r="WLR20" s="6"/>
-      <c r="WLV20" s="6"/>
-      <c r="WLZ20" s="6"/>
-      <c r="WMD20" s="6"/>
-      <c r="WMH20" s="6"/>
-      <c r="WML20" s="6"/>
-      <c r="WMP20" s="6"/>
-      <c r="WMT20" s="6"/>
-      <c r="WMX20" s="6"/>
-      <c r="WNB20" s="6"/>
-      <c r="WNF20" s="6"/>
-      <c r="WNJ20" s="6"/>
-      <c r="WNN20" s="6"/>
-      <c r="WNR20" s="6"/>
-      <c r="WNV20" s="6"/>
-      <c r="WNZ20" s="6"/>
-      <c r="WOD20" s="6"/>
-      <c r="WOH20" s="6"/>
-      <c r="WOL20" s="6"/>
-      <c r="WOP20" s="6"/>
-      <c r="WOT20" s="6"/>
-      <c r="WOX20" s="6"/>
-      <c r="WPB20" s="6"/>
-      <c r="WPF20" s="6"/>
-      <c r="WPJ20" s="6"/>
-      <c r="WPN20" s="6"/>
-      <c r="WPR20" s="6"/>
-      <c r="WPV20" s="6"/>
-      <c r="WPZ20" s="6"/>
-      <c r="WQD20" s="6"/>
-      <c r="WQH20" s="6"/>
-      <c r="WQL20" s="6"/>
-      <c r="WQP20" s="6"/>
-      <c r="WQT20" s="6"/>
-      <c r="WQX20" s="6"/>
-      <c r="WRB20" s="6"/>
-      <c r="WRF20" s="6"/>
-      <c r="WRJ20" s="6"/>
-      <c r="WRN20" s="6"/>
-      <c r="WRR20" s="6"/>
-      <c r="WRV20" s="6"/>
-      <c r="WRZ20" s="6"/>
-      <c r="WSD20" s="6"/>
-      <c r="WSH20" s="6"/>
-      <c r="WSL20" s="6"/>
-      <c r="WSP20" s="6"/>
-      <c r="WST20" s="6"/>
-      <c r="WSX20" s="6"/>
-      <c r="WTB20" s="6"/>
-      <c r="WTF20" s="6"/>
-      <c r="WTJ20" s="6"/>
-      <c r="WTN20" s="6"/>
-      <c r="WTR20" s="6"/>
-      <c r="WTV20" s="6"/>
-      <c r="WTZ20" s="6"/>
-      <c r="WUD20" s="6"/>
-      <c r="WUH20" s="6"/>
-      <c r="WUL20" s="6"/>
-      <c r="WUP20" s="6"/>
-      <c r="WUT20" s="6"/>
-      <c r="WUX20" s="6"/>
-      <c r="WVB20" s="6"/>
-      <c r="WVF20" s="6"/>
-      <c r="WVJ20" s="6"/>
-      <c r="WVN20" s="6"/>
-      <c r="WVR20" s="6"/>
-      <c r="WVV20" s="6"/>
-      <c r="WVZ20" s="6"/>
-      <c r="WWD20" s="6"/>
-      <c r="WWH20" s="6"/>
-      <c r="WWL20" s="6"/>
-      <c r="WWP20" s="6"/>
-      <c r="WWT20" s="6"/>
-      <c r="WWX20" s="6"/>
-      <c r="WXB20" s="6"/>
-      <c r="WXF20" s="6"/>
-      <c r="WXJ20" s="6"/>
-      <c r="WXN20" s="6"/>
-      <c r="WXR20" s="6"/>
-      <c r="WXV20" s="6"/>
-      <c r="WXZ20" s="6"/>
-      <c r="WYD20" s="6"/>
-      <c r="WYH20" s="6"/>
-      <c r="WYL20" s="6"/>
-      <c r="WYP20" s="6"/>
-      <c r="WYT20" s="6"/>
-      <c r="WYX20" s="6"/>
-      <c r="WZB20" s="6"/>
-      <c r="WZF20" s="6"/>
-      <c r="WZJ20" s="6"/>
-      <c r="WZN20" s="6"/>
-      <c r="WZR20" s="6"/>
-      <c r="WZV20" s="6"/>
-      <c r="WZZ20" s="6"/>
-      <c r="XAD20" s="6"/>
-      <c r="XAH20" s="6"/>
-      <c r="XAL20" s="6"/>
-      <c r="XAP20" s="6"/>
-      <c r="XAT20" s="6"/>
-      <c r="XAX20" s="6"/>
-      <c r="XBB20" s="6"/>
-      <c r="XBF20" s="6"/>
-      <c r="XBJ20" s="6"/>
-      <c r="XBN20" s="6"/>
-      <c r="XBR20" s="6"/>
-      <c r="XBV20" s="6"/>
-      <c r="XBZ20" s="6"/>
-      <c r="XCD20" s="6"/>
-      <c r="XCH20" s="6"/>
-      <c r="XCL20" s="6"/>
-      <c r="XCP20" s="6"/>
-      <c r="XCT20" s="6"/>
-      <c r="XCX20" s="6"/>
-      <c r="XDB20" s="6"/>
-      <c r="XDF20" s="6"/>
-      <c r="XDJ20" s="6"/>
-      <c r="XDN20" s="6"/>
-      <c r="XDR20" s="6"/>
-      <c r="XDV20" s="6"/>
-      <c r="XDZ20" s="6"/>
-      <c r="XED20" s="6"/>
-      <c r="XEH20" s="6"/>
-      <c r="XEL20" s="6"/>
-      <c r="XEP20" s="6"/>
-      <c r="XET20" s="6"/>
-      <c r="XEX20" s="6"/>
-      <c r="XFB20" s="6"/>
+    <row r="20" spans="2:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" s="7" customFormat="1">
+      <c r="B20" s="8"/>
+      <c r="F20" s="5"/>
+      <c r="J20" s="8"/>
+      <c r="L20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="R20" s="5"/>
+      <c r="V20" s="5"/>
+      <c r="Z20" s="5"/>
+      <c r="AD20" s="5"/>
+      <c r="AH20" s="5"/>
+      <c r="AL20" s="5"/>
+      <c r="AP20" s="5"/>
+      <c r="AT20" s="5"/>
+      <c r="AX20" s="5"/>
+      <c r="BB20" s="5"/>
+      <c r="BF20" s="5"/>
+      <c r="BJ20" s="5"/>
+      <c r="BN20" s="5"/>
+      <c r="BR20" s="5"/>
+      <c r="BV20" s="5"/>
+      <c r="BZ20" s="5"/>
+      <c r="CD20" s="5"/>
+      <c r="CH20" s="5"/>
+      <c r="CL20" s="5"/>
+      <c r="CP20" s="5"/>
+      <c r="CT20" s="5"/>
+      <c r="CX20" s="5"/>
+      <c r="DB20" s="5"/>
+      <c r="DF20" s="5"/>
+      <c r="DJ20" s="5"/>
+      <c r="DN20" s="5"/>
+      <c r="DR20" s="5"/>
+      <c r="DV20" s="5"/>
+      <c r="DZ20" s="5"/>
+      <c r="ED20" s="5"/>
+      <c r="EH20" s="5"/>
+      <c r="EL20" s="5"/>
+      <c r="EP20" s="5"/>
+      <c r="ET20" s="5"/>
+      <c r="EX20" s="5"/>
+      <c r="FB20" s="5"/>
+      <c r="FF20" s="5"/>
+      <c r="FJ20" s="5"/>
+      <c r="FN20" s="5"/>
+      <c r="FR20" s="5"/>
+      <c r="FV20" s="5"/>
+      <c r="FZ20" s="5"/>
+      <c r="GD20" s="5"/>
+      <c r="GH20" s="5"/>
+      <c r="GL20" s="5"/>
+      <c r="GP20" s="5"/>
+      <c r="GT20" s="5"/>
+      <c r="GX20" s="5"/>
+      <c r="HB20" s="5"/>
+      <c r="HF20" s="5"/>
+      <c r="HJ20" s="5"/>
+      <c r="HN20" s="5"/>
+      <c r="HR20" s="5"/>
+      <c r="HV20" s="5"/>
+      <c r="HZ20" s="5"/>
+      <c r="ID20" s="5"/>
+      <c r="IH20" s="5"/>
+      <c r="IL20" s="5"/>
+      <c r="IP20" s="5"/>
+      <c r="IT20" s="5"/>
+      <c r="IX20" s="5"/>
+      <c r="JB20" s="5"/>
+      <c r="JF20" s="5"/>
+      <c r="JJ20" s="5"/>
+      <c r="JN20" s="5"/>
+      <c r="JR20" s="5"/>
+      <c r="JV20" s="5"/>
+      <c r="JZ20" s="5"/>
+      <c r="KD20" s="5"/>
+      <c r="KH20" s="5"/>
+      <c r="KL20" s="5"/>
+      <c r="KP20" s="5"/>
+      <c r="KT20" s="5"/>
+      <c r="KX20" s="5"/>
+      <c r="LB20" s="5"/>
+      <c r="LF20" s="5"/>
+      <c r="LJ20" s="5"/>
+      <c r="LN20" s="5"/>
+      <c r="LR20" s="5"/>
+      <c r="LV20" s="5"/>
+      <c r="LZ20" s="5"/>
+      <c r="MD20" s="5"/>
+      <c r="MH20" s="5"/>
+      <c r="ML20" s="5"/>
+      <c r="MP20" s="5"/>
+      <c r="MT20" s="5"/>
+      <c r="MX20" s="5"/>
+      <c r="NB20" s="5"/>
+      <c r="NF20" s="5"/>
+      <c r="NJ20" s="5"/>
+      <c r="NN20" s="5"/>
+      <c r="NR20" s="5"/>
+      <c r="NV20" s="5"/>
+      <c r="NZ20" s="5"/>
+      <c r="OD20" s="5"/>
+      <c r="OH20" s="5"/>
+      <c r="OL20" s="5"/>
+      <c r="OP20" s="5"/>
+      <c r="OT20" s="5"/>
+      <c r="OX20" s="5"/>
+      <c r="PB20" s="5"/>
+      <c r="PF20" s="5"/>
+      <c r="PJ20" s="5"/>
+      <c r="PN20" s="5"/>
+      <c r="PR20" s="5"/>
+      <c r="PV20" s="5"/>
+      <c r="PZ20" s="5"/>
+      <c r="QD20" s="5"/>
+      <c r="QH20" s="5"/>
+      <c r="QL20" s="5"/>
+      <c r="QP20" s="5"/>
+      <c r="QT20" s="5"/>
+      <c r="QX20" s="5"/>
+      <c r="RB20" s="5"/>
+      <c r="RF20" s="5"/>
+      <c r="RJ20" s="5"/>
+      <c r="RN20" s="5"/>
+      <c r="RR20" s="5"/>
+      <c r="RV20" s="5"/>
+      <c r="RZ20" s="5"/>
+      <c r="SD20" s="5"/>
+      <c r="SH20" s="5"/>
+      <c r="SL20" s="5"/>
+      <c r="SP20" s="5"/>
+      <c r="ST20" s="5"/>
+      <c r="SX20" s="5"/>
+      <c r="TB20" s="5"/>
+      <c r="TF20" s="5"/>
+      <c r="TJ20" s="5"/>
+      <c r="TN20" s="5"/>
+      <c r="TR20" s="5"/>
+      <c r="TV20" s="5"/>
+      <c r="TZ20" s="5"/>
+      <c r="UD20" s="5"/>
+      <c r="UH20" s="5"/>
+      <c r="UL20" s="5"/>
+      <c r="UP20" s="5"/>
+      <c r="UT20" s="5"/>
+      <c r="UX20" s="5"/>
+      <c r="VB20" s="5"/>
+      <c r="VF20" s="5"/>
+      <c r="VJ20" s="5"/>
+      <c r="VN20" s="5"/>
+      <c r="VR20" s="5"/>
+      <c r="VV20" s="5"/>
+      <c r="VZ20" s="5"/>
+      <c r="WD20" s="5"/>
+      <c r="WH20" s="5"/>
+      <c r="WL20" s="5"/>
+      <c r="WP20" s="5"/>
+      <c r="WT20" s="5"/>
+      <c r="WX20" s="5"/>
+      <c r="XB20" s="5"/>
+      <c r="XF20" s="5"/>
+      <c r="XJ20" s="5"/>
+      <c r="XN20" s="5"/>
+      <c r="XR20" s="5"/>
+      <c r="XV20" s="5"/>
+      <c r="XZ20" s="5"/>
+      <c r="YD20" s="5"/>
+      <c r="YH20" s="5"/>
+      <c r="YL20" s="5"/>
+      <c r="YP20" s="5"/>
+      <c r="YT20" s="5"/>
+      <c r="YX20" s="5"/>
+      <c r="ZB20" s="5"/>
+      <c r="ZF20" s="5"/>
+      <c r="ZJ20" s="5"/>
+      <c r="ZN20" s="5"/>
+      <c r="ZR20" s="5"/>
+      <c r="ZV20" s="5"/>
+      <c r="ZZ20" s="5"/>
+      <c r="AAD20" s="5"/>
+      <c r="AAH20" s="5"/>
+      <c r="AAL20" s="5"/>
+      <c r="AAP20" s="5"/>
+      <c r="AAT20" s="5"/>
+      <c r="AAX20" s="5"/>
+      <c r="ABB20" s="5"/>
+      <c r="ABF20" s="5"/>
+      <c r="ABJ20" s="5"/>
+      <c r="ABN20" s="5"/>
+      <c r="ABR20" s="5"/>
+      <c r="ABV20" s="5"/>
+      <c r="ABZ20" s="5"/>
+      <c r="ACD20" s="5"/>
+      <c r="ACH20" s="5"/>
+      <c r="ACL20" s="5"/>
+      <c r="ACP20" s="5"/>
+      <c r="ACT20" s="5"/>
+      <c r="ACX20" s="5"/>
+      <c r="ADB20" s="5"/>
+      <c r="ADF20" s="5"/>
+      <c r="ADJ20" s="5"/>
+      <c r="ADN20" s="5"/>
+      <c r="ADR20" s="5"/>
+      <c r="ADV20" s="5"/>
+      <c r="ADZ20" s="5"/>
+      <c r="AED20" s="5"/>
+      <c r="AEH20" s="5"/>
+      <c r="AEL20" s="5"/>
+      <c r="AEP20" s="5"/>
+      <c r="AET20" s="5"/>
+      <c r="AEX20" s="5"/>
+      <c r="AFB20" s="5"/>
+      <c r="AFF20" s="5"/>
+      <c r="AFJ20" s="5"/>
+      <c r="AFN20" s="5"/>
+      <c r="AFR20" s="5"/>
+      <c r="AFV20" s="5"/>
+      <c r="AFZ20" s="5"/>
+      <c r="AGD20" s="5"/>
+      <c r="AGH20" s="5"/>
+      <c r="AGL20" s="5"/>
+      <c r="AGP20" s="5"/>
+      <c r="AGT20" s="5"/>
+      <c r="AGX20" s="5"/>
+      <c r="AHB20" s="5"/>
+      <c r="AHF20" s="5"/>
+      <c r="AHJ20" s="5"/>
+      <c r="AHN20" s="5"/>
+      <c r="AHR20" s="5"/>
+      <c r="AHV20" s="5"/>
+      <c r="AHZ20" s="5"/>
+      <c r="AID20" s="5"/>
+      <c r="AIH20" s="5"/>
+      <c r="AIL20" s="5"/>
+      <c r="AIP20" s="5"/>
+      <c r="AIT20" s="5"/>
+      <c r="AIX20" s="5"/>
+      <c r="AJB20" s="5"/>
+      <c r="AJF20" s="5"/>
+      <c r="AJJ20" s="5"/>
+      <c r="AJN20" s="5"/>
+      <c r="AJR20" s="5"/>
+      <c r="AJV20" s="5"/>
+      <c r="AJZ20" s="5"/>
+      <c r="AKD20" s="5"/>
+      <c r="AKH20" s="5"/>
+      <c r="AKL20" s="5"/>
+      <c r="AKP20" s="5"/>
+      <c r="AKT20" s="5"/>
+      <c r="AKX20" s="5"/>
+      <c r="ALB20" s="5"/>
+      <c r="ALF20" s="5"/>
+      <c r="ALJ20" s="5"/>
+      <c r="ALN20" s="5"/>
+      <c r="ALR20" s="5"/>
+      <c r="ALV20" s="5"/>
+      <c r="ALZ20" s="5"/>
+      <c r="AMD20" s="5"/>
+      <c r="AMH20" s="5"/>
+      <c r="AML20" s="5"/>
+      <c r="AMP20" s="5"/>
+      <c r="AMT20" s="5"/>
+      <c r="AMX20" s="5"/>
+      <c r="ANB20" s="5"/>
+      <c r="ANF20" s="5"/>
+      <c r="ANJ20" s="5"/>
+      <c r="ANN20" s="5"/>
+      <c r="ANR20" s="5"/>
+      <c r="ANV20" s="5"/>
+      <c r="ANZ20" s="5"/>
+      <c r="AOD20" s="5"/>
+      <c r="AOH20" s="5"/>
+      <c r="AOL20" s="5"/>
+      <c r="AOP20" s="5"/>
+      <c r="AOT20" s="5"/>
+      <c r="AOX20" s="5"/>
+      <c r="APB20" s="5"/>
+      <c r="APF20" s="5"/>
+      <c r="APJ20" s="5"/>
+      <c r="APN20" s="5"/>
+      <c r="APR20" s="5"/>
+      <c r="APV20" s="5"/>
+      <c r="APZ20" s="5"/>
+      <c r="AQD20" s="5"/>
+      <c r="AQH20" s="5"/>
+      <c r="AQL20" s="5"/>
+      <c r="AQP20" s="5"/>
+      <c r="AQT20" s="5"/>
+      <c r="AQX20" s="5"/>
+      <c r="ARB20" s="5"/>
+      <c r="ARF20" s="5"/>
+      <c r="ARJ20" s="5"/>
+      <c r="ARN20" s="5"/>
+      <c r="ARR20" s="5"/>
+      <c r="ARV20" s="5"/>
+      <c r="ARZ20" s="5"/>
+      <c r="ASD20" s="5"/>
+      <c r="ASH20" s="5"/>
+      <c r="ASL20" s="5"/>
+      <c r="ASP20" s="5"/>
+      <c r="AST20" s="5"/>
+      <c r="ASX20" s="5"/>
+      <c r="ATB20" s="5"/>
+      <c r="ATF20" s="5"/>
+      <c r="ATJ20" s="5"/>
+      <c r="ATN20" s="5"/>
+      <c r="ATR20" s="5"/>
+      <c r="ATV20" s="5"/>
+      <c r="ATZ20" s="5"/>
+      <c r="AUD20" s="5"/>
+      <c r="AUH20" s="5"/>
+      <c r="AUL20" s="5"/>
+      <c r="AUP20" s="5"/>
+      <c r="AUT20" s="5"/>
+      <c r="AUX20" s="5"/>
+      <c r="AVB20" s="5"/>
+      <c r="AVF20" s="5"/>
+      <c r="AVJ20" s="5"/>
+      <c r="AVN20" s="5"/>
+      <c r="AVR20" s="5"/>
+      <c r="AVV20" s="5"/>
+      <c r="AVZ20" s="5"/>
+      <c r="AWD20" s="5"/>
+      <c r="AWH20" s="5"/>
+      <c r="AWL20" s="5"/>
+      <c r="AWP20" s="5"/>
+      <c r="AWT20" s="5"/>
+      <c r="AWX20" s="5"/>
+      <c r="AXB20" s="5"/>
+      <c r="AXF20" s="5"/>
+      <c r="AXJ20" s="5"/>
+      <c r="AXN20" s="5"/>
+      <c r="AXR20" s="5"/>
+      <c r="AXV20" s="5"/>
+      <c r="AXZ20" s="5"/>
+      <c r="AYD20" s="5"/>
+      <c r="AYH20" s="5"/>
+      <c r="AYL20" s="5"/>
+      <c r="AYP20" s="5"/>
+      <c r="AYT20" s="5"/>
+      <c r="AYX20" s="5"/>
+      <c r="AZB20" s="5"/>
+      <c r="AZF20" s="5"/>
+      <c r="AZJ20" s="5"/>
+      <c r="AZN20" s="5"/>
+      <c r="AZR20" s="5"/>
+      <c r="AZV20" s="5"/>
+      <c r="AZZ20" s="5"/>
+      <c r="BAD20" s="5"/>
+      <c r="BAH20" s="5"/>
+      <c r="BAL20" s="5"/>
+      <c r="BAP20" s="5"/>
+      <c r="BAT20" s="5"/>
+      <c r="BAX20" s="5"/>
+      <c r="BBB20" s="5"/>
+      <c r="BBF20" s="5"/>
+      <c r="BBJ20" s="5"/>
+      <c r="BBN20" s="5"/>
+      <c r="BBR20" s="5"/>
+      <c r="BBV20" s="5"/>
+      <c r="BBZ20" s="5"/>
+      <c r="BCD20" s="5"/>
+      <c r="BCH20" s="5"/>
+      <c r="BCL20" s="5"/>
+      <c r="BCP20" s="5"/>
+      <c r="BCT20" s="5"/>
+      <c r="BCX20" s="5"/>
+      <c r="BDB20" s="5"/>
+      <c r="BDF20" s="5"/>
+      <c r="BDJ20" s="5"/>
+      <c r="BDN20" s="5"/>
+      <c r="BDR20" s="5"/>
+      <c r="BDV20" s="5"/>
+      <c r="BDZ20" s="5"/>
+      <c r="BED20" s="5"/>
+      <c r="BEH20" s="5"/>
+      <c r="BEL20" s="5"/>
+      <c r="BEP20" s="5"/>
+      <c r="BET20" s="5"/>
+      <c r="BEX20" s="5"/>
+      <c r="BFB20" s="5"/>
+      <c r="BFF20" s="5"/>
+      <c r="BFJ20" s="5"/>
+      <c r="BFN20" s="5"/>
+      <c r="BFR20" s="5"/>
+      <c r="BFV20" s="5"/>
+      <c r="BFZ20" s="5"/>
+      <c r="BGD20" s="5"/>
+      <c r="BGH20" s="5"/>
+      <c r="BGL20" s="5"/>
+      <c r="BGP20" s="5"/>
+      <c r="BGT20" s="5"/>
+      <c r="BGX20" s="5"/>
+      <c r="BHB20" s="5"/>
+      <c r="BHF20" s="5"/>
+      <c r="BHJ20" s="5"/>
+      <c r="BHN20" s="5"/>
+      <c r="BHR20" s="5"/>
+      <c r="BHV20" s="5"/>
+      <c r="BHZ20" s="5"/>
+      <c r="BID20" s="5"/>
+      <c r="BIH20" s="5"/>
+      <c r="BIL20" s="5"/>
+      <c r="BIP20" s="5"/>
+      <c r="BIT20" s="5"/>
+      <c r="BIX20" s="5"/>
+      <c r="BJB20" s="5"/>
+      <c r="BJF20" s="5"/>
+      <c r="BJJ20" s="5"/>
+      <c r="BJN20" s="5"/>
+      <c r="BJR20" s="5"/>
+      <c r="BJV20" s="5"/>
+      <c r="BJZ20" s="5"/>
+      <c r="BKD20" s="5"/>
+      <c r="BKH20" s="5"/>
+      <c r="BKL20" s="5"/>
+      <c r="BKP20" s="5"/>
+      <c r="BKT20" s="5"/>
+      <c r="BKX20" s="5"/>
+      <c r="BLB20" s="5"/>
+      <c r="BLF20" s="5"/>
+      <c r="BLJ20" s="5"/>
+      <c r="BLN20" s="5"/>
+      <c r="BLR20" s="5"/>
+      <c r="BLV20" s="5"/>
+      <c r="BLZ20" s="5"/>
+      <c r="BMD20" s="5"/>
+      <c r="BMH20" s="5"/>
+      <c r="BML20" s="5"/>
+      <c r="BMP20" s="5"/>
+      <c r="BMT20" s="5"/>
+      <c r="BMX20" s="5"/>
+      <c r="BNB20" s="5"/>
+      <c r="BNF20" s="5"/>
+      <c r="BNJ20" s="5"/>
+      <c r="BNN20" s="5"/>
+      <c r="BNR20" s="5"/>
+      <c r="BNV20" s="5"/>
+      <c r="BNZ20" s="5"/>
+      <c r="BOD20" s="5"/>
+      <c r="BOH20" s="5"/>
+      <c r="BOL20" s="5"/>
+      <c r="BOP20" s="5"/>
+      <c r="BOT20" s="5"/>
+      <c r="BOX20" s="5"/>
+      <c r="BPB20" s="5"/>
+      <c r="BPF20" s="5"/>
+      <c r="BPJ20" s="5"/>
+      <c r="BPN20" s="5"/>
+      <c r="BPR20" s="5"/>
+      <c r="BPV20" s="5"/>
+      <c r="BPZ20" s="5"/>
+      <c r="BQD20" s="5"/>
+      <c r="BQH20" s="5"/>
+      <c r="BQL20" s="5"/>
+      <c r="BQP20" s="5"/>
+      <c r="BQT20" s="5"/>
+      <c r="BQX20" s="5"/>
+      <c r="BRB20" s="5"/>
+      <c r="BRF20" s="5"/>
+      <c r="BRJ20" s="5"/>
+      <c r="BRN20" s="5"/>
+      <c r="BRR20" s="5"/>
+      <c r="BRV20" s="5"/>
+      <c r="BRZ20" s="5"/>
+      <c r="BSD20" s="5"/>
+      <c r="BSH20" s="5"/>
+      <c r="BSL20" s="5"/>
+      <c r="BSP20" s="5"/>
+      <c r="BST20" s="5"/>
+      <c r="BSX20" s="5"/>
+      <c r="BTB20" s="5"/>
+      <c r="BTF20" s="5"/>
+      <c r="BTJ20" s="5"/>
+      <c r="BTN20" s="5"/>
+      <c r="BTR20" s="5"/>
+      <c r="BTV20" s="5"/>
+      <c r="BTZ20" s="5"/>
+      <c r="BUD20" s="5"/>
+      <c r="BUH20" s="5"/>
+      <c r="BUL20" s="5"/>
+      <c r="BUP20" s="5"/>
+      <c r="BUT20" s="5"/>
+      <c r="BUX20" s="5"/>
+      <c r="BVB20" s="5"/>
+      <c r="BVF20" s="5"/>
+      <c r="BVJ20" s="5"/>
+      <c r="BVN20" s="5"/>
+      <c r="BVR20" s="5"/>
+      <c r="BVV20" s="5"/>
+      <c r="BVZ20" s="5"/>
+      <c r="BWD20" s="5"/>
+      <c r="BWH20" s="5"/>
+      <c r="BWL20" s="5"/>
+      <c r="BWP20" s="5"/>
+      <c r="BWT20" s="5"/>
+      <c r="BWX20" s="5"/>
+      <c r="BXB20" s="5"/>
+      <c r="BXF20" s="5"/>
+      <c r="BXJ20" s="5"/>
+      <c r="BXN20" s="5"/>
+      <c r="BXR20" s="5"/>
+      <c r="BXV20" s="5"/>
+      <c r="BXZ20" s="5"/>
+      <c r="BYD20" s="5"/>
+      <c r="BYH20" s="5"/>
+      <c r="BYL20" s="5"/>
+      <c r="BYP20" s="5"/>
+      <c r="BYT20" s="5"/>
+      <c r="BYX20" s="5"/>
+      <c r="BZB20" s="5"/>
+      <c r="BZF20" s="5"/>
+      <c r="BZJ20" s="5"/>
+      <c r="BZN20" s="5"/>
+      <c r="BZR20" s="5"/>
+      <c r="BZV20" s="5"/>
+      <c r="BZZ20" s="5"/>
+      <c r="CAD20" s="5"/>
+      <c r="CAH20" s="5"/>
+      <c r="CAL20" s="5"/>
+      <c r="CAP20" s="5"/>
+      <c r="CAT20" s="5"/>
+      <c r="CAX20" s="5"/>
+      <c r="CBB20" s="5"/>
+      <c r="CBF20" s="5"/>
+      <c r="CBJ20" s="5"/>
+      <c r="CBN20" s="5"/>
+      <c r="CBR20" s="5"/>
+      <c r="CBV20" s="5"/>
+      <c r="CBZ20" s="5"/>
+      <c r="CCD20" s="5"/>
+      <c r="CCH20" s="5"/>
+      <c r="CCL20" s="5"/>
+      <c r="CCP20" s="5"/>
+      <c r="CCT20" s="5"/>
+      <c r="CCX20" s="5"/>
+      <c r="CDB20" s="5"/>
+      <c r="CDF20" s="5"/>
+      <c r="CDJ20" s="5"/>
+      <c r="CDN20" s="5"/>
+      <c r="CDR20" s="5"/>
+      <c r="CDV20" s="5"/>
+      <c r="CDZ20" s="5"/>
+      <c r="CED20" s="5"/>
+      <c r="CEH20" s="5"/>
+      <c r="CEL20" s="5"/>
+      <c r="CEP20" s="5"/>
+      <c r="CET20" s="5"/>
+      <c r="CEX20" s="5"/>
+      <c r="CFB20" s="5"/>
+      <c r="CFF20" s="5"/>
+      <c r="CFJ20" s="5"/>
+      <c r="CFN20" s="5"/>
+      <c r="CFR20" s="5"/>
+      <c r="CFV20" s="5"/>
+      <c r="CFZ20" s="5"/>
+      <c r="CGD20" s="5"/>
+      <c r="CGH20" s="5"/>
+      <c r="CGL20" s="5"/>
+      <c r="CGP20" s="5"/>
+      <c r="CGT20" s="5"/>
+      <c r="CGX20" s="5"/>
+      <c r="CHB20" s="5"/>
+      <c r="CHF20" s="5"/>
+      <c r="CHJ20" s="5"/>
+      <c r="CHN20" s="5"/>
+      <c r="CHR20" s="5"/>
+      <c r="CHV20" s="5"/>
+      <c r="CHZ20" s="5"/>
+      <c r="CID20" s="5"/>
+      <c r="CIH20" s="5"/>
+      <c r="CIL20" s="5"/>
+      <c r="CIP20" s="5"/>
+      <c r="CIT20" s="5"/>
+      <c r="CIX20" s="5"/>
+      <c r="CJB20" s="5"/>
+      <c r="CJF20" s="5"/>
+      <c r="CJJ20" s="5"/>
+      <c r="CJN20" s="5"/>
+      <c r="CJR20" s="5"/>
+      <c r="CJV20" s="5"/>
+      <c r="CJZ20" s="5"/>
+      <c r="CKD20" s="5"/>
+      <c r="CKH20" s="5"/>
+      <c r="CKL20" s="5"/>
+      <c r="CKP20" s="5"/>
+      <c r="CKT20" s="5"/>
+      <c r="CKX20" s="5"/>
+      <c r="CLB20" s="5"/>
+      <c r="CLF20" s="5"/>
+      <c r="CLJ20" s="5"/>
+      <c r="CLN20" s="5"/>
+      <c r="CLR20" s="5"/>
+      <c r="CLV20" s="5"/>
+      <c r="CLZ20" s="5"/>
+      <c r="CMD20" s="5"/>
+      <c r="CMH20" s="5"/>
+      <c r="CML20" s="5"/>
+      <c r="CMP20" s="5"/>
+      <c r="CMT20" s="5"/>
+      <c r="CMX20" s="5"/>
+      <c r="CNB20" s="5"/>
+      <c r="CNF20" s="5"/>
+      <c r="CNJ20" s="5"/>
+      <c r="CNN20" s="5"/>
+      <c r="CNR20" s="5"/>
+      <c r="CNV20" s="5"/>
+      <c r="CNZ20" s="5"/>
+      <c r="COD20" s="5"/>
+      <c r="COH20" s="5"/>
+      <c r="COL20" s="5"/>
+      <c r="COP20" s="5"/>
+      <c r="COT20" s="5"/>
+      <c r="COX20" s="5"/>
+      <c r="CPB20" s="5"/>
+      <c r="CPF20" s="5"/>
+      <c r="CPJ20" s="5"/>
+      <c r="CPN20" s="5"/>
+      <c r="CPR20" s="5"/>
+      <c r="CPV20" s="5"/>
+      <c r="CPZ20" s="5"/>
+      <c r="CQD20" s="5"/>
+      <c r="CQH20" s="5"/>
+      <c r="CQL20" s="5"/>
+      <c r="CQP20" s="5"/>
+      <c r="CQT20" s="5"/>
+      <c r="CQX20" s="5"/>
+      <c r="CRB20" s="5"/>
+      <c r="CRF20" s="5"/>
+      <c r="CRJ20" s="5"/>
+      <c r="CRN20" s="5"/>
+      <c r="CRR20" s="5"/>
+      <c r="CRV20" s="5"/>
+      <c r="CRZ20" s="5"/>
+      <c r="CSD20" s="5"/>
+      <c r="CSH20" s="5"/>
+      <c r="CSL20" s="5"/>
+      <c r="CSP20" s="5"/>
+      <c r="CST20" s="5"/>
+      <c r="CSX20" s="5"/>
+      <c r="CTB20" s="5"/>
+      <c r="CTF20" s="5"/>
+      <c r="CTJ20" s="5"/>
+      <c r="CTN20" s="5"/>
+      <c r="CTR20" s="5"/>
+      <c r="CTV20" s="5"/>
+      <c r="CTZ20" s="5"/>
+      <c r="CUD20" s="5"/>
+      <c r="CUH20" s="5"/>
+      <c r="CUL20" s="5"/>
+      <c r="CUP20" s="5"/>
+      <c r="CUT20" s="5"/>
+      <c r="CUX20" s="5"/>
+      <c r="CVB20" s="5"/>
+      <c r="CVF20" s="5"/>
+      <c r="CVJ20" s="5"/>
+      <c r="CVN20" s="5"/>
+      <c r="CVR20" s="5"/>
+      <c r="CVV20" s="5"/>
+      <c r="CVZ20" s="5"/>
+      <c r="CWD20" s="5"/>
+      <c r="CWH20" s="5"/>
+      <c r="CWL20" s="5"/>
+      <c r="CWP20" s="5"/>
+      <c r="CWT20" s="5"/>
+      <c r="CWX20" s="5"/>
+      <c r="CXB20" s="5"/>
+      <c r="CXF20" s="5"/>
+      <c r="CXJ20" s="5"/>
+      <c r="CXN20" s="5"/>
+      <c r="CXR20" s="5"/>
+      <c r="CXV20" s="5"/>
+      <c r="CXZ20" s="5"/>
+      <c r="CYD20" s="5"/>
+      <c r="CYH20" s="5"/>
+      <c r="CYL20" s="5"/>
+      <c r="CYP20" s="5"/>
+      <c r="CYT20" s="5"/>
+      <c r="CYX20" s="5"/>
+      <c r="CZB20" s="5"/>
+      <c r="CZF20" s="5"/>
+      <c r="CZJ20" s="5"/>
+      <c r="CZN20" s="5"/>
+      <c r="CZR20" s="5"/>
+      <c r="CZV20" s="5"/>
+      <c r="CZZ20" s="5"/>
+      <c r="DAD20" s="5"/>
+      <c r="DAH20" s="5"/>
+      <c r="DAL20" s="5"/>
+      <c r="DAP20" s="5"/>
+      <c r="DAT20" s="5"/>
+      <c r="DAX20" s="5"/>
+      <c r="DBB20" s="5"/>
+      <c r="DBF20" s="5"/>
+      <c r="DBJ20" s="5"/>
+      <c r="DBN20" s="5"/>
+      <c r="DBR20" s="5"/>
+      <c r="DBV20" s="5"/>
+      <c r="DBZ20" s="5"/>
+      <c r="DCD20" s="5"/>
+      <c r="DCH20" s="5"/>
+      <c r="DCL20" s="5"/>
+      <c r="DCP20" s="5"/>
+      <c r="DCT20" s="5"/>
+      <c r="DCX20" s="5"/>
+      <c r="DDB20" s="5"/>
+      <c r="DDF20" s="5"/>
+      <c r="DDJ20" s="5"/>
+      <c r="DDN20" s="5"/>
+      <c r="DDR20" s="5"/>
+      <c r="DDV20" s="5"/>
+      <c r="DDZ20" s="5"/>
+      <c r="DED20" s="5"/>
+      <c r="DEH20" s="5"/>
+      <c r="DEL20" s="5"/>
+      <c r="DEP20" s="5"/>
+      <c r="DET20" s="5"/>
+      <c r="DEX20" s="5"/>
+      <c r="DFB20" s="5"/>
+      <c r="DFF20" s="5"/>
+      <c r="DFJ20" s="5"/>
+      <c r="DFN20" s="5"/>
+      <c r="DFR20" s="5"/>
+      <c r="DFV20" s="5"/>
+      <c r="DFZ20" s="5"/>
+      <c r="DGD20" s="5"/>
+      <c r="DGH20" s="5"/>
+      <c r="DGL20" s="5"/>
+      <c r="DGP20" s="5"/>
+      <c r="DGT20" s="5"/>
+      <c r="DGX20" s="5"/>
+      <c r="DHB20" s="5"/>
+      <c r="DHF20" s="5"/>
+      <c r="DHJ20" s="5"/>
+      <c r="DHN20" s="5"/>
+      <c r="DHR20" s="5"/>
+      <c r="DHV20" s="5"/>
+      <c r="DHZ20" s="5"/>
+      <c r="DID20" s="5"/>
+      <c r="DIH20" s="5"/>
+      <c r="DIL20" s="5"/>
+      <c r="DIP20" s="5"/>
+      <c r="DIT20" s="5"/>
+      <c r="DIX20" s="5"/>
+      <c r="DJB20" s="5"/>
+      <c r="DJF20" s="5"/>
+      <c r="DJJ20" s="5"/>
+      <c r="DJN20" s="5"/>
+      <c r="DJR20" s="5"/>
+      <c r="DJV20" s="5"/>
+      <c r="DJZ20" s="5"/>
+      <c r="DKD20" s="5"/>
+      <c r="DKH20" s="5"/>
+      <c r="DKL20" s="5"/>
+      <c r="DKP20" s="5"/>
+      <c r="DKT20" s="5"/>
+      <c r="DKX20" s="5"/>
+      <c r="DLB20" s="5"/>
+      <c r="DLF20" s="5"/>
+      <c r="DLJ20" s="5"/>
+      <c r="DLN20" s="5"/>
+      <c r="DLR20" s="5"/>
+      <c r="DLV20" s="5"/>
+      <c r="DLZ20" s="5"/>
+      <c r="DMD20" s="5"/>
+      <c r="DMH20" s="5"/>
+      <c r="DML20" s="5"/>
+      <c r="DMP20" s="5"/>
+      <c r="DMT20" s="5"/>
+      <c r="DMX20" s="5"/>
+      <c r="DNB20" s="5"/>
+      <c r="DNF20" s="5"/>
+      <c r="DNJ20" s="5"/>
+      <c r="DNN20" s="5"/>
+      <c r="DNR20" s="5"/>
+      <c r="DNV20" s="5"/>
+      <c r="DNZ20" s="5"/>
+      <c r="DOD20" s="5"/>
+      <c r="DOH20" s="5"/>
+      <c r="DOL20" s="5"/>
+      <c r="DOP20" s="5"/>
+      <c r="DOT20" s="5"/>
+      <c r="DOX20" s="5"/>
+      <c r="DPB20" s="5"/>
+      <c r="DPF20" s="5"/>
+      <c r="DPJ20" s="5"/>
+      <c r="DPN20" s="5"/>
+      <c r="DPR20" s="5"/>
+      <c r="DPV20" s="5"/>
+      <c r="DPZ20" s="5"/>
+      <c r="DQD20" s="5"/>
+      <c r="DQH20" s="5"/>
+      <c r="DQL20" s="5"/>
+      <c r="DQP20" s="5"/>
+      <c r="DQT20" s="5"/>
+      <c r="DQX20" s="5"/>
+      <c r="DRB20" s="5"/>
+      <c r="DRF20" s="5"/>
+      <c r="DRJ20" s="5"/>
+      <c r="DRN20" s="5"/>
+      <c r="DRR20" s="5"/>
+      <c r="DRV20" s="5"/>
+      <c r="DRZ20" s="5"/>
+      <c r="DSD20" s="5"/>
+      <c r="DSH20" s="5"/>
+      <c r="DSL20" s="5"/>
+      <c r="DSP20" s="5"/>
+      <c r="DST20" s="5"/>
+      <c r="DSX20" s="5"/>
+      <c r="DTB20" s="5"/>
+      <c r="DTF20" s="5"/>
+      <c r="DTJ20" s="5"/>
+      <c r="DTN20" s="5"/>
+      <c r="DTR20" s="5"/>
+      <c r="DTV20" s="5"/>
+      <c r="DTZ20" s="5"/>
+      <c r="DUD20" s="5"/>
+      <c r="DUH20" s="5"/>
+      <c r="DUL20" s="5"/>
+      <c r="DUP20" s="5"/>
+      <c r="DUT20" s="5"/>
+      <c r="DUX20" s="5"/>
+      <c r="DVB20" s="5"/>
+      <c r="DVF20" s="5"/>
+      <c r="DVJ20" s="5"/>
+      <c r="DVN20" s="5"/>
+      <c r="DVR20" s="5"/>
+      <c r="DVV20" s="5"/>
+      <c r="DVZ20" s="5"/>
+      <c r="DWD20" s="5"/>
+      <c r="DWH20" s="5"/>
+      <c r="DWL20" s="5"/>
+      <c r="DWP20" s="5"/>
+      <c r="DWT20" s="5"/>
+      <c r="DWX20" s="5"/>
+      <c r="DXB20" s="5"/>
+      <c r="DXF20" s="5"/>
+      <c r="DXJ20" s="5"/>
+      <c r="DXN20" s="5"/>
+      <c r="DXR20" s="5"/>
+      <c r="DXV20" s="5"/>
+      <c r="DXZ20" s="5"/>
+      <c r="DYD20" s="5"/>
+      <c r="DYH20" s="5"/>
+      <c r="DYL20" s="5"/>
+      <c r="DYP20" s="5"/>
+      <c r="DYT20" s="5"/>
+      <c r="DYX20" s="5"/>
+      <c r="DZB20" s="5"/>
+      <c r="DZF20" s="5"/>
+      <c r="DZJ20" s="5"/>
+      <c r="DZN20" s="5"/>
+      <c r="DZR20" s="5"/>
+      <c r="DZV20" s="5"/>
+      <c r="DZZ20" s="5"/>
+      <c r="EAD20" s="5"/>
+      <c r="EAH20" s="5"/>
+      <c r="EAL20" s="5"/>
+      <c r="EAP20" s="5"/>
+      <c r="EAT20" s="5"/>
+      <c r="EAX20" s="5"/>
+      <c r="EBB20" s="5"/>
+      <c r="EBF20" s="5"/>
+      <c r="EBJ20" s="5"/>
+      <c r="EBN20" s="5"/>
+      <c r="EBR20" s="5"/>
+      <c r="EBV20" s="5"/>
+      <c r="EBZ20" s="5"/>
+      <c r="ECD20" s="5"/>
+      <c r="ECH20" s="5"/>
+      <c r="ECL20" s="5"/>
+      <c r="ECP20" s="5"/>
+      <c r="ECT20" s="5"/>
+      <c r="ECX20" s="5"/>
+      <c r="EDB20" s="5"/>
+      <c r="EDF20" s="5"/>
+      <c r="EDJ20" s="5"/>
+      <c r="EDN20" s="5"/>
+      <c r="EDR20" s="5"/>
+      <c r="EDV20" s="5"/>
+      <c r="EDZ20" s="5"/>
+      <c r="EED20" s="5"/>
+      <c r="EEH20" s="5"/>
+      <c r="EEL20" s="5"/>
+      <c r="EEP20" s="5"/>
+      <c r="EET20" s="5"/>
+      <c r="EEX20" s="5"/>
+      <c r="EFB20" s="5"/>
+      <c r="EFF20" s="5"/>
+      <c r="EFJ20" s="5"/>
+      <c r="EFN20" s="5"/>
+      <c r="EFR20" s="5"/>
+      <c r="EFV20" s="5"/>
+      <c r="EFZ20" s="5"/>
+      <c r="EGD20" s="5"/>
+      <c r="EGH20" s="5"/>
+      <c r="EGL20" s="5"/>
+      <c r="EGP20" s="5"/>
+      <c r="EGT20" s="5"/>
+      <c r="EGX20" s="5"/>
+      <c r="EHB20" s="5"/>
+      <c r="EHF20" s="5"/>
+      <c r="EHJ20" s="5"/>
+      <c r="EHN20" s="5"/>
+      <c r="EHR20" s="5"/>
+      <c r="EHV20" s="5"/>
+      <c r="EHZ20" s="5"/>
+      <c r="EID20" s="5"/>
+      <c r="EIH20" s="5"/>
+      <c r="EIL20" s="5"/>
+      <c r="EIP20" s="5"/>
+      <c r="EIT20" s="5"/>
+      <c r="EIX20" s="5"/>
+      <c r="EJB20" s="5"/>
+      <c r="EJF20" s="5"/>
+      <c r="EJJ20" s="5"/>
+      <c r="EJN20" s="5"/>
+      <c r="EJR20" s="5"/>
+      <c r="EJV20" s="5"/>
+      <c r="EJZ20" s="5"/>
+      <c r="EKD20" s="5"/>
+      <c r="EKH20" s="5"/>
+      <c r="EKL20" s="5"/>
+      <c r="EKP20" s="5"/>
+      <c r="EKT20" s="5"/>
+      <c r="EKX20" s="5"/>
+      <c r="ELB20" s="5"/>
+      <c r="ELF20" s="5"/>
+      <c r="ELJ20" s="5"/>
+      <c r="ELN20" s="5"/>
+      <c r="ELR20" s="5"/>
+      <c r="ELV20" s="5"/>
+      <c r="ELZ20" s="5"/>
+      <c r="EMD20" s="5"/>
+      <c r="EMH20" s="5"/>
+      <c r="EML20" s="5"/>
+      <c r="EMP20" s="5"/>
+      <c r="EMT20" s="5"/>
+      <c r="EMX20" s="5"/>
+      <c r="ENB20" s="5"/>
+      <c r="ENF20" s="5"/>
+      <c r="ENJ20" s="5"/>
+      <c r="ENN20" s="5"/>
+      <c r="ENR20" s="5"/>
+      <c r="ENV20" s="5"/>
+      <c r="ENZ20" s="5"/>
+      <c r="EOD20" s="5"/>
+      <c r="EOH20" s="5"/>
+      <c r="EOL20" s="5"/>
+      <c r="EOP20" s="5"/>
+      <c r="EOT20" s="5"/>
+      <c r="EOX20" s="5"/>
+      <c r="EPB20" s="5"/>
+      <c r="EPF20" s="5"/>
+      <c r="EPJ20" s="5"/>
+      <c r="EPN20" s="5"/>
+      <c r="EPR20" s="5"/>
+      <c r="EPV20" s="5"/>
+      <c r="EPZ20" s="5"/>
+      <c r="EQD20" s="5"/>
+      <c r="EQH20" s="5"/>
+      <c r="EQL20" s="5"/>
+      <c r="EQP20" s="5"/>
+      <c r="EQT20" s="5"/>
+      <c r="EQX20" s="5"/>
+      <c r="ERB20" s="5"/>
+      <c r="ERF20" s="5"/>
+      <c r="ERJ20" s="5"/>
+      <c r="ERN20" s="5"/>
+      <c r="ERR20" s="5"/>
+      <c r="ERV20" s="5"/>
+      <c r="ERZ20" s="5"/>
+      <c r="ESD20" s="5"/>
+      <c r="ESH20" s="5"/>
+      <c r="ESL20" s="5"/>
+      <c r="ESP20" s="5"/>
+      <c r="EST20" s="5"/>
+      <c r="ESX20" s="5"/>
+      <c r="ETB20" s="5"/>
+      <c r="ETF20" s="5"/>
+      <c r="ETJ20" s="5"/>
+      <c r="ETN20" s="5"/>
+      <c r="ETR20" s="5"/>
+      <c r="ETV20" s="5"/>
+      <c r="ETZ20" s="5"/>
+      <c r="EUD20" s="5"/>
+      <c r="EUH20" s="5"/>
+      <c r="EUL20" s="5"/>
+      <c r="EUP20" s="5"/>
+      <c r="EUT20" s="5"/>
+      <c r="EUX20" s="5"/>
+      <c r="EVB20" s="5"/>
+      <c r="EVF20" s="5"/>
+      <c r="EVJ20" s="5"/>
+      <c r="EVN20" s="5"/>
+      <c r="EVR20" s="5"/>
+      <c r="EVV20" s="5"/>
+      <c r="EVZ20" s="5"/>
+      <c r="EWD20" s="5"/>
+      <c r="EWH20" s="5"/>
+      <c r="EWL20" s="5"/>
+      <c r="EWP20" s="5"/>
+      <c r="EWT20" s="5"/>
+      <c r="EWX20" s="5"/>
+      <c r="EXB20" s="5"/>
+      <c r="EXF20" s="5"/>
+      <c r="EXJ20" s="5"/>
+      <c r="EXN20" s="5"/>
+      <c r="EXR20" s="5"/>
+      <c r="EXV20" s="5"/>
+      <c r="EXZ20" s="5"/>
+      <c r="EYD20" s="5"/>
+      <c r="EYH20" s="5"/>
+      <c r="EYL20" s="5"/>
+      <c r="EYP20" s="5"/>
+      <c r="EYT20" s="5"/>
+      <c r="EYX20" s="5"/>
+      <c r="EZB20" s="5"/>
+      <c r="EZF20" s="5"/>
+      <c r="EZJ20" s="5"/>
+      <c r="EZN20" s="5"/>
+      <c r="EZR20" s="5"/>
+      <c r="EZV20" s="5"/>
+      <c r="EZZ20" s="5"/>
+      <c r="FAD20" s="5"/>
+      <c r="FAH20" s="5"/>
+      <c r="FAL20" s="5"/>
+      <c r="FAP20" s="5"/>
+      <c r="FAT20" s="5"/>
+      <c r="FAX20" s="5"/>
+      <c r="FBB20" s="5"/>
+      <c r="FBF20" s="5"/>
+      <c r="FBJ20" s="5"/>
+      <c r="FBN20" s="5"/>
+      <c r="FBR20" s="5"/>
+      <c r="FBV20" s="5"/>
+      <c r="FBZ20" s="5"/>
+      <c r="FCD20" s="5"/>
+      <c r="FCH20" s="5"/>
+      <c r="FCL20" s="5"/>
+      <c r="FCP20" s="5"/>
+      <c r="FCT20" s="5"/>
+      <c r="FCX20" s="5"/>
+      <c r="FDB20" s="5"/>
+      <c r="FDF20" s="5"/>
+      <c r="FDJ20" s="5"/>
+      <c r="FDN20" s="5"/>
+      <c r="FDR20" s="5"/>
+      <c r="FDV20" s="5"/>
+      <c r="FDZ20" s="5"/>
+      <c r="FED20" s="5"/>
+      <c r="FEH20" s="5"/>
+      <c r="FEL20" s="5"/>
+      <c r="FEP20" s="5"/>
+      <c r="FET20" s="5"/>
+      <c r="FEX20" s="5"/>
+      <c r="FFB20" s="5"/>
+      <c r="FFF20" s="5"/>
+      <c r="FFJ20" s="5"/>
+      <c r="FFN20" s="5"/>
+      <c r="FFR20" s="5"/>
+      <c r="FFV20" s="5"/>
+      <c r="FFZ20" s="5"/>
+      <c r="FGD20" s="5"/>
+      <c r="FGH20" s="5"/>
+      <c r="FGL20" s="5"/>
+      <c r="FGP20" s="5"/>
+      <c r="FGT20" s="5"/>
+      <c r="FGX20" s="5"/>
+      <c r="FHB20" s="5"/>
+      <c r="FHF20" s="5"/>
+      <c r="FHJ20" s="5"/>
+      <c r="FHN20" s="5"/>
+      <c r="FHR20" s="5"/>
+      <c r="FHV20" s="5"/>
+      <c r="FHZ20" s="5"/>
+      <c r="FID20" s="5"/>
+      <c r="FIH20" s="5"/>
+      <c r="FIL20" s="5"/>
+      <c r="FIP20" s="5"/>
+      <c r="FIT20" s="5"/>
+      <c r="FIX20" s="5"/>
+      <c r="FJB20" s="5"/>
+      <c r="FJF20" s="5"/>
+      <c r="FJJ20" s="5"/>
+      <c r="FJN20" s="5"/>
+      <c r="FJR20" s="5"/>
+      <c r="FJV20" s="5"/>
+      <c r="FJZ20" s="5"/>
+      <c r="FKD20" s="5"/>
+      <c r="FKH20" s="5"/>
+      <c r="FKL20" s="5"/>
+      <c r="FKP20" s="5"/>
+      <c r="FKT20" s="5"/>
+      <c r="FKX20" s="5"/>
+      <c r="FLB20" s="5"/>
+      <c r="FLF20" s="5"/>
+      <c r="FLJ20" s="5"/>
+      <c r="FLN20" s="5"/>
+      <c r="FLR20" s="5"/>
+      <c r="FLV20" s="5"/>
+      <c r="FLZ20" s="5"/>
+      <c r="FMD20" s="5"/>
+      <c r="FMH20" s="5"/>
+      <c r="FML20" s="5"/>
+      <c r="FMP20" s="5"/>
+      <c r="FMT20" s="5"/>
+      <c r="FMX20" s="5"/>
+      <c r="FNB20" s="5"/>
+      <c r="FNF20" s="5"/>
+      <c r="FNJ20" s="5"/>
+      <c r="FNN20" s="5"/>
+      <c r="FNR20" s="5"/>
+      <c r="FNV20" s="5"/>
+      <c r="FNZ20" s="5"/>
+      <c r="FOD20" s="5"/>
+      <c r="FOH20" s="5"/>
+      <c r="FOL20" s="5"/>
+      <c r="FOP20" s="5"/>
+      <c r="FOT20" s="5"/>
+      <c r="FOX20" s="5"/>
+      <c r="FPB20" s="5"/>
+      <c r="FPF20" s="5"/>
+      <c r="FPJ20" s="5"/>
+      <c r="FPN20" s="5"/>
+      <c r="FPR20" s="5"/>
+      <c r="FPV20" s="5"/>
+      <c r="FPZ20" s="5"/>
+      <c r="FQD20" s="5"/>
+      <c r="FQH20" s="5"/>
+      <c r="FQL20" s="5"/>
+      <c r="FQP20" s="5"/>
+      <c r="FQT20" s="5"/>
+      <c r="FQX20" s="5"/>
+      <c r="FRB20" s="5"/>
+      <c r="FRF20" s="5"/>
+      <c r="FRJ20" s="5"/>
+      <c r="FRN20" s="5"/>
+      <c r="FRR20" s="5"/>
+      <c r="FRV20" s="5"/>
+      <c r="FRZ20" s="5"/>
+      <c r="FSD20" s="5"/>
+      <c r="FSH20" s="5"/>
+      <c r="FSL20" s="5"/>
+      <c r="FSP20" s="5"/>
+      <c r="FST20" s="5"/>
+      <c r="FSX20" s="5"/>
+      <c r="FTB20" s="5"/>
+      <c r="FTF20" s="5"/>
+      <c r="FTJ20" s="5"/>
+      <c r="FTN20" s="5"/>
+      <c r="FTR20" s="5"/>
+      <c r="FTV20" s="5"/>
+      <c r="FTZ20" s="5"/>
+      <c r="FUD20" s="5"/>
+      <c r="FUH20" s="5"/>
+      <c r="FUL20" s="5"/>
+      <c r="FUP20" s="5"/>
+      <c r="FUT20" s="5"/>
+      <c r="FUX20" s="5"/>
+      <c r="FVB20" s="5"/>
+      <c r="FVF20" s="5"/>
+      <c r="FVJ20" s="5"/>
+      <c r="FVN20" s="5"/>
+      <c r="FVR20" s="5"/>
+      <c r="FVV20" s="5"/>
+      <c r="FVZ20" s="5"/>
+      <c r="FWD20" s="5"/>
+      <c r="FWH20" s="5"/>
+      <c r="FWL20" s="5"/>
+      <c r="FWP20" s="5"/>
+      <c r="FWT20" s="5"/>
+      <c r="FWX20" s="5"/>
+      <c r="FXB20" s="5"/>
+      <c r="FXF20" s="5"/>
+      <c r="FXJ20" s="5"/>
+      <c r="FXN20" s="5"/>
+      <c r="FXR20" s="5"/>
+      <c r="FXV20" s="5"/>
+      <c r="FXZ20" s="5"/>
+      <c r="FYD20" s="5"/>
+      <c r="FYH20" s="5"/>
+      <c r="FYL20" s="5"/>
+      <c r="FYP20" s="5"/>
+      <c r="FYT20" s="5"/>
+      <c r="FYX20" s="5"/>
+      <c r="FZB20" s="5"/>
+      <c r="FZF20" s="5"/>
+      <c r="FZJ20" s="5"/>
+      <c r="FZN20" s="5"/>
+      <c r="FZR20" s="5"/>
+      <c r="FZV20" s="5"/>
+      <c r="FZZ20" s="5"/>
+      <c r="GAD20" s="5"/>
+      <c r="GAH20" s="5"/>
+      <c r="GAL20" s="5"/>
+      <c r="GAP20" s="5"/>
+      <c r="GAT20" s="5"/>
+      <c r="GAX20" s="5"/>
+      <c r="GBB20" s="5"/>
+      <c r="GBF20" s="5"/>
+      <c r="GBJ20" s="5"/>
+      <c r="GBN20" s="5"/>
+      <c r="GBR20" s="5"/>
+      <c r="GBV20" s="5"/>
+      <c r="GBZ20" s="5"/>
+      <c r="GCD20" s="5"/>
+      <c r="GCH20" s="5"/>
+      <c r="GCL20" s="5"/>
+      <c r="GCP20" s="5"/>
+      <c r="GCT20" s="5"/>
+      <c r="GCX20" s="5"/>
+      <c r="GDB20" s="5"/>
+      <c r="GDF20" s="5"/>
+      <c r="GDJ20" s="5"/>
+      <c r="GDN20" s="5"/>
+      <c r="GDR20" s="5"/>
+      <c r="GDV20" s="5"/>
+      <c r="GDZ20" s="5"/>
+      <c r="GED20" s="5"/>
+      <c r="GEH20" s="5"/>
+      <c r="GEL20" s="5"/>
+      <c r="GEP20" s="5"/>
+      <c r="GET20" s="5"/>
+      <c r="GEX20" s="5"/>
+      <c r="GFB20" s="5"/>
+      <c r="GFF20" s="5"/>
+      <c r="GFJ20" s="5"/>
+      <c r="GFN20" s="5"/>
+      <c r="GFR20" s="5"/>
+      <c r="GFV20" s="5"/>
+      <c r="GFZ20" s="5"/>
+      <c r="GGD20" s="5"/>
+      <c r="GGH20" s="5"/>
+      <c r="GGL20" s="5"/>
+      <c r="GGP20" s="5"/>
+      <c r="GGT20" s="5"/>
+      <c r="GGX20" s="5"/>
+      <c r="GHB20" s="5"/>
+      <c r="GHF20" s="5"/>
+      <c r="GHJ20" s="5"/>
+      <c r="GHN20" s="5"/>
+      <c r="GHR20" s="5"/>
+      <c r="GHV20" s="5"/>
+      <c r="GHZ20" s="5"/>
+      <c r="GID20" s="5"/>
+      <c r="GIH20" s="5"/>
+      <c r="GIL20" s="5"/>
+      <c r="GIP20" s="5"/>
+      <c r="GIT20" s="5"/>
+      <c r="GIX20" s="5"/>
+      <c r="GJB20" s="5"/>
+      <c r="GJF20" s="5"/>
+      <c r="GJJ20" s="5"/>
+      <c r="GJN20" s="5"/>
+      <c r="GJR20" s="5"/>
+      <c r="GJV20" s="5"/>
+      <c r="GJZ20" s="5"/>
+      <c r="GKD20" s="5"/>
+      <c r="GKH20" s="5"/>
+      <c r="GKL20" s="5"/>
+      <c r="GKP20" s="5"/>
+      <c r="GKT20" s="5"/>
+      <c r="GKX20" s="5"/>
+      <c r="GLB20" s="5"/>
+      <c r="GLF20" s="5"/>
+      <c r="GLJ20" s="5"/>
+      <c r="GLN20" s="5"/>
+      <c r="GLR20" s="5"/>
+      <c r="GLV20" s="5"/>
+      <c r="GLZ20" s="5"/>
+      <c r="GMD20" s="5"/>
+      <c r="GMH20" s="5"/>
+      <c r="GML20" s="5"/>
+      <c r="GMP20" s="5"/>
+      <c r="GMT20" s="5"/>
+      <c r="GMX20" s="5"/>
+      <c r="GNB20" s="5"/>
+      <c r="GNF20" s="5"/>
+      <c r="GNJ20" s="5"/>
+      <c r="GNN20" s="5"/>
+      <c r="GNR20" s="5"/>
+      <c r="GNV20" s="5"/>
+      <c r="GNZ20" s="5"/>
+      <c r="GOD20" s="5"/>
+      <c r="GOH20" s="5"/>
+      <c r="GOL20" s="5"/>
+      <c r="GOP20" s="5"/>
+      <c r="GOT20" s="5"/>
+      <c r="GOX20" s="5"/>
+      <c r="GPB20" s="5"/>
+      <c r="GPF20" s="5"/>
+      <c r="GPJ20" s="5"/>
+      <c r="GPN20" s="5"/>
+      <c r="GPR20" s="5"/>
+      <c r="GPV20" s="5"/>
+      <c r="GPZ20" s="5"/>
+      <c r="GQD20" s="5"/>
+      <c r="GQH20" s="5"/>
+      <c r="GQL20" s="5"/>
+      <c r="GQP20" s="5"/>
+      <c r="GQT20" s="5"/>
+      <c r="GQX20" s="5"/>
+      <c r="GRB20" s="5"/>
+      <c r="GRF20" s="5"/>
+      <c r="GRJ20" s="5"/>
+      <c r="GRN20" s="5"/>
+      <c r="GRR20" s="5"/>
+      <c r="GRV20" s="5"/>
+      <c r="GRZ20" s="5"/>
+      <c r="GSD20" s="5"/>
+      <c r="GSH20" s="5"/>
+      <c r="GSL20" s="5"/>
+      <c r="GSP20" s="5"/>
+      <c r="GST20" s="5"/>
+      <c r="GSX20" s="5"/>
+      <c r="GTB20" s="5"/>
+      <c r="GTF20" s="5"/>
+      <c r="GTJ20" s="5"/>
+      <c r="GTN20" s="5"/>
+      <c r="GTR20" s="5"/>
+      <c r="GTV20" s="5"/>
+      <c r="GTZ20" s="5"/>
+      <c r="GUD20" s="5"/>
+      <c r="GUH20" s="5"/>
+      <c r="GUL20" s="5"/>
+      <c r="GUP20" s="5"/>
+      <c r="GUT20" s="5"/>
+      <c r="GUX20" s="5"/>
+      <c r="GVB20" s="5"/>
+      <c r="GVF20" s="5"/>
+      <c r="GVJ20" s="5"/>
+      <c r="GVN20" s="5"/>
+      <c r="GVR20" s="5"/>
+      <c r="GVV20" s="5"/>
+      <c r="GVZ20" s="5"/>
+      <c r="GWD20" s="5"/>
+      <c r="GWH20" s="5"/>
+      <c r="GWL20" s="5"/>
+      <c r="GWP20" s="5"/>
+      <c r="GWT20" s="5"/>
+      <c r="GWX20" s="5"/>
+      <c r="GXB20" s="5"/>
+      <c r="GXF20" s="5"/>
+      <c r="GXJ20" s="5"/>
+      <c r="GXN20" s="5"/>
+      <c r="GXR20" s="5"/>
+      <c r="GXV20" s="5"/>
+      <c r="GXZ20" s="5"/>
+      <c r="GYD20" s="5"/>
+      <c r="GYH20" s="5"/>
+      <c r="GYL20" s="5"/>
+      <c r="GYP20" s="5"/>
+      <c r="GYT20" s="5"/>
+      <c r="GYX20" s="5"/>
+      <c r="GZB20" s="5"/>
+      <c r="GZF20" s="5"/>
+      <c r="GZJ20" s="5"/>
+      <c r="GZN20" s="5"/>
+      <c r="GZR20" s="5"/>
+      <c r="GZV20" s="5"/>
+      <c r="GZZ20" s="5"/>
+      <c r="HAD20" s="5"/>
+      <c r="HAH20" s="5"/>
+      <c r="HAL20" s="5"/>
+      <c r="HAP20" s="5"/>
+      <c r="HAT20" s="5"/>
+      <c r="HAX20" s="5"/>
+      <c r="HBB20" s="5"/>
+      <c r="HBF20" s="5"/>
+      <c r="HBJ20" s="5"/>
+      <c r="HBN20" s="5"/>
+      <c r="HBR20" s="5"/>
+      <c r="HBV20" s="5"/>
+      <c r="HBZ20" s="5"/>
+      <c r="HCD20" s="5"/>
+      <c r="HCH20" s="5"/>
+      <c r="HCL20" s="5"/>
+      <c r="HCP20" s="5"/>
+      <c r="HCT20" s="5"/>
+      <c r="HCX20" s="5"/>
+      <c r="HDB20" s="5"/>
+      <c r="HDF20" s="5"/>
+      <c r="HDJ20" s="5"/>
+      <c r="HDN20" s="5"/>
+      <c r="HDR20" s="5"/>
+      <c r="HDV20" s="5"/>
+      <c r="HDZ20" s="5"/>
+      <c r="HED20" s="5"/>
+      <c r="HEH20" s="5"/>
+      <c r="HEL20" s="5"/>
+      <c r="HEP20" s="5"/>
+      <c r="HET20" s="5"/>
+      <c r="HEX20" s="5"/>
+      <c r="HFB20" s="5"/>
+      <c r="HFF20" s="5"/>
+      <c r="HFJ20" s="5"/>
+      <c r="HFN20" s="5"/>
+      <c r="HFR20" s="5"/>
+      <c r="HFV20" s="5"/>
+      <c r="HFZ20" s="5"/>
+      <c r="HGD20" s="5"/>
+      <c r="HGH20" s="5"/>
+      <c r="HGL20" s="5"/>
+      <c r="HGP20" s="5"/>
+      <c r="HGT20" s="5"/>
+      <c r="HGX20" s="5"/>
+      <c r="HHB20" s="5"/>
+      <c r="HHF20" s="5"/>
+      <c r="HHJ20" s="5"/>
+      <c r="HHN20" s="5"/>
+      <c r="HHR20" s="5"/>
+      <c r="HHV20" s="5"/>
+      <c r="HHZ20" s="5"/>
+      <c r="HID20" s="5"/>
+      <c r="HIH20" s="5"/>
+      <c r="HIL20" s="5"/>
+      <c r="HIP20" s="5"/>
+      <c r="HIT20" s="5"/>
+      <c r="HIX20" s="5"/>
+      <c r="HJB20" s="5"/>
+      <c r="HJF20" s="5"/>
+      <c r="HJJ20" s="5"/>
+      <c r="HJN20" s="5"/>
+      <c r="HJR20" s="5"/>
+      <c r="HJV20" s="5"/>
+      <c r="HJZ20" s="5"/>
+      <c r="HKD20" s="5"/>
+      <c r="HKH20" s="5"/>
+      <c r="HKL20" s="5"/>
+      <c r="HKP20" s="5"/>
+      <c r="HKT20" s="5"/>
+      <c r="HKX20" s="5"/>
+      <c r="HLB20" s="5"/>
+      <c r="HLF20" s="5"/>
+      <c r="HLJ20" s="5"/>
+      <c r="HLN20" s="5"/>
+      <c r="HLR20" s="5"/>
+      <c r="HLV20" s="5"/>
+      <c r="HLZ20" s="5"/>
+      <c r="HMD20" s="5"/>
+      <c r="HMH20" s="5"/>
+      <c r="HML20" s="5"/>
+      <c r="HMP20" s="5"/>
+      <c r="HMT20" s="5"/>
+      <c r="HMX20" s="5"/>
+      <c r="HNB20" s="5"/>
+      <c r="HNF20" s="5"/>
+      <c r="HNJ20" s="5"/>
+      <c r="HNN20" s="5"/>
+      <c r="HNR20" s="5"/>
+      <c r="HNV20" s="5"/>
+      <c r="HNZ20" s="5"/>
+      <c r="HOD20" s="5"/>
+      <c r="HOH20" s="5"/>
+      <c r="HOL20" s="5"/>
+      <c r="HOP20" s="5"/>
+      <c r="HOT20" s="5"/>
+      <c r="HOX20" s="5"/>
+      <c r="HPB20" s="5"/>
+      <c r="HPF20" s="5"/>
+      <c r="HPJ20" s="5"/>
+      <c r="HPN20" s="5"/>
+      <c r="HPR20" s="5"/>
+      <c r="HPV20" s="5"/>
+      <c r="HPZ20" s="5"/>
+      <c r="HQD20" s="5"/>
+      <c r="HQH20" s="5"/>
+      <c r="HQL20" s="5"/>
+      <c r="HQP20" s="5"/>
+      <c r="HQT20" s="5"/>
+      <c r="HQX20" s="5"/>
+      <c r="HRB20" s="5"/>
+      <c r="HRF20" s="5"/>
+      <c r="HRJ20" s="5"/>
+      <c r="HRN20" s="5"/>
+      <c r="HRR20" s="5"/>
+      <c r="HRV20" s="5"/>
+      <c r="HRZ20" s="5"/>
+      <c r="HSD20" s="5"/>
+      <c r="HSH20" s="5"/>
+      <c r="HSL20" s="5"/>
+      <c r="HSP20" s="5"/>
+      <c r="HST20" s="5"/>
+      <c r="HSX20" s="5"/>
+      <c r="HTB20" s="5"/>
+      <c r="HTF20" s="5"/>
+      <c r="HTJ20" s="5"/>
+      <c r="HTN20" s="5"/>
+      <c r="HTR20" s="5"/>
+      <c r="HTV20" s="5"/>
+      <c r="HTZ20" s="5"/>
+      <c r="HUD20" s="5"/>
+      <c r="HUH20" s="5"/>
+      <c r="HUL20" s="5"/>
+      <c r="HUP20" s="5"/>
+      <c r="HUT20" s="5"/>
+      <c r="HUX20" s="5"/>
+      <c r="HVB20" s="5"/>
+      <c r="HVF20" s="5"/>
+      <c r="HVJ20" s="5"/>
+      <c r="HVN20" s="5"/>
+      <c r="HVR20" s="5"/>
+      <c r="HVV20" s="5"/>
+      <c r="HVZ20" s="5"/>
+      <c r="HWD20" s="5"/>
+      <c r="HWH20" s="5"/>
+      <c r="HWL20" s="5"/>
+      <c r="HWP20" s="5"/>
+      <c r="HWT20" s="5"/>
+      <c r="HWX20" s="5"/>
+      <c r="HXB20" s="5"/>
+      <c r="HXF20" s="5"/>
+      <c r="HXJ20" s="5"/>
+      <c r="HXN20" s="5"/>
+      <c r="HXR20" s="5"/>
+      <c r="HXV20" s="5"/>
+      <c r="HXZ20" s="5"/>
+      <c r="HYD20" s="5"/>
+      <c r="HYH20" s="5"/>
+      <c r="HYL20" s="5"/>
+      <c r="HYP20" s="5"/>
+      <c r="HYT20" s="5"/>
+      <c r="HYX20" s="5"/>
+      <c r="HZB20" s="5"/>
+      <c r="HZF20" s="5"/>
+      <c r="HZJ20" s="5"/>
+      <c r="HZN20" s="5"/>
+      <c r="HZR20" s="5"/>
+      <c r="HZV20" s="5"/>
+      <c r="HZZ20" s="5"/>
+      <c r="IAD20" s="5"/>
+      <c r="IAH20" s="5"/>
+      <c r="IAL20" s="5"/>
+      <c r="IAP20" s="5"/>
+      <c r="IAT20" s="5"/>
+      <c r="IAX20" s="5"/>
+      <c r="IBB20" s="5"/>
+      <c r="IBF20" s="5"/>
+      <c r="IBJ20" s="5"/>
+      <c r="IBN20" s="5"/>
+      <c r="IBR20" s="5"/>
+      <c r="IBV20" s="5"/>
+      <c r="IBZ20" s="5"/>
+      <c r="ICD20" s="5"/>
+      <c r="ICH20" s="5"/>
+      <c r="ICL20" s="5"/>
+      <c r="ICP20" s="5"/>
+      <c r="ICT20" s="5"/>
+      <c r="ICX20" s="5"/>
+      <c r="IDB20" s="5"/>
+      <c r="IDF20" s="5"/>
+      <c r="IDJ20" s="5"/>
+      <c r="IDN20" s="5"/>
+      <c r="IDR20" s="5"/>
+      <c r="IDV20" s="5"/>
+      <c r="IDZ20" s="5"/>
+      <c r="IED20" s="5"/>
+      <c r="IEH20" s="5"/>
+      <c r="IEL20" s="5"/>
+      <c r="IEP20" s="5"/>
+      <c r="IET20" s="5"/>
+      <c r="IEX20" s="5"/>
+      <c r="IFB20" s="5"/>
+      <c r="IFF20" s="5"/>
+      <c r="IFJ20" s="5"/>
+      <c r="IFN20" s="5"/>
+      <c r="IFR20" s="5"/>
+      <c r="IFV20" s="5"/>
+      <c r="IFZ20" s="5"/>
+      <c r="IGD20" s="5"/>
+      <c r="IGH20" s="5"/>
+      <c r="IGL20" s="5"/>
+      <c r="IGP20" s="5"/>
+      <c r="IGT20" s="5"/>
+      <c r="IGX20" s="5"/>
+      <c r="IHB20" s="5"/>
+      <c r="IHF20" s="5"/>
+      <c r="IHJ20" s="5"/>
+      <c r="IHN20" s="5"/>
+      <c r="IHR20" s="5"/>
+      <c r="IHV20" s="5"/>
+      <c r="IHZ20" s="5"/>
+      <c r="IID20" s="5"/>
+      <c r="IIH20" s="5"/>
+      <c r="IIL20" s="5"/>
+      <c r="IIP20" s="5"/>
+      <c r="IIT20" s="5"/>
+      <c r="IIX20" s="5"/>
+      <c r="IJB20" s="5"/>
+      <c r="IJF20" s="5"/>
+      <c r="IJJ20" s="5"/>
+      <c r="IJN20" s="5"/>
+      <c r="IJR20" s="5"/>
+      <c r="IJV20" s="5"/>
+      <c r="IJZ20" s="5"/>
+      <c r="IKD20" s="5"/>
+      <c r="IKH20" s="5"/>
+      <c r="IKL20" s="5"/>
+      <c r="IKP20" s="5"/>
+      <c r="IKT20" s="5"/>
+      <c r="IKX20" s="5"/>
+      <c r="ILB20" s="5"/>
+      <c r="ILF20" s="5"/>
+      <c r="ILJ20" s="5"/>
+      <c r="ILN20" s="5"/>
+      <c r="ILR20" s="5"/>
+      <c r="ILV20" s="5"/>
+      <c r="ILZ20" s="5"/>
+      <c r="IMD20" s="5"/>
+      <c r="IMH20" s="5"/>
+      <c r="IML20" s="5"/>
+      <c r="IMP20" s="5"/>
+      <c r="IMT20" s="5"/>
+      <c r="IMX20" s="5"/>
+      <c r="INB20" s="5"/>
+      <c r="INF20" s="5"/>
+      <c r="INJ20" s="5"/>
+      <c r="INN20" s="5"/>
+      <c r="INR20" s="5"/>
+      <c r="INV20" s="5"/>
+      <c r="INZ20" s="5"/>
+      <c r="IOD20" s="5"/>
+      <c r="IOH20" s="5"/>
+      <c r="IOL20" s="5"/>
+      <c r="IOP20" s="5"/>
+      <c r="IOT20" s="5"/>
+      <c r="IOX20" s="5"/>
+      <c r="IPB20" s="5"/>
+      <c r="IPF20" s="5"/>
+      <c r="IPJ20" s="5"/>
+      <c r="IPN20" s="5"/>
+      <c r="IPR20" s="5"/>
+      <c r="IPV20" s="5"/>
+      <c r="IPZ20" s="5"/>
+      <c r="IQD20" s="5"/>
+      <c r="IQH20" s="5"/>
+      <c r="IQL20" s="5"/>
+      <c r="IQP20" s="5"/>
+      <c r="IQT20" s="5"/>
+      <c r="IQX20" s="5"/>
+      <c r="IRB20" s="5"/>
+      <c r="IRF20" s="5"/>
+      <c r="IRJ20" s="5"/>
+      <c r="IRN20" s="5"/>
+      <c r="IRR20" s="5"/>
+      <c r="IRV20" s="5"/>
+      <c r="IRZ20" s="5"/>
+      <c r="ISD20" s="5"/>
+      <c r="ISH20" s="5"/>
+      <c r="ISL20" s="5"/>
+      <c r="ISP20" s="5"/>
+      <c r="IST20" s="5"/>
+      <c r="ISX20" s="5"/>
+      <c r="ITB20" s="5"/>
+      <c r="ITF20" s="5"/>
+      <c r="ITJ20" s="5"/>
+      <c r="ITN20" s="5"/>
+      <c r="ITR20" s="5"/>
+      <c r="ITV20" s="5"/>
+      <c r="ITZ20" s="5"/>
+      <c r="IUD20" s="5"/>
+      <c r="IUH20" s="5"/>
+      <c r="IUL20" s="5"/>
+      <c r="IUP20" s="5"/>
+      <c r="IUT20" s="5"/>
+      <c r="IUX20" s="5"/>
+      <c r="IVB20" s="5"/>
+      <c r="IVF20" s="5"/>
+      <c r="IVJ20" s="5"/>
+      <c r="IVN20" s="5"/>
+      <c r="IVR20" s="5"/>
+      <c r="IVV20" s="5"/>
+      <c r="IVZ20" s="5"/>
+      <c r="IWD20" s="5"/>
+      <c r="IWH20" s="5"/>
+      <c r="IWL20" s="5"/>
+      <c r="IWP20" s="5"/>
+      <c r="IWT20" s="5"/>
+      <c r="IWX20" s="5"/>
+      <c r="IXB20" s="5"/>
+      <c r="IXF20" s="5"/>
+      <c r="IXJ20" s="5"/>
+      <c r="IXN20" s="5"/>
+      <c r="IXR20" s="5"/>
+      <c r="IXV20" s="5"/>
+      <c r="IXZ20" s="5"/>
+      <c r="IYD20" s="5"/>
+      <c r="IYH20" s="5"/>
+      <c r="IYL20" s="5"/>
+      <c r="IYP20" s="5"/>
+      <c r="IYT20" s="5"/>
+      <c r="IYX20" s="5"/>
+      <c r="IZB20" s="5"/>
+      <c r="IZF20" s="5"/>
+      <c r="IZJ20" s="5"/>
+      <c r="IZN20" s="5"/>
+      <c r="IZR20" s="5"/>
+      <c r="IZV20" s="5"/>
+      <c r="IZZ20" s="5"/>
+      <c r="JAD20" s="5"/>
+      <c r="JAH20" s="5"/>
+      <c r="JAL20" s="5"/>
+      <c r="JAP20" s="5"/>
+      <c r="JAT20" s="5"/>
+      <c r="JAX20" s="5"/>
+      <c r="JBB20" s="5"/>
+      <c r="JBF20" s="5"/>
+      <c r="JBJ20" s="5"/>
+      <c r="JBN20" s="5"/>
+      <c r="JBR20" s="5"/>
+      <c r="JBV20" s="5"/>
+      <c r="JBZ20" s="5"/>
+      <c r="JCD20" s="5"/>
+      <c r="JCH20" s="5"/>
+      <c r="JCL20" s="5"/>
+      <c r="JCP20" s="5"/>
+      <c r="JCT20" s="5"/>
+      <c r="JCX20" s="5"/>
+      <c r="JDB20" s="5"/>
+      <c r="JDF20" s="5"/>
+      <c r="JDJ20" s="5"/>
+      <c r="JDN20" s="5"/>
+      <c r="JDR20" s="5"/>
+      <c r="JDV20" s="5"/>
+      <c r="JDZ20" s="5"/>
+      <c r="JED20" s="5"/>
+      <c r="JEH20" s="5"/>
+      <c r="JEL20" s="5"/>
+      <c r="JEP20" s="5"/>
+      <c r="JET20" s="5"/>
+      <c r="JEX20" s="5"/>
+      <c r="JFB20" s="5"/>
+      <c r="JFF20" s="5"/>
+      <c r="JFJ20" s="5"/>
+      <c r="JFN20" s="5"/>
+      <c r="JFR20" s="5"/>
+      <c r="JFV20" s="5"/>
+      <c r="JFZ20" s="5"/>
+      <c r="JGD20" s="5"/>
+      <c r="JGH20" s="5"/>
+      <c r="JGL20" s="5"/>
+      <c r="JGP20" s="5"/>
+      <c r="JGT20" s="5"/>
+      <c r="JGX20" s="5"/>
+      <c r="JHB20" s="5"/>
+      <c r="JHF20" s="5"/>
+      <c r="JHJ20" s="5"/>
+      <c r="JHN20" s="5"/>
+      <c r="JHR20" s="5"/>
+      <c r="JHV20" s="5"/>
+      <c r="JHZ20" s="5"/>
+      <c r="JID20" s="5"/>
+      <c r="JIH20" s="5"/>
+      <c r="JIL20" s="5"/>
+      <c r="JIP20" s="5"/>
+      <c r="JIT20" s="5"/>
+      <c r="JIX20" s="5"/>
+      <c r="JJB20" s="5"/>
+      <c r="JJF20" s="5"/>
+      <c r="JJJ20" s="5"/>
+      <c r="JJN20" s="5"/>
+      <c r="JJR20" s="5"/>
+      <c r="JJV20" s="5"/>
+      <c r="JJZ20" s="5"/>
+      <c r="JKD20" s="5"/>
+      <c r="JKH20" s="5"/>
+      <c r="JKL20" s="5"/>
+      <c r="JKP20" s="5"/>
+      <c r="JKT20" s="5"/>
+      <c r="JKX20" s="5"/>
+      <c r="JLB20" s="5"/>
+      <c r="JLF20" s="5"/>
+      <c r="JLJ20" s="5"/>
+      <c r="JLN20" s="5"/>
+      <c r="JLR20" s="5"/>
+      <c r="JLV20" s="5"/>
+      <c r="JLZ20" s="5"/>
+      <c r="JMD20" s="5"/>
+      <c r="JMH20" s="5"/>
+      <c r="JML20" s="5"/>
+      <c r="JMP20" s="5"/>
+      <c r="JMT20" s="5"/>
+      <c r="JMX20" s="5"/>
+      <c r="JNB20" s="5"/>
+      <c r="JNF20" s="5"/>
+      <c r="JNJ20" s="5"/>
+      <c r="JNN20" s="5"/>
+      <c r="JNR20" s="5"/>
+      <c r="JNV20" s="5"/>
+      <c r="JNZ20" s="5"/>
+      <c r="JOD20" s="5"/>
+      <c r="JOH20" s="5"/>
+      <c r="JOL20" s="5"/>
+      <c r="JOP20" s="5"/>
+      <c r="JOT20" s="5"/>
+      <c r="JOX20" s="5"/>
+      <c r="JPB20" s="5"/>
+      <c r="JPF20" s="5"/>
+      <c r="JPJ20" s="5"/>
+      <c r="JPN20" s="5"/>
+      <c r="JPR20" s="5"/>
+      <c r="JPV20" s="5"/>
+      <c r="JPZ20" s="5"/>
+      <c r="JQD20" s="5"/>
+      <c r="JQH20" s="5"/>
+      <c r="JQL20" s="5"/>
+      <c r="JQP20" s="5"/>
+      <c r="JQT20" s="5"/>
+      <c r="JQX20" s="5"/>
+      <c r="JRB20" s="5"/>
+      <c r="JRF20" s="5"/>
+      <c r="JRJ20" s="5"/>
+      <c r="JRN20" s="5"/>
+      <c r="JRR20" s="5"/>
+      <c r="JRV20" s="5"/>
+      <c r="JRZ20" s="5"/>
+      <c r="JSD20" s="5"/>
+      <c r="JSH20" s="5"/>
+      <c r="JSL20" s="5"/>
+      <c r="JSP20" s="5"/>
+      <c r="JST20" s="5"/>
+      <c r="JSX20" s="5"/>
+      <c r="JTB20" s="5"/>
+      <c r="JTF20" s="5"/>
+      <c r="JTJ20" s="5"/>
+      <c r="JTN20" s="5"/>
+      <c r="JTR20" s="5"/>
+      <c r="JTV20" s="5"/>
+      <c r="JTZ20" s="5"/>
+      <c r="JUD20" s="5"/>
+      <c r="JUH20" s="5"/>
+      <c r="JUL20" s="5"/>
+      <c r="JUP20" s="5"/>
+      <c r="JUT20" s="5"/>
+      <c r="JUX20" s="5"/>
+      <c r="JVB20" s="5"/>
+      <c r="JVF20" s="5"/>
+      <c r="JVJ20" s="5"/>
+      <c r="JVN20" s="5"/>
+      <c r="JVR20" s="5"/>
+      <c r="JVV20" s="5"/>
+      <c r="JVZ20" s="5"/>
+      <c r="JWD20" s="5"/>
+      <c r="JWH20" s="5"/>
+      <c r="JWL20" s="5"/>
+      <c r="JWP20" s="5"/>
+      <c r="JWT20" s="5"/>
+      <c r="JWX20" s="5"/>
+      <c r="JXB20" s="5"/>
+      <c r="JXF20" s="5"/>
+      <c r="JXJ20" s="5"/>
+      <c r="JXN20" s="5"/>
+      <c r="JXR20" s="5"/>
+      <c r="JXV20" s="5"/>
+      <c r="JXZ20" s="5"/>
+      <c r="JYD20" s="5"/>
+      <c r="JYH20" s="5"/>
+      <c r="JYL20" s="5"/>
+      <c r="JYP20" s="5"/>
+      <c r="JYT20" s="5"/>
+      <c r="JYX20" s="5"/>
+      <c r="JZB20" s="5"/>
+      <c r="JZF20" s="5"/>
+      <c r="JZJ20" s="5"/>
+      <c r="JZN20" s="5"/>
+      <c r="JZR20" s="5"/>
+      <c r="JZV20" s="5"/>
+      <c r="JZZ20" s="5"/>
+      <c r="KAD20" s="5"/>
+      <c r="KAH20" s="5"/>
+      <c r="KAL20" s="5"/>
+      <c r="KAP20" s="5"/>
+      <c r="KAT20" s="5"/>
+      <c r="KAX20" s="5"/>
+      <c r="KBB20" s="5"/>
+      <c r="KBF20" s="5"/>
+      <c r="KBJ20" s="5"/>
+      <c r="KBN20" s="5"/>
+      <c r="KBR20" s="5"/>
+      <c r="KBV20" s="5"/>
+      <c r="KBZ20" s="5"/>
+      <c r="KCD20" s="5"/>
+      <c r="KCH20" s="5"/>
+      <c r="KCL20" s="5"/>
+      <c r="KCP20" s="5"/>
+      <c r="KCT20" s="5"/>
+      <c r="KCX20" s="5"/>
+      <c r="KDB20" s="5"/>
+      <c r="KDF20" s="5"/>
+      <c r="KDJ20" s="5"/>
+      <c r="KDN20" s="5"/>
+      <c r="KDR20" s="5"/>
+      <c r="KDV20" s="5"/>
+      <c r="KDZ20" s="5"/>
+      <c r="KED20" s="5"/>
+      <c r="KEH20" s="5"/>
+      <c r="KEL20" s="5"/>
+      <c r="KEP20" s="5"/>
+      <c r="KET20" s="5"/>
+      <c r="KEX20" s="5"/>
+      <c r="KFB20" s="5"/>
+      <c r="KFF20" s="5"/>
+      <c r="KFJ20" s="5"/>
+      <c r="KFN20" s="5"/>
+      <c r="KFR20" s="5"/>
+      <c r="KFV20" s="5"/>
+      <c r="KFZ20" s="5"/>
+      <c r="KGD20" s="5"/>
+      <c r="KGH20" s="5"/>
+      <c r="KGL20" s="5"/>
+      <c r="KGP20" s="5"/>
+      <c r="KGT20" s="5"/>
+      <c r="KGX20" s="5"/>
+      <c r="KHB20" s="5"/>
+      <c r="KHF20" s="5"/>
+      <c r="KHJ20" s="5"/>
+      <c r="KHN20" s="5"/>
+      <c r="KHR20" s="5"/>
+      <c r="KHV20" s="5"/>
+      <c r="KHZ20" s="5"/>
+      <c r="KID20" s="5"/>
+      <c r="KIH20" s="5"/>
+      <c r="KIL20" s="5"/>
+      <c r="KIP20" s="5"/>
+      <c r="KIT20" s="5"/>
+      <c r="KIX20" s="5"/>
+      <c r="KJB20" s="5"/>
+      <c r="KJF20" s="5"/>
+      <c r="KJJ20" s="5"/>
+      <c r="KJN20" s="5"/>
+      <c r="KJR20" s="5"/>
+      <c r="KJV20" s="5"/>
+      <c r="KJZ20" s="5"/>
+      <c r="KKD20" s="5"/>
+      <c r="KKH20" s="5"/>
+      <c r="KKL20" s="5"/>
+      <c r="KKP20" s="5"/>
+      <c r="KKT20" s="5"/>
+      <c r="KKX20" s="5"/>
+      <c r="KLB20" s="5"/>
+      <c r="KLF20" s="5"/>
+      <c r="KLJ20" s="5"/>
+      <c r="KLN20" s="5"/>
+      <c r="KLR20" s="5"/>
+      <c r="KLV20" s="5"/>
+      <c r="KLZ20" s="5"/>
+      <c r="KMD20" s="5"/>
+      <c r="KMH20" s="5"/>
+      <c r="KML20" s="5"/>
+      <c r="KMP20" s="5"/>
+      <c r="KMT20" s="5"/>
+      <c r="KMX20" s="5"/>
+      <c r="KNB20" s="5"/>
+      <c r="KNF20" s="5"/>
+      <c r="KNJ20" s="5"/>
+      <c r="KNN20" s="5"/>
+      <c r="KNR20" s="5"/>
+      <c r="KNV20" s="5"/>
+      <c r="KNZ20" s="5"/>
+      <c r="KOD20" s="5"/>
+      <c r="KOH20" s="5"/>
+      <c r="KOL20" s="5"/>
+      <c r="KOP20" s="5"/>
+      <c r="KOT20" s="5"/>
+      <c r="KOX20" s="5"/>
+      <c r="KPB20" s="5"/>
+      <c r="KPF20" s="5"/>
+      <c r="KPJ20" s="5"/>
+      <c r="KPN20" s="5"/>
+      <c r="KPR20" s="5"/>
+      <c r="KPV20" s="5"/>
+      <c r="KPZ20" s="5"/>
+      <c r="KQD20" s="5"/>
+      <c r="KQH20" s="5"/>
+      <c r="KQL20" s="5"/>
+      <c r="KQP20" s="5"/>
+      <c r="KQT20" s="5"/>
+      <c r="KQX20" s="5"/>
+      <c r="KRB20" s="5"/>
+      <c r="KRF20" s="5"/>
+      <c r="KRJ20" s="5"/>
+      <c r="KRN20" s="5"/>
+      <c r="KRR20" s="5"/>
+      <c r="KRV20" s="5"/>
+      <c r="KRZ20" s="5"/>
+      <c r="KSD20" s="5"/>
+      <c r="KSH20" s="5"/>
+      <c r="KSL20" s="5"/>
+      <c r="KSP20" s="5"/>
+      <c r="KST20" s="5"/>
+      <c r="KSX20" s="5"/>
+      <c r="KTB20" s="5"/>
+      <c r="KTF20" s="5"/>
+      <c r="KTJ20" s="5"/>
+      <c r="KTN20" s="5"/>
+      <c r="KTR20" s="5"/>
+      <c r="KTV20" s="5"/>
+      <c r="KTZ20" s="5"/>
+      <c r="KUD20" s="5"/>
+      <c r="KUH20" s="5"/>
+      <c r="KUL20" s="5"/>
+      <c r="KUP20" s="5"/>
+      <c r="KUT20" s="5"/>
+      <c r="KUX20" s="5"/>
+      <c r="KVB20" s="5"/>
+      <c r="KVF20" s="5"/>
+      <c r="KVJ20" s="5"/>
+      <c r="KVN20" s="5"/>
+      <c r="KVR20" s="5"/>
+      <c r="KVV20" s="5"/>
+      <c r="KVZ20" s="5"/>
+      <c r="KWD20" s="5"/>
+      <c r="KWH20" s="5"/>
+      <c r="KWL20" s="5"/>
+      <c r="KWP20" s="5"/>
+      <c r="KWT20" s="5"/>
+      <c r="KWX20" s="5"/>
+      <c r="KXB20" s="5"/>
+      <c r="KXF20" s="5"/>
+      <c r="KXJ20" s="5"/>
+      <c r="KXN20" s="5"/>
+      <c r="KXR20" s="5"/>
+      <c r="KXV20" s="5"/>
+      <c r="KXZ20" s="5"/>
+      <c r="KYD20" s="5"/>
+      <c r="KYH20" s="5"/>
+      <c r="KYL20" s="5"/>
+      <c r="KYP20" s="5"/>
+      <c r="KYT20" s="5"/>
+      <c r="KYX20" s="5"/>
+      <c r="KZB20" s="5"/>
+      <c r="KZF20" s="5"/>
+      <c r="KZJ20" s="5"/>
+      <c r="KZN20" s="5"/>
+      <c r="KZR20" s="5"/>
+      <c r="KZV20" s="5"/>
+      <c r="KZZ20" s="5"/>
+      <c r="LAD20" s="5"/>
+      <c r="LAH20" s="5"/>
+      <c r="LAL20" s="5"/>
+      <c r="LAP20" s="5"/>
+      <c r="LAT20" s="5"/>
+      <c r="LAX20" s="5"/>
+      <c r="LBB20" s="5"/>
+      <c r="LBF20" s="5"/>
+      <c r="LBJ20" s="5"/>
+      <c r="LBN20" s="5"/>
+      <c r="LBR20" s="5"/>
+      <c r="LBV20" s="5"/>
+      <c r="LBZ20" s="5"/>
+      <c r="LCD20" s="5"/>
+      <c r="LCH20" s="5"/>
+      <c r="LCL20" s="5"/>
+      <c r="LCP20" s="5"/>
+      <c r="LCT20" s="5"/>
+      <c r="LCX20" s="5"/>
+      <c r="LDB20" s="5"/>
+      <c r="LDF20" s="5"/>
+      <c r="LDJ20" s="5"/>
+      <c r="LDN20" s="5"/>
+      <c r="LDR20" s="5"/>
+      <c r="LDV20" s="5"/>
+      <c r="LDZ20" s="5"/>
+      <c r="LED20" s="5"/>
+      <c r="LEH20" s="5"/>
+      <c r="LEL20" s="5"/>
+      <c r="LEP20" s="5"/>
+      <c r="LET20" s="5"/>
+      <c r="LEX20" s="5"/>
+      <c r="LFB20" s="5"/>
+      <c r="LFF20" s="5"/>
+      <c r="LFJ20" s="5"/>
+      <c r="LFN20" s="5"/>
+      <c r="LFR20" s="5"/>
+      <c r="LFV20" s="5"/>
+      <c r="LFZ20" s="5"/>
+      <c r="LGD20" s="5"/>
+      <c r="LGH20" s="5"/>
+      <c r="LGL20" s="5"/>
+      <c r="LGP20" s="5"/>
+      <c r="LGT20" s="5"/>
+      <c r="LGX20" s="5"/>
+      <c r="LHB20" s="5"/>
+      <c r="LHF20" s="5"/>
+      <c r="LHJ20" s="5"/>
+      <c r="LHN20" s="5"/>
+      <c r="LHR20" s="5"/>
+      <c r="LHV20" s="5"/>
+      <c r="LHZ20" s="5"/>
+      <c r="LID20" s="5"/>
+      <c r="LIH20" s="5"/>
+      <c r="LIL20" s="5"/>
+      <c r="LIP20" s="5"/>
+      <c r="LIT20" s="5"/>
+      <c r="LIX20" s="5"/>
+      <c r="LJB20" s="5"/>
+      <c r="LJF20" s="5"/>
+      <c r="LJJ20" s="5"/>
+      <c r="LJN20" s="5"/>
+      <c r="LJR20" s="5"/>
+      <c r="LJV20" s="5"/>
+      <c r="LJZ20" s="5"/>
+      <c r="LKD20" s="5"/>
+      <c r="LKH20" s="5"/>
+      <c r="LKL20" s="5"/>
+      <c r="LKP20" s="5"/>
+      <c r="LKT20" s="5"/>
+      <c r="LKX20" s="5"/>
+      <c r="LLB20" s="5"/>
+      <c r="LLF20" s="5"/>
+      <c r="LLJ20" s="5"/>
+      <c r="LLN20" s="5"/>
+      <c r="LLR20" s="5"/>
+      <c r="LLV20" s="5"/>
+      <c r="LLZ20" s="5"/>
+      <c r="LMD20" s="5"/>
+      <c r="LMH20" s="5"/>
+      <c r="LML20" s="5"/>
+      <c r="LMP20" s="5"/>
+      <c r="LMT20" s="5"/>
+      <c r="LMX20" s="5"/>
+      <c r="LNB20" s="5"/>
+      <c r="LNF20" s="5"/>
+      <c r="LNJ20" s="5"/>
+      <c r="LNN20" s="5"/>
+      <c r="LNR20" s="5"/>
+      <c r="LNV20" s="5"/>
+      <c r="LNZ20" s="5"/>
+      <c r="LOD20" s="5"/>
+      <c r="LOH20" s="5"/>
+      <c r="LOL20" s="5"/>
+      <c r="LOP20" s="5"/>
+      <c r="LOT20" s="5"/>
+      <c r="LOX20" s="5"/>
+      <c r="LPB20" s="5"/>
+      <c r="LPF20" s="5"/>
+      <c r="LPJ20" s="5"/>
+      <c r="LPN20" s="5"/>
+      <c r="LPR20" s="5"/>
+      <c r="LPV20" s="5"/>
+      <c r="LPZ20" s="5"/>
+      <c r="LQD20" s="5"/>
+      <c r="LQH20" s="5"/>
+      <c r="LQL20" s="5"/>
+      <c r="LQP20" s="5"/>
+      <c r="LQT20" s="5"/>
+      <c r="LQX20" s="5"/>
+      <c r="LRB20" s="5"/>
+      <c r="LRF20" s="5"/>
+      <c r="LRJ20" s="5"/>
+      <c r="LRN20" s="5"/>
+      <c r="LRR20" s="5"/>
+      <c r="LRV20" s="5"/>
+      <c r="LRZ20" s="5"/>
+      <c r="LSD20" s="5"/>
+      <c r="LSH20" s="5"/>
+      <c r="LSL20" s="5"/>
+      <c r="LSP20" s="5"/>
+      <c r="LST20" s="5"/>
+      <c r="LSX20" s="5"/>
+      <c r="LTB20" s="5"/>
+      <c r="LTF20" s="5"/>
+      <c r="LTJ20" s="5"/>
+      <c r="LTN20" s="5"/>
+      <c r="LTR20" s="5"/>
+      <c r="LTV20" s="5"/>
+      <c r="LTZ20" s="5"/>
+      <c r="LUD20" s="5"/>
+      <c r="LUH20" s="5"/>
+      <c r="LUL20" s="5"/>
+      <c r="LUP20" s="5"/>
+      <c r="LUT20" s="5"/>
+      <c r="LUX20" s="5"/>
+      <c r="LVB20" s="5"/>
+      <c r="LVF20" s="5"/>
+      <c r="LVJ20" s="5"/>
+      <c r="LVN20" s="5"/>
+      <c r="LVR20" s="5"/>
+      <c r="LVV20" s="5"/>
+      <c r="LVZ20" s="5"/>
+      <c r="LWD20" s="5"/>
+      <c r="LWH20" s="5"/>
+      <c r="LWL20" s="5"/>
+      <c r="LWP20" s="5"/>
+      <c r="LWT20" s="5"/>
+      <c r="LWX20" s="5"/>
+      <c r="LXB20" s="5"/>
+      <c r="LXF20" s="5"/>
+      <c r="LXJ20" s="5"/>
+      <c r="LXN20" s="5"/>
+      <c r="LXR20" s="5"/>
+      <c r="LXV20" s="5"/>
+      <c r="LXZ20" s="5"/>
+      <c r="LYD20" s="5"/>
+      <c r="LYH20" s="5"/>
+      <c r="LYL20" s="5"/>
+      <c r="LYP20" s="5"/>
+      <c r="LYT20" s="5"/>
+      <c r="LYX20" s="5"/>
+      <c r="LZB20" s="5"/>
+      <c r="LZF20" s="5"/>
+      <c r="LZJ20" s="5"/>
+      <c r="LZN20" s="5"/>
+      <c r="LZR20" s="5"/>
+      <c r="LZV20" s="5"/>
+      <c r="LZZ20" s="5"/>
+      <c r="MAD20" s="5"/>
+      <c r="MAH20" s="5"/>
+      <c r="MAL20" s="5"/>
+      <c r="MAP20" s="5"/>
+      <c r="MAT20" s="5"/>
+      <c r="MAX20" s="5"/>
+      <c r="MBB20" s="5"/>
+      <c r="MBF20" s="5"/>
+      <c r="MBJ20" s="5"/>
+      <c r="MBN20" s="5"/>
+      <c r="MBR20" s="5"/>
+      <c r="MBV20" s="5"/>
+      <c r="MBZ20" s="5"/>
+      <c r="MCD20" s="5"/>
+      <c r="MCH20" s="5"/>
+      <c r="MCL20" s="5"/>
+      <c r="MCP20" s="5"/>
+      <c r="MCT20" s="5"/>
+      <c r="MCX20" s="5"/>
+      <c r="MDB20" s="5"/>
+      <c r="MDF20" s="5"/>
+      <c r="MDJ20" s="5"/>
+      <c r="MDN20" s="5"/>
+      <c r="MDR20" s="5"/>
+      <c r="MDV20" s="5"/>
+      <c r="MDZ20" s="5"/>
+      <c r="MED20" s="5"/>
+      <c r="MEH20" s="5"/>
+      <c r="MEL20" s="5"/>
+      <c r="MEP20" s="5"/>
+      <c r="MET20" s="5"/>
+      <c r="MEX20" s="5"/>
+      <c r="MFB20" s="5"/>
+      <c r="MFF20" s="5"/>
+      <c r="MFJ20" s="5"/>
+      <c r="MFN20" s="5"/>
+      <c r="MFR20" s="5"/>
+      <c r="MFV20" s="5"/>
+      <c r="MFZ20" s="5"/>
+      <c r="MGD20" s="5"/>
+      <c r="MGH20" s="5"/>
+      <c r="MGL20" s="5"/>
+      <c r="MGP20" s="5"/>
+      <c r="MGT20" s="5"/>
+      <c r="MGX20" s="5"/>
+      <c r="MHB20" s="5"/>
+      <c r="MHF20" s="5"/>
+      <c r="MHJ20" s="5"/>
+      <c r="MHN20" s="5"/>
+      <c r="MHR20" s="5"/>
+      <c r="MHV20" s="5"/>
+      <c r="MHZ20" s="5"/>
+      <c r="MID20" s="5"/>
+      <c r="MIH20" s="5"/>
+      <c r="MIL20" s="5"/>
+      <c r="MIP20" s="5"/>
+      <c r="MIT20" s="5"/>
+      <c r="MIX20" s="5"/>
+      <c r="MJB20" s="5"/>
+      <c r="MJF20" s="5"/>
+      <c r="MJJ20" s="5"/>
+      <c r="MJN20" s="5"/>
+      <c r="MJR20" s="5"/>
+      <c r="MJV20" s="5"/>
+      <c r="MJZ20" s="5"/>
+      <c r="MKD20" s="5"/>
+      <c r="MKH20" s="5"/>
+      <c r="MKL20" s="5"/>
+      <c r="MKP20" s="5"/>
+      <c r="MKT20" s="5"/>
+      <c r="MKX20" s="5"/>
+      <c r="MLB20" s="5"/>
+      <c r="MLF20" s="5"/>
+      <c r="MLJ20" s="5"/>
+      <c r="MLN20" s="5"/>
+      <c r="MLR20" s="5"/>
+      <c r="MLV20" s="5"/>
+      <c r="MLZ20" s="5"/>
+      <c r="MMD20" s="5"/>
+      <c r="MMH20" s="5"/>
+      <c r="MML20" s="5"/>
+      <c r="MMP20" s="5"/>
+      <c r="MMT20" s="5"/>
+      <c r="MMX20" s="5"/>
+      <c r="MNB20" s="5"/>
+      <c r="MNF20" s="5"/>
+      <c r="MNJ20" s="5"/>
+      <c r="MNN20" s="5"/>
+      <c r="MNR20" s="5"/>
+      <c r="MNV20" s="5"/>
+      <c r="MNZ20" s="5"/>
+      <c r="MOD20" s="5"/>
+      <c r="MOH20" s="5"/>
+      <c r="MOL20" s="5"/>
+      <c r="MOP20" s="5"/>
+      <c r="MOT20" s="5"/>
+      <c r="MOX20" s="5"/>
+      <c r="MPB20" s="5"/>
+      <c r="MPF20" s="5"/>
+      <c r="MPJ20" s="5"/>
+      <c r="MPN20" s="5"/>
+      <c r="MPR20" s="5"/>
+      <c r="MPV20" s="5"/>
+      <c r="MPZ20" s="5"/>
+      <c r="MQD20" s="5"/>
+      <c r="MQH20" s="5"/>
+      <c r="MQL20" s="5"/>
+      <c r="MQP20" s="5"/>
+      <c r="MQT20" s="5"/>
+      <c r="MQX20" s="5"/>
+      <c r="MRB20" s="5"/>
+      <c r="MRF20" s="5"/>
+      <c r="MRJ20" s="5"/>
+      <c r="MRN20" s="5"/>
+      <c r="MRR20" s="5"/>
+      <c r="MRV20" s="5"/>
+      <c r="MRZ20" s="5"/>
+      <c r="MSD20" s="5"/>
+      <c r="MSH20" s="5"/>
+      <c r="MSL20" s="5"/>
+      <c r="MSP20" s="5"/>
+      <c r="MST20" s="5"/>
+      <c r="MSX20" s="5"/>
+      <c r="MTB20" s="5"/>
+      <c r="MTF20" s="5"/>
+      <c r="MTJ20" s="5"/>
+      <c r="MTN20" s="5"/>
+      <c r="MTR20" s="5"/>
+      <c r="MTV20" s="5"/>
+      <c r="MTZ20" s="5"/>
+      <c r="MUD20" s="5"/>
+      <c r="MUH20" s="5"/>
+      <c r="MUL20" s="5"/>
+      <c r="MUP20" s="5"/>
+      <c r="MUT20" s="5"/>
+      <c r="MUX20" s="5"/>
+      <c r="MVB20" s="5"/>
+      <c r="MVF20" s="5"/>
+      <c r="MVJ20" s="5"/>
+      <c r="MVN20" s="5"/>
+      <c r="MVR20" s="5"/>
+      <c r="MVV20" s="5"/>
+      <c r="MVZ20" s="5"/>
+      <c r="MWD20" s="5"/>
+      <c r="MWH20" s="5"/>
+      <c r="MWL20" s="5"/>
+      <c r="MWP20" s="5"/>
+      <c r="MWT20" s="5"/>
+      <c r="MWX20" s="5"/>
+      <c r="MXB20" s="5"/>
+      <c r="MXF20" s="5"/>
+      <c r="MXJ20" s="5"/>
+      <c r="MXN20" s="5"/>
+      <c r="MXR20" s="5"/>
+      <c r="MXV20" s="5"/>
+      <c r="MXZ20" s="5"/>
+      <c r="MYD20" s="5"/>
+      <c r="MYH20" s="5"/>
+      <c r="MYL20" s="5"/>
+      <c r="MYP20" s="5"/>
+      <c r="MYT20" s="5"/>
+      <c r="MYX20" s="5"/>
+      <c r="MZB20" s="5"/>
+      <c r="MZF20" s="5"/>
+      <c r="MZJ20" s="5"/>
+      <c r="MZN20" s="5"/>
+      <c r="MZR20" s="5"/>
+      <c r="MZV20" s="5"/>
+      <c r="MZZ20" s="5"/>
+      <c r="NAD20" s="5"/>
+      <c r="NAH20" s="5"/>
+      <c r="NAL20" s="5"/>
+      <c r="NAP20" s="5"/>
+      <c r="NAT20" s="5"/>
+      <c r="NAX20" s="5"/>
+      <c r="NBB20" s="5"/>
+      <c r="NBF20" s="5"/>
+      <c r="NBJ20" s="5"/>
+      <c r="NBN20" s="5"/>
+      <c r="NBR20" s="5"/>
+      <c r="NBV20" s="5"/>
+      <c r="NBZ20" s="5"/>
+      <c r="NCD20" s="5"/>
+      <c r="NCH20" s="5"/>
+      <c r="NCL20" s="5"/>
+      <c r="NCP20" s="5"/>
+      <c r="NCT20" s="5"/>
+      <c r="NCX20" s="5"/>
+      <c r="NDB20" s="5"/>
+      <c r="NDF20" s="5"/>
+      <c r="NDJ20" s="5"/>
+      <c r="NDN20" s="5"/>
+      <c r="NDR20" s="5"/>
+      <c r="NDV20" s="5"/>
+      <c r="NDZ20" s="5"/>
+      <c r="NED20" s="5"/>
+      <c r="NEH20" s="5"/>
+      <c r="NEL20" s="5"/>
+      <c r="NEP20" s="5"/>
+      <c r="NET20" s="5"/>
+      <c r="NEX20" s="5"/>
+      <c r="NFB20" s="5"/>
+      <c r="NFF20" s="5"/>
+      <c r="NFJ20" s="5"/>
+      <c r="NFN20" s="5"/>
+      <c r="NFR20" s="5"/>
+      <c r="NFV20" s="5"/>
+      <c r="NFZ20" s="5"/>
+      <c r="NGD20" s="5"/>
+      <c r="NGH20" s="5"/>
+      <c r="NGL20" s="5"/>
+      <c r="NGP20" s="5"/>
+      <c r="NGT20" s="5"/>
+      <c r="NGX20" s="5"/>
+      <c r="NHB20" s="5"/>
+      <c r="NHF20" s="5"/>
+      <c r="NHJ20" s="5"/>
+      <c r="NHN20" s="5"/>
+      <c r="NHR20" s="5"/>
+      <c r="NHV20" s="5"/>
+      <c r="NHZ20" s="5"/>
+      <c r="NID20" s="5"/>
+      <c r="NIH20" s="5"/>
+      <c r="NIL20" s="5"/>
+      <c r="NIP20" s="5"/>
+      <c r="NIT20" s="5"/>
+      <c r="NIX20" s="5"/>
+      <c r="NJB20" s="5"/>
+      <c r="NJF20" s="5"/>
+      <c r="NJJ20" s="5"/>
+      <c r="NJN20" s="5"/>
+      <c r="NJR20" s="5"/>
+      <c r="NJV20" s="5"/>
+      <c r="NJZ20" s="5"/>
+      <c r="NKD20" s="5"/>
+      <c r="NKH20" s="5"/>
+      <c r="NKL20" s="5"/>
+      <c r="NKP20" s="5"/>
+      <c r="NKT20" s="5"/>
+      <c r="NKX20" s="5"/>
+      <c r="NLB20" s="5"/>
+      <c r="NLF20" s="5"/>
+      <c r="NLJ20" s="5"/>
+      <c r="NLN20" s="5"/>
+      <c r="NLR20" s="5"/>
+      <c r="NLV20" s="5"/>
+      <c r="NLZ20" s="5"/>
+      <c r="NMD20" s="5"/>
+      <c r="NMH20" s="5"/>
+      <c r="NML20" s="5"/>
+      <c r="NMP20" s="5"/>
+      <c r="NMT20" s="5"/>
+      <c r="NMX20" s="5"/>
+      <c r="NNB20" s="5"/>
+      <c r="NNF20" s="5"/>
+      <c r="NNJ20" s="5"/>
+      <c r="NNN20" s="5"/>
+      <c r="NNR20" s="5"/>
+      <c r="NNV20" s="5"/>
+      <c r="NNZ20" s="5"/>
+      <c r="NOD20" s="5"/>
+      <c r="NOH20" s="5"/>
+      <c r="NOL20" s="5"/>
+      <c r="NOP20" s="5"/>
+      <c r="NOT20" s="5"/>
+      <c r="NOX20" s="5"/>
+      <c r="NPB20" s="5"/>
+      <c r="NPF20" s="5"/>
+      <c r="NPJ20" s="5"/>
+      <c r="NPN20" s="5"/>
+      <c r="NPR20" s="5"/>
+      <c r="NPV20" s="5"/>
+      <c r="NPZ20" s="5"/>
+      <c r="NQD20" s="5"/>
+      <c r="NQH20" s="5"/>
+      <c r="NQL20" s="5"/>
+      <c r="NQP20" s="5"/>
+      <c r="NQT20" s="5"/>
+      <c r="NQX20" s="5"/>
+      <c r="NRB20" s="5"/>
+      <c r="NRF20" s="5"/>
+      <c r="NRJ20" s="5"/>
+      <c r="NRN20" s="5"/>
+      <c r="NRR20" s="5"/>
+      <c r="NRV20" s="5"/>
+      <c r="NRZ20" s="5"/>
+      <c r="NSD20" s="5"/>
+      <c r="NSH20" s="5"/>
+      <c r="NSL20" s="5"/>
+      <c r="NSP20" s="5"/>
+      <c r="NST20" s="5"/>
+      <c r="NSX20" s="5"/>
+      <c r="NTB20" s="5"/>
+      <c r="NTF20" s="5"/>
+      <c r="NTJ20" s="5"/>
+      <c r="NTN20" s="5"/>
+      <c r="NTR20" s="5"/>
+      <c r="NTV20" s="5"/>
+      <c r="NTZ20" s="5"/>
+      <c r="NUD20" s="5"/>
+      <c r="NUH20" s="5"/>
+      <c r="NUL20" s="5"/>
+      <c r="NUP20" s="5"/>
+      <c r="NUT20" s="5"/>
+      <c r="NUX20" s="5"/>
+      <c r="NVB20" s="5"/>
+      <c r="NVF20" s="5"/>
+      <c r="NVJ20" s="5"/>
+      <c r="NVN20" s="5"/>
+      <c r="NVR20" s="5"/>
+      <c r="NVV20" s="5"/>
+      <c r="NVZ20" s="5"/>
+      <c r="NWD20" s="5"/>
+      <c r="NWH20" s="5"/>
+      <c r="NWL20" s="5"/>
+      <c r="NWP20" s="5"/>
+      <c r="NWT20" s="5"/>
+      <c r="NWX20" s="5"/>
+      <c r="NXB20" s="5"/>
+      <c r="NXF20" s="5"/>
+      <c r="NXJ20" s="5"/>
+      <c r="NXN20" s="5"/>
+      <c r="NXR20" s="5"/>
+      <c r="NXV20" s="5"/>
+      <c r="NXZ20" s="5"/>
+      <c r="NYD20" s="5"/>
+      <c r="NYH20" s="5"/>
+      <c r="NYL20" s="5"/>
+      <c r="NYP20" s="5"/>
+      <c r="NYT20" s="5"/>
+      <c r="NYX20" s="5"/>
+      <c r="NZB20" s="5"/>
+      <c r="NZF20" s="5"/>
+      <c r="NZJ20" s="5"/>
+      <c r="NZN20" s="5"/>
+      <c r="NZR20" s="5"/>
+      <c r="NZV20" s="5"/>
+      <c r="NZZ20" s="5"/>
+      <c r="OAD20" s="5"/>
+      <c r="OAH20" s="5"/>
+      <c r="OAL20" s="5"/>
+      <c r="OAP20" s="5"/>
+      <c r="OAT20" s="5"/>
+      <c r="OAX20" s="5"/>
+      <c r="OBB20" s="5"/>
+      <c r="OBF20" s="5"/>
+      <c r="OBJ20" s="5"/>
+      <c r="OBN20" s="5"/>
+      <c r="OBR20" s="5"/>
+      <c r="OBV20" s="5"/>
+      <c r="OBZ20" s="5"/>
+      <c r="OCD20" s="5"/>
+      <c r="OCH20" s="5"/>
+      <c r="OCL20" s="5"/>
+      <c r="OCP20" s="5"/>
+      <c r="OCT20" s="5"/>
+      <c r="OCX20" s="5"/>
+      <c r="ODB20" s="5"/>
+      <c r="ODF20" s="5"/>
+      <c r="ODJ20" s="5"/>
+      <c r="ODN20" s="5"/>
+      <c r="ODR20" s="5"/>
+      <c r="ODV20" s="5"/>
+      <c r="ODZ20" s="5"/>
+      <c r="OED20" s="5"/>
+      <c r="OEH20" s="5"/>
+      <c r="OEL20" s="5"/>
+      <c r="OEP20" s="5"/>
+      <c r="OET20" s="5"/>
+      <c r="OEX20" s="5"/>
+      <c r="OFB20" s="5"/>
+      <c r="OFF20" s="5"/>
+      <c r="OFJ20" s="5"/>
+      <c r="OFN20" s="5"/>
+      <c r="OFR20" s="5"/>
+      <c r="OFV20" s="5"/>
+      <c r="OFZ20" s="5"/>
+      <c r="OGD20" s="5"/>
+      <c r="OGH20" s="5"/>
+      <c r="OGL20" s="5"/>
+      <c r="OGP20" s="5"/>
+      <c r="OGT20" s="5"/>
+      <c r="OGX20" s="5"/>
+      <c r="OHB20" s="5"/>
+      <c r="OHF20" s="5"/>
+      <c r="OHJ20" s="5"/>
+      <c r="OHN20" s="5"/>
+      <c r="OHR20" s="5"/>
+      <c r="OHV20" s="5"/>
+      <c r="OHZ20" s="5"/>
+      <c r="OID20" s="5"/>
+      <c r="OIH20" s="5"/>
+      <c r="OIL20" s="5"/>
+      <c r="OIP20" s="5"/>
+      <c r="OIT20" s="5"/>
+      <c r="OIX20" s="5"/>
+      <c r="OJB20" s="5"/>
+      <c r="OJF20" s="5"/>
+      <c r="OJJ20" s="5"/>
+      <c r="OJN20" s="5"/>
+      <c r="OJR20" s="5"/>
+      <c r="OJV20" s="5"/>
+      <c r="OJZ20" s="5"/>
+      <c r="OKD20" s="5"/>
+      <c r="OKH20" s="5"/>
+      <c r="OKL20" s="5"/>
+      <c r="OKP20" s="5"/>
+      <c r="OKT20" s="5"/>
+      <c r="OKX20" s="5"/>
+      <c r="OLB20" s="5"/>
+      <c r="OLF20" s="5"/>
+      <c r="OLJ20" s="5"/>
+      <c r="OLN20" s="5"/>
+      <c r="OLR20" s="5"/>
+      <c r="OLV20" s="5"/>
+      <c r="OLZ20" s="5"/>
+      <c r="OMD20" s="5"/>
+      <c r="OMH20" s="5"/>
+      <c r="OML20" s="5"/>
+      <c r="OMP20" s="5"/>
+      <c r="OMT20" s="5"/>
+      <c r="OMX20" s="5"/>
+      <c r="ONB20" s="5"/>
+      <c r="ONF20" s="5"/>
+      <c r="ONJ20" s="5"/>
+      <c r="ONN20" s="5"/>
+      <c r="ONR20" s="5"/>
+      <c r="ONV20" s="5"/>
+      <c r="ONZ20" s="5"/>
+      <c r="OOD20" s="5"/>
+      <c r="OOH20" s="5"/>
+      <c r="OOL20" s="5"/>
+      <c r="OOP20" s="5"/>
+      <c r="OOT20" s="5"/>
+      <c r="OOX20" s="5"/>
+      <c r="OPB20" s="5"/>
+      <c r="OPF20" s="5"/>
+      <c r="OPJ20" s="5"/>
+      <c r="OPN20" s="5"/>
+      <c r="OPR20" s="5"/>
+      <c r="OPV20" s="5"/>
+      <c r="OPZ20" s="5"/>
+      <c r="OQD20" s="5"/>
+      <c r="OQH20" s="5"/>
+      <c r="OQL20" s="5"/>
+      <c r="OQP20" s="5"/>
+      <c r="OQT20" s="5"/>
+      <c r="OQX20" s="5"/>
+      <c r="ORB20" s="5"/>
+      <c r="ORF20" s="5"/>
+      <c r="ORJ20" s="5"/>
+      <c r="ORN20" s="5"/>
+      <c r="ORR20" s="5"/>
+      <c r="ORV20" s="5"/>
+      <c r="ORZ20" s="5"/>
+      <c r="OSD20" s="5"/>
+      <c r="OSH20" s="5"/>
+      <c r="OSL20" s="5"/>
+      <c r="OSP20" s="5"/>
+      <c r="OST20" s="5"/>
+      <c r="OSX20" s="5"/>
+      <c r="OTB20" s="5"/>
+      <c r="OTF20" s="5"/>
+      <c r="OTJ20" s="5"/>
+      <c r="OTN20" s="5"/>
+      <c r="OTR20" s="5"/>
+      <c r="OTV20" s="5"/>
+      <c r="OTZ20" s="5"/>
+      <c r="OUD20" s="5"/>
+      <c r="OUH20" s="5"/>
+      <c r="OUL20" s="5"/>
+      <c r="OUP20" s="5"/>
+      <c r="OUT20" s="5"/>
+      <c r="OUX20" s="5"/>
+      <c r="OVB20" s="5"/>
+      <c r="OVF20" s="5"/>
+      <c r="OVJ20" s="5"/>
+      <c r="OVN20" s="5"/>
+      <c r="OVR20" s="5"/>
+      <c r="OVV20" s="5"/>
+      <c r="OVZ20" s="5"/>
+      <c r="OWD20" s="5"/>
+      <c r="OWH20" s="5"/>
+      <c r="OWL20" s="5"/>
+      <c r="OWP20" s="5"/>
+      <c r="OWT20" s="5"/>
+      <c r="OWX20" s="5"/>
+      <c r="OXB20" s="5"/>
+      <c r="OXF20" s="5"/>
+      <c r="OXJ20" s="5"/>
+      <c r="OXN20" s="5"/>
+      <c r="OXR20" s="5"/>
+      <c r="OXV20" s="5"/>
+      <c r="OXZ20" s="5"/>
+      <c r="OYD20" s="5"/>
+      <c r="OYH20" s="5"/>
+      <c r="OYL20" s="5"/>
+      <c r="OYP20" s="5"/>
+      <c r="OYT20" s="5"/>
+      <c r="OYX20" s="5"/>
+      <c r="OZB20" s="5"/>
+      <c r="OZF20" s="5"/>
+      <c r="OZJ20" s="5"/>
+      <c r="OZN20" s="5"/>
+      <c r="OZR20" s="5"/>
+      <c r="OZV20" s="5"/>
+      <c r="OZZ20" s="5"/>
+      <c r="PAD20" s="5"/>
+      <c r="PAH20" s="5"/>
+      <c r="PAL20" s="5"/>
+      <c r="PAP20" s="5"/>
+      <c r="PAT20" s="5"/>
+      <c r="PAX20" s="5"/>
+      <c r="PBB20" s="5"/>
+      <c r="PBF20" s="5"/>
+      <c r="PBJ20" s="5"/>
+      <c r="PBN20" s="5"/>
+      <c r="PBR20" s="5"/>
+      <c r="PBV20" s="5"/>
+      <c r="PBZ20" s="5"/>
+      <c r="PCD20" s="5"/>
+      <c r="PCH20" s="5"/>
+      <c r="PCL20" s="5"/>
+      <c r="PCP20" s="5"/>
+      <c r="PCT20" s="5"/>
+      <c r="PCX20" s="5"/>
+      <c r="PDB20" s="5"/>
+      <c r="PDF20" s="5"/>
+      <c r="PDJ20" s="5"/>
+      <c r="PDN20" s="5"/>
+      <c r="PDR20" s="5"/>
+      <c r="PDV20" s="5"/>
+      <c r="PDZ20" s="5"/>
+      <c r="PED20" s="5"/>
+      <c r="PEH20" s="5"/>
+      <c r="PEL20" s="5"/>
+      <c r="PEP20" s="5"/>
+      <c r="PET20" s="5"/>
+      <c r="PEX20" s="5"/>
+      <c r="PFB20" s="5"/>
+      <c r="PFF20" s="5"/>
+      <c r="PFJ20" s="5"/>
+      <c r="PFN20" s="5"/>
+      <c r="PFR20" s="5"/>
+      <c r="PFV20" s="5"/>
+      <c r="PFZ20" s="5"/>
+      <c r="PGD20" s="5"/>
+      <c r="PGH20" s="5"/>
+      <c r="PGL20" s="5"/>
+      <c r="PGP20" s="5"/>
+      <c r="PGT20" s="5"/>
+      <c r="PGX20" s="5"/>
+      <c r="PHB20" s="5"/>
+      <c r="PHF20" s="5"/>
+      <c r="PHJ20" s="5"/>
+      <c r="PHN20" s="5"/>
+      <c r="PHR20" s="5"/>
+      <c r="PHV20" s="5"/>
+      <c r="PHZ20" s="5"/>
+      <c r="PID20" s="5"/>
+      <c r="PIH20" s="5"/>
+      <c r="PIL20" s="5"/>
+      <c r="PIP20" s="5"/>
+      <c r="PIT20" s="5"/>
+      <c r="PIX20" s="5"/>
+      <c r="PJB20" s="5"/>
+      <c r="PJF20" s="5"/>
+      <c r="PJJ20" s="5"/>
+      <c r="PJN20" s="5"/>
+      <c r="PJR20" s="5"/>
+      <c r="PJV20" s="5"/>
+      <c r="PJZ20" s="5"/>
+      <c r="PKD20" s="5"/>
+      <c r="PKH20" s="5"/>
+      <c r="PKL20" s="5"/>
+      <c r="PKP20" s="5"/>
+      <c r="PKT20" s="5"/>
+      <c r="PKX20" s="5"/>
+      <c r="PLB20" s="5"/>
+      <c r="PLF20" s="5"/>
+      <c r="PLJ20" s="5"/>
+      <c r="PLN20" s="5"/>
+      <c r="PLR20" s="5"/>
+      <c r="PLV20" s="5"/>
+      <c r="PLZ20" s="5"/>
+      <c r="PMD20" s="5"/>
+      <c r="PMH20" s="5"/>
+      <c r="PML20" s="5"/>
+      <c r="PMP20" s="5"/>
+      <c r="PMT20" s="5"/>
+      <c r="PMX20" s="5"/>
+      <c r="PNB20" s="5"/>
+      <c r="PNF20" s="5"/>
+      <c r="PNJ20" s="5"/>
+      <c r="PNN20" s="5"/>
+      <c r="PNR20" s="5"/>
+      <c r="PNV20" s="5"/>
+      <c r="PNZ20" s="5"/>
+      <c r="POD20" s="5"/>
+      <c r="POH20" s="5"/>
+      <c r="POL20" s="5"/>
+      <c r="POP20" s="5"/>
+      <c r="POT20" s="5"/>
+      <c r="POX20" s="5"/>
+      <c r="PPB20" s="5"/>
+      <c r="PPF20" s="5"/>
+      <c r="PPJ20" s="5"/>
+      <c r="PPN20" s="5"/>
+      <c r="PPR20" s="5"/>
+      <c r="PPV20" s="5"/>
+      <c r="PPZ20" s="5"/>
+      <c r="PQD20" s="5"/>
+      <c r="PQH20" s="5"/>
+      <c r="PQL20" s="5"/>
+      <c r="PQP20" s="5"/>
+      <c r="PQT20" s="5"/>
+      <c r="PQX20" s="5"/>
+      <c r="PRB20" s="5"/>
+      <c r="PRF20" s="5"/>
+      <c r="PRJ20" s="5"/>
+      <c r="PRN20" s="5"/>
+      <c r="PRR20" s="5"/>
+      <c r="PRV20" s="5"/>
+      <c r="PRZ20" s="5"/>
+      <c r="PSD20" s="5"/>
+      <c r="PSH20" s="5"/>
+      <c r="PSL20" s="5"/>
+      <c r="PSP20" s="5"/>
+      <c r="PST20" s="5"/>
+      <c r="PSX20" s="5"/>
+      <c r="PTB20" s="5"/>
+      <c r="PTF20" s="5"/>
+      <c r="PTJ20" s="5"/>
+      <c r="PTN20" s="5"/>
+      <c r="PTR20" s="5"/>
+      <c r="PTV20" s="5"/>
+      <c r="PTZ20" s="5"/>
+      <c r="PUD20" s="5"/>
+      <c r="PUH20" s="5"/>
+      <c r="PUL20" s="5"/>
+      <c r="PUP20" s="5"/>
+      <c r="PUT20" s="5"/>
+      <c r="PUX20" s="5"/>
+      <c r="PVB20" s="5"/>
+      <c r="PVF20" s="5"/>
+      <c r="PVJ20" s="5"/>
+      <c r="PVN20" s="5"/>
+      <c r="PVR20" s="5"/>
+      <c r="PVV20" s="5"/>
+      <c r="PVZ20" s="5"/>
+      <c r="PWD20" s="5"/>
+      <c r="PWH20" s="5"/>
+      <c r="PWL20" s="5"/>
+      <c r="PWP20" s="5"/>
+      <c r="PWT20" s="5"/>
+      <c r="PWX20" s="5"/>
+      <c r="PXB20" s="5"/>
+      <c r="PXF20" s="5"/>
+      <c r="PXJ20" s="5"/>
+      <c r="PXN20" s="5"/>
+      <c r="PXR20" s="5"/>
+      <c r="PXV20" s="5"/>
+      <c r="PXZ20" s="5"/>
+      <c r="PYD20" s="5"/>
+      <c r="PYH20" s="5"/>
+      <c r="PYL20" s="5"/>
+      <c r="PYP20" s="5"/>
+      <c r="PYT20" s="5"/>
+      <c r="PYX20" s="5"/>
+      <c r="PZB20" s="5"/>
+      <c r="PZF20" s="5"/>
+      <c r="PZJ20" s="5"/>
+      <c r="PZN20" s="5"/>
+      <c r="PZR20" s="5"/>
+      <c r="PZV20" s="5"/>
+      <c r="PZZ20" s="5"/>
+      <c r="QAD20" s="5"/>
+      <c r="QAH20" s="5"/>
+      <c r="QAL20" s="5"/>
+      <c r="QAP20" s="5"/>
+      <c r="QAT20" s="5"/>
+      <c r="QAX20" s="5"/>
+      <c r="QBB20" s="5"/>
+      <c r="QBF20" s="5"/>
+      <c r="QBJ20" s="5"/>
+      <c r="QBN20" s="5"/>
+      <c r="QBR20" s="5"/>
+      <c r="QBV20" s="5"/>
+      <c r="QBZ20" s="5"/>
+      <c r="QCD20" s="5"/>
+      <c r="QCH20" s="5"/>
+      <c r="QCL20" s="5"/>
+      <c r="QCP20" s="5"/>
+      <c r="QCT20" s="5"/>
+      <c r="QCX20" s="5"/>
+      <c r="QDB20" s="5"/>
+      <c r="QDF20" s="5"/>
+      <c r="QDJ20" s="5"/>
+      <c r="QDN20" s="5"/>
+      <c r="QDR20" s="5"/>
+      <c r="QDV20" s="5"/>
+      <c r="QDZ20" s="5"/>
+      <c r="QED20" s="5"/>
+      <c r="QEH20" s="5"/>
+      <c r="QEL20" s="5"/>
+      <c r="QEP20" s="5"/>
+      <c r="QET20" s="5"/>
+      <c r="QEX20" s="5"/>
+      <c r="QFB20" s="5"/>
+      <c r="QFF20" s="5"/>
+      <c r="QFJ20" s="5"/>
+      <c r="QFN20" s="5"/>
+      <c r="QFR20" s="5"/>
+      <c r="QFV20" s="5"/>
+      <c r="QFZ20" s="5"/>
+      <c r="QGD20" s="5"/>
+      <c r="QGH20" s="5"/>
+      <c r="QGL20" s="5"/>
+      <c r="QGP20" s="5"/>
+      <c r="QGT20" s="5"/>
+      <c r="QGX20" s="5"/>
+      <c r="QHB20" s="5"/>
+      <c r="QHF20" s="5"/>
+      <c r="QHJ20" s="5"/>
+      <c r="QHN20" s="5"/>
+      <c r="QHR20" s="5"/>
+      <c r="QHV20" s="5"/>
+      <c r="QHZ20" s="5"/>
+      <c r="QID20" s="5"/>
+      <c r="QIH20" s="5"/>
+      <c r="QIL20" s="5"/>
+      <c r="QIP20" s="5"/>
+      <c r="QIT20" s="5"/>
+      <c r="QIX20" s="5"/>
+      <c r="QJB20" s="5"/>
+      <c r="QJF20" s="5"/>
+      <c r="QJJ20" s="5"/>
+      <c r="QJN20" s="5"/>
+      <c r="QJR20" s="5"/>
+      <c r="QJV20" s="5"/>
+      <c r="QJZ20" s="5"/>
+      <c r="QKD20" s="5"/>
+      <c r="QKH20" s="5"/>
+      <c r="QKL20" s="5"/>
+      <c r="QKP20" s="5"/>
+      <c r="QKT20" s="5"/>
+      <c r="QKX20" s="5"/>
+      <c r="QLB20" s="5"/>
+      <c r="QLF20" s="5"/>
+      <c r="QLJ20" s="5"/>
+      <c r="QLN20" s="5"/>
+      <c r="QLR20" s="5"/>
+      <c r="QLV20" s="5"/>
+      <c r="QLZ20" s="5"/>
+      <c r="QMD20" s="5"/>
+      <c r="QMH20" s="5"/>
+      <c r="QML20" s="5"/>
+      <c r="QMP20" s="5"/>
+      <c r="QMT20" s="5"/>
+      <c r="QMX20" s="5"/>
+      <c r="QNB20" s="5"/>
+      <c r="QNF20" s="5"/>
+      <c r="QNJ20" s="5"/>
+      <c r="QNN20" s="5"/>
+      <c r="QNR20" s="5"/>
+      <c r="QNV20" s="5"/>
+      <c r="QNZ20" s="5"/>
+      <c r="QOD20" s="5"/>
+      <c r="QOH20" s="5"/>
+      <c r="QOL20" s="5"/>
+      <c r="QOP20" s="5"/>
+      <c r="QOT20" s="5"/>
+      <c r="QOX20" s="5"/>
+      <c r="QPB20" s="5"/>
+      <c r="QPF20" s="5"/>
+      <c r="QPJ20" s="5"/>
+      <c r="QPN20" s="5"/>
+      <c r="QPR20" s="5"/>
+      <c r="QPV20" s="5"/>
+      <c r="QPZ20" s="5"/>
+      <c r="QQD20" s="5"/>
+      <c r="QQH20" s="5"/>
+      <c r="QQL20" s="5"/>
+      <c r="QQP20" s="5"/>
+      <c r="QQT20" s="5"/>
+      <c r="QQX20" s="5"/>
+      <c r="QRB20" s="5"/>
+      <c r="QRF20" s="5"/>
+      <c r="QRJ20" s="5"/>
+      <c r="QRN20" s="5"/>
+      <c r="QRR20" s="5"/>
+      <c r="QRV20" s="5"/>
+      <c r="QRZ20" s="5"/>
+      <c r="QSD20" s="5"/>
+      <c r="QSH20" s="5"/>
+      <c r="QSL20" s="5"/>
+      <c r="QSP20" s="5"/>
+      <c r="QST20" s="5"/>
+      <c r="QSX20" s="5"/>
+      <c r="QTB20" s="5"/>
+      <c r="QTF20" s="5"/>
+      <c r="QTJ20" s="5"/>
+      <c r="QTN20" s="5"/>
+      <c r="QTR20" s="5"/>
+      <c r="QTV20" s="5"/>
+      <c r="QTZ20" s="5"/>
+      <c r="QUD20" s="5"/>
+      <c r="QUH20" s="5"/>
+      <c r="QUL20" s="5"/>
+      <c r="QUP20" s="5"/>
+      <c r="QUT20" s="5"/>
+      <c r="QUX20" s="5"/>
+      <c r="QVB20" s="5"/>
+      <c r="QVF20" s="5"/>
+      <c r="QVJ20" s="5"/>
+      <c r="QVN20" s="5"/>
+      <c r="QVR20" s="5"/>
+      <c r="QVV20" s="5"/>
+      <c r="QVZ20" s="5"/>
+      <c r="QWD20" s="5"/>
+      <c r="QWH20" s="5"/>
+      <c r="QWL20" s="5"/>
+      <c r="QWP20" s="5"/>
+      <c r="QWT20" s="5"/>
+      <c r="QWX20" s="5"/>
+      <c r="QXB20" s="5"/>
+      <c r="QXF20" s="5"/>
+      <c r="QXJ20" s="5"/>
+      <c r="QXN20" s="5"/>
+      <c r="QXR20" s="5"/>
+      <c r="QXV20" s="5"/>
+      <c r="QXZ20" s="5"/>
+      <c r="QYD20" s="5"/>
+      <c r="QYH20" s="5"/>
+      <c r="QYL20" s="5"/>
+      <c r="QYP20" s="5"/>
+      <c r="QYT20" s="5"/>
+      <c r="QYX20" s="5"/>
+      <c r="QZB20" s="5"/>
+      <c r="QZF20" s="5"/>
+      <c r="QZJ20" s="5"/>
+      <c r="QZN20" s="5"/>
+      <c r="QZR20" s="5"/>
+      <c r="QZV20" s="5"/>
+      <c r="QZZ20" s="5"/>
+      <c r="RAD20" s="5"/>
+      <c r="RAH20" s="5"/>
+      <c r="RAL20" s="5"/>
+      <c r="RAP20" s="5"/>
+      <c r="RAT20" s="5"/>
+      <c r="RAX20" s="5"/>
+      <c r="RBB20" s="5"/>
+      <c r="RBF20" s="5"/>
+      <c r="RBJ20" s="5"/>
+      <c r="RBN20" s="5"/>
+      <c r="RBR20" s="5"/>
+      <c r="RBV20" s="5"/>
+      <c r="RBZ20" s="5"/>
+      <c r="RCD20" s="5"/>
+      <c r="RCH20" s="5"/>
+      <c r="RCL20" s="5"/>
+      <c r="RCP20" s="5"/>
+      <c r="RCT20" s="5"/>
+      <c r="RCX20" s="5"/>
+      <c r="RDB20" s="5"/>
+      <c r="RDF20" s="5"/>
+      <c r="RDJ20" s="5"/>
+      <c r="RDN20" s="5"/>
+      <c r="RDR20" s="5"/>
+      <c r="RDV20" s="5"/>
+      <c r="RDZ20" s="5"/>
+      <c r="RED20" s="5"/>
+      <c r="REH20" s="5"/>
+      <c r="REL20" s="5"/>
+      <c r="REP20" s="5"/>
+      <c r="RET20" s="5"/>
+      <c r="REX20" s="5"/>
+      <c r="RFB20" s="5"/>
+      <c r="RFF20" s="5"/>
+      <c r="RFJ20" s="5"/>
+      <c r="RFN20" s="5"/>
+      <c r="RFR20" s="5"/>
+      <c r="RFV20" s="5"/>
+      <c r="RFZ20" s="5"/>
+      <c r="RGD20" s="5"/>
+      <c r="RGH20" s="5"/>
+      <c r="RGL20" s="5"/>
+      <c r="RGP20" s="5"/>
+      <c r="RGT20" s="5"/>
+      <c r="RGX20" s="5"/>
+      <c r="RHB20" s="5"/>
+      <c r="RHF20" s="5"/>
+      <c r="RHJ20" s="5"/>
+      <c r="RHN20" s="5"/>
+      <c r="RHR20" s="5"/>
+      <c r="RHV20" s="5"/>
+      <c r="RHZ20" s="5"/>
+      <c r="RID20" s="5"/>
+      <c r="RIH20" s="5"/>
+      <c r="RIL20" s="5"/>
+      <c r="RIP20" s="5"/>
+      <c r="RIT20" s="5"/>
+      <c r="RIX20" s="5"/>
+      <c r="RJB20" s="5"/>
+      <c r="RJF20" s="5"/>
+      <c r="RJJ20" s="5"/>
+      <c r="RJN20" s="5"/>
+      <c r="RJR20" s="5"/>
+      <c r="RJV20" s="5"/>
+      <c r="RJZ20" s="5"/>
+      <c r="RKD20" s="5"/>
+      <c r="RKH20" s="5"/>
+      <c r="RKL20" s="5"/>
+      <c r="RKP20" s="5"/>
+      <c r="RKT20" s="5"/>
+      <c r="RKX20" s="5"/>
+      <c r="RLB20" s="5"/>
+      <c r="RLF20" s="5"/>
+      <c r="RLJ20" s="5"/>
+      <c r="RLN20" s="5"/>
+      <c r="RLR20" s="5"/>
+      <c r="RLV20" s="5"/>
+      <c r="RLZ20" s="5"/>
+      <c r="RMD20" s="5"/>
+      <c r="RMH20" s="5"/>
+      <c r="RML20" s="5"/>
+      <c r="RMP20" s="5"/>
+      <c r="RMT20" s="5"/>
+      <c r="RMX20" s="5"/>
+      <c r="RNB20" s="5"/>
+      <c r="RNF20" s="5"/>
+      <c r="RNJ20" s="5"/>
+      <c r="RNN20" s="5"/>
+      <c r="RNR20" s="5"/>
+      <c r="RNV20" s="5"/>
+      <c r="RNZ20" s="5"/>
+      <c r="ROD20" s="5"/>
+      <c r="ROH20" s="5"/>
+      <c r="ROL20" s="5"/>
+      <c r="ROP20" s="5"/>
+      <c r="ROT20" s="5"/>
+      <c r="ROX20" s="5"/>
+      <c r="RPB20" s="5"/>
+      <c r="RPF20" s="5"/>
+      <c r="RPJ20" s="5"/>
+      <c r="RPN20" s="5"/>
+      <c r="RPR20" s="5"/>
+      <c r="RPV20" s="5"/>
+      <c r="RPZ20" s="5"/>
+      <c r="RQD20" s="5"/>
+      <c r="RQH20" s="5"/>
+      <c r="RQL20" s="5"/>
+      <c r="RQP20" s="5"/>
+      <c r="RQT20" s="5"/>
+      <c r="RQX20" s="5"/>
+      <c r="RRB20" s="5"/>
+      <c r="RRF20" s="5"/>
+      <c r="RRJ20" s="5"/>
+      <c r="RRN20" s="5"/>
+      <c r="RRR20" s="5"/>
+      <c r="RRV20" s="5"/>
+      <c r="RRZ20" s="5"/>
+      <c r="RSD20" s="5"/>
+      <c r="RSH20" s="5"/>
+      <c r="RSL20" s="5"/>
+      <c r="RSP20" s="5"/>
+      <c r="RST20" s="5"/>
+      <c r="RSX20" s="5"/>
+      <c r="RTB20" s="5"/>
+      <c r="RTF20" s="5"/>
+      <c r="RTJ20" s="5"/>
+      <c r="RTN20" s="5"/>
+      <c r="RTR20" s="5"/>
+      <c r="RTV20" s="5"/>
+      <c r="RTZ20" s="5"/>
+      <c r="RUD20" s="5"/>
+      <c r="RUH20" s="5"/>
+      <c r="RUL20" s="5"/>
+      <c r="RUP20" s="5"/>
+      <c r="RUT20" s="5"/>
+      <c r="RUX20" s="5"/>
+      <c r="RVB20" s="5"/>
+      <c r="RVF20" s="5"/>
+      <c r="RVJ20" s="5"/>
+      <c r="RVN20" s="5"/>
+      <c r="RVR20" s="5"/>
+      <c r="RVV20" s="5"/>
+      <c r="RVZ20" s="5"/>
+      <c r="RWD20" s="5"/>
+      <c r="RWH20" s="5"/>
+      <c r="RWL20" s="5"/>
+      <c r="RWP20" s="5"/>
+      <c r="RWT20" s="5"/>
+      <c r="RWX20" s="5"/>
+      <c r="RXB20" s="5"/>
+      <c r="RXF20" s="5"/>
+      <c r="RXJ20" s="5"/>
+      <c r="RXN20" s="5"/>
+      <c r="RXR20" s="5"/>
+      <c r="RXV20" s="5"/>
+      <c r="RXZ20" s="5"/>
+      <c r="RYD20" s="5"/>
+      <c r="RYH20" s="5"/>
+      <c r="RYL20" s="5"/>
+      <c r="RYP20" s="5"/>
+      <c r="RYT20" s="5"/>
+      <c r="RYX20" s="5"/>
+      <c r="RZB20" s="5"/>
+      <c r="RZF20" s="5"/>
+      <c r="RZJ20" s="5"/>
+      <c r="RZN20" s="5"/>
+      <c r="RZR20" s="5"/>
+      <c r="RZV20" s="5"/>
+      <c r="RZZ20" s="5"/>
+      <c r="SAD20" s="5"/>
+      <c r="SAH20" s="5"/>
+      <c r="SAL20" s="5"/>
+      <c r="SAP20" s="5"/>
+      <c r="SAT20" s="5"/>
+      <c r="SAX20" s="5"/>
+      <c r="SBB20" s="5"/>
+      <c r="SBF20" s="5"/>
+      <c r="SBJ20" s="5"/>
+      <c r="SBN20" s="5"/>
+      <c r="SBR20" s="5"/>
+      <c r="SBV20" s="5"/>
+      <c r="SBZ20" s="5"/>
+      <c r="SCD20" s="5"/>
+      <c r="SCH20" s="5"/>
+      <c r="SCL20" s="5"/>
+      <c r="SCP20" s="5"/>
+      <c r="SCT20" s="5"/>
+      <c r="SCX20" s="5"/>
+      <c r="SDB20" s="5"/>
+      <c r="SDF20" s="5"/>
+      <c r="SDJ20" s="5"/>
+      <c r="SDN20" s="5"/>
+      <c r="SDR20" s="5"/>
+      <c r="SDV20" s="5"/>
+      <c r="SDZ20" s="5"/>
+      <c r="SED20" s="5"/>
+      <c r="SEH20" s="5"/>
+      <c r="SEL20" s="5"/>
+      <c r="SEP20" s="5"/>
+      <c r="SET20" s="5"/>
+      <c r="SEX20" s="5"/>
+      <c r="SFB20" s="5"/>
+      <c r="SFF20" s="5"/>
+      <c r="SFJ20" s="5"/>
+      <c r="SFN20" s="5"/>
+      <c r="SFR20" s="5"/>
+      <c r="SFV20" s="5"/>
+      <c r="SFZ20" s="5"/>
+      <c r="SGD20" s="5"/>
+      <c r="SGH20" s="5"/>
+      <c r="SGL20" s="5"/>
+      <c r="SGP20" s="5"/>
+      <c r="SGT20" s="5"/>
+      <c r="SGX20" s="5"/>
+      <c r="SHB20" s="5"/>
+      <c r="SHF20" s="5"/>
+      <c r="SHJ20" s="5"/>
+      <c r="SHN20" s="5"/>
+      <c r="SHR20" s="5"/>
+      <c r="SHV20" s="5"/>
+      <c r="SHZ20" s="5"/>
+      <c r="SID20" s="5"/>
+      <c r="SIH20" s="5"/>
+      <c r="SIL20" s="5"/>
+      <c r="SIP20" s="5"/>
+      <c r="SIT20" s="5"/>
+      <c r="SIX20" s="5"/>
+      <c r="SJB20" s="5"/>
+      <c r="SJF20" s="5"/>
+      <c r="SJJ20" s="5"/>
+      <c r="SJN20" s="5"/>
+      <c r="SJR20" s="5"/>
+      <c r="SJV20" s="5"/>
+      <c r="SJZ20" s="5"/>
+      <c r="SKD20" s="5"/>
+      <c r="SKH20" s="5"/>
+      <c r="SKL20" s="5"/>
+      <c r="SKP20" s="5"/>
+      <c r="SKT20" s="5"/>
+      <c r="SKX20" s="5"/>
+      <c r="SLB20" s="5"/>
+      <c r="SLF20" s="5"/>
+      <c r="SLJ20" s="5"/>
+      <c r="SLN20" s="5"/>
+      <c r="SLR20" s="5"/>
+      <c r="SLV20" s="5"/>
+      <c r="SLZ20" s="5"/>
+      <c r="SMD20" s="5"/>
+      <c r="SMH20" s="5"/>
+      <c r="SML20" s="5"/>
+      <c r="SMP20" s="5"/>
+      <c r="SMT20" s="5"/>
+      <c r="SMX20" s="5"/>
+      <c r="SNB20" s="5"/>
+      <c r="SNF20" s="5"/>
+      <c r="SNJ20" s="5"/>
+      <c r="SNN20" s="5"/>
+      <c r="SNR20" s="5"/>
+      <c r="SNV20" s="5"/>
+      <c r="SNZ20" s="5"/>
+      <c r="SOD20" s="5"/>
+      <c r="SOH20" s="5"/>
+      <c r="SOL20" s="5"/>
+      <c r="SOP20" s="5"/>
+      <c r="SOT20" s="5"/>
+      <c r="SOX20" s="5"/>
+      <c r="SPB20" s="5"/>
+      <c r="SPF20" s="5"/>
+      <c r="SPJ20" s="5"/>
+      <c r="SPN20" s="5"/>
+      <c r="SPR20" s="5"/>
+      <c r="SPV20" s="5"/>
+      <c r="SPZ20" s="5"/>
+      <c r="SQD20" s="5"/>
+      <c r="SQH20" s="5"/>
+      <c r="SQL20" s="5"/>
+      <c r="SQP20" s="5"/>
+      <c r="SQT20" s="5"/>
+      <c r="SQX20" s="5"/>
+      <c r="SRB20" s="5"/>
+      <c r="SRF20" s="5"/>
+      <c r="SRJ20" s="5"/>
+      <c r="SRN20" s="5"/>
+      <c r="SRR20" s="5"/>
+      <c r="SRV20" s="5"/>
+      <c r="SRZ20" s="5"/>
+      <c r="SSD20" s="5"/>
+      <c r="SSH20" s="5"/>
+      <c r="SSL20" s="5"/>
+      <c r="SSP20" s="5"/>
+      <c r="SST20" s="5"/>
+      <c r="SSX20" s="5"/>
+      <c r="STB20" s="5"/>
+      <c r="STF20" s="5"/>
+      <c r="STJ20" s="5"/>
+      <c r="STN20" s="5"/>
+      <c r="STR20" s="5"/>
+      <c r="STV20" s="5"/>
+      <c r="STZ20" s="5"/>
+      <c r="SUD20" s="5"/>
+      <c r="SUH20" s="5"/>
+      <c r="SUL20" s="5"/>
+      <c r="SUP20" s="5"/>
+      <c r="SUT20" s="5"/>
+      <c r="SUX20" s="5"/>
+      <c r="SVB20" s="5"/>
+      <c r="SVF20" s="5"/>
+      <c r="SVJ20" s="5"/>
+      <c r="SVN20" s="5"/>
+      <c r="SVR20" s="5"/>
+      <c r="SVV20" s="5"/>
+      <c r="SVZ20" s="5"/>
+      <c r="SWD20" s="5"/>
+      <c r="SWH20" s="5"/>
+      <c r="SWL20" s="5"/>
+      <c r="SWP20" s="5"/>
+      <c r="SWT20" s="5"/>
+      <c r="SWX20" s="5"/>
+      <c r="SXB20" s="5"/>
+      <c r="SXF20" s="5"/>
+      <c r="SXJ20" s="5"/>
+      <c r="SXN20" s="5"/>
+      <c r="SXR20" s="5"/>
+      <c r="SXV20" s="5"/>
+      <c r="SXZ20" s="5"/>
+      <c r="SYD20" s="5"/>
+      <c r="SYH20" s="5"/>
+      <c r="SYL20" s="5"/>
+      <c r="SYP20" s="5"/>
+      <c r="SYT20" s="5"/>
+      <c r="SYX20" s="5"/>
+      <c r="SZB20" s="5"/>
+      <c r="SZF20" s="5"/>
+      <c r="SZJ20" s="5"/>
+      <c r="SZN20" s="5"/>
+      <c r="SZR20" s="5"/>
+      <c r="SZV20" s="5"/>
+      <c r="SZZ20" s="5"/>
+      <c r="TAD20" s="5"/>
+      <c r="TAH20" s="5"/>
+      <c r="TAL20" s="5"/>
+      <c r="TAP20" s="5"/>
+      <c r="TAT20" s="5"/>
+      <c r="TAX20" s="5"/>
+      <c r="TBB20" s="5"/>
+      <c r="TBF20" s="5"/>
+      <c r="TBJ20" s="5"/>
+      <c r="TBN20" s="5"/>
+      <c r="TBR20" s="5"/>
+      <c r="TBV20" s="5"/>
+      <c r="TBZ20" s="5"/>
+      <c r="TCD20" s="5"/>
+      <c r="TCH20" s="5"/>
+      <c r="TCL20" s="5"/>
+      <c r="TCP20" s="5"/>
+      <c r="TCT20" s="5"/>
+      <c r="TCX20" s="5"/>
+      <c r="TDB20" s="5"/>
+      <c r="TDF20" s="5"/>
+      <c r="TDJ20" s="5"/>
+      <c r="TDN20" s="5"/>
+      <c r="TDR20" s="5"/>
+      <c r="TDV20" s="5"/>
+      <c r="TDZ20" s="5"/>
+      <c r="TED20" s="5"/>
+      <c r="TEH20" s="5"/>
+      <c r="TEL20" s="5"/>
+      <c r="TEP20" s="5"/>
+      <c r="TET20" s="5"/>
+      <c r="TEX20" s="5"/>
+      <c r="TFB20" s="5"/>
+      <c r="TFF20" s="5"/>
+      <c r="TFJ20" s="5"/>
+      <c r="TFN20" s="5"/>
+      <c r="TFR20" s="5"/>
+      <c r="TFV20" s="5"/>
+      <c r="TFZ20" s="5"/>
+      <c r="TGD20" s="5"/>
+      <c r="TGH20" s="5"/>
+      <c r="TGL20" s="5"/>
+      <c r="TGP20" s="5"/>
+      <c r="TGT20" s="5"/>
+      <c r="TGX20" s="5"/>
+      <c r="THB20" s="5"/>
+      <c r="THF20" s="5"/>
+      <c r="THJ20" s="5"/>
+      <c r="THN20" s="5"/>
+      <c r="THR20" s="5"/>
+      <c r="THV20" s="5"/>
+      <c r="THZ20" s="5"/>
+      <c r="TID20" s="5"/>
+      <c r="TIH20" s="5"/>
+      <c r="TIL20" s="5"/>
+      <c r="TIP20" s="5"/>
+      <c r="TIT20" s="5"/>
+      <c r="TIX20" s="5"/>
+      <c r="TJB20" s="5"/>
+      <c r="TJF20" s="5"/>
+      <c r="TJJ20" s="5"/>
+      <c r="TJN20" s="5"/>
+      <c r="TJR20" s="5"/>
+      <c r="TJV20" s="5"/>
+      <c r="TJZ20" s="5"/>
+      <c r="TKD20" s="5"/>
+      <c r="TKH20" s="5"/>
+      <c r="TKL20" s="5"/>
+      <c r="TKP20" s="5"/>
+      <c r="TKT20" s="5"/>
+      <c r="TKX20" s="5"/>
+      <c r="TLB20" s="5"/>
+      <c r="TLF20" s="5"/>
+      <c r="TLJ20" s="5"/>
+      <c r="TLN20" s="5"/>
+      <c r="TLR20" s="5"/>
+      <c r="TLV20" s="5"/>
+      <c r="TLZ20" s="5"/>
+      <c r="TMD20" s="5"/>
+      <c r="TMH20" s="5"/>
+      <c r="TML20" s="5"/>
+      <c r="TMP20" s="5"/>
+      <c r="TMT20" s="5"/>
+      <c r="TMX20" s="5"/>
+      <c r="TNB20" s="5"/>
+      <c r="TNF20" s="5"/>
+      <c r="TNJ20" s="5"/>
+      <c r="TNN20" s="5"/>
+      <c r="TNR20" s="5"/>
+      <c r="TNV20" s="5"/>
+      <c r="TNZ20" s="5"/>
+      <c r="TOD20" s="5"/>
+      <c r="TOH20" s="5"/>
+      <c r="TOL20" s="5"/>
+      <c r="TOP20" s="5"/>
+      <c r="TOT20" s="5"/>
+      <c r="TOX20" s="5"/>
+      <c r="TPB20" s="5"/>
+      <c r="TPF20" s="5"/>
+      <c r="TPJ20" s="5"/>
+      <c r="TPN20" s="5"/>
+      <c r="TPR20" s="5"/>
+      <c r="TPV20" s="5"/>
+      <c r="TPZ20" s="5"/>
+      <c r="TQD20" s="5"/>
+      <c r="TQH20" s="5"/>
+      <c r="TQL20" s="5"/>
+      <c r="TQP20" s="5"/>
+      <c r="TQT20" s="5"/>
+      <c r="TQX20" s="5"/>
+      <c r="TRB20" s="5"/>
+      <c r="TRF20" s="5"/>
+      <c r="TRJ20" s="5"/>
+      <c r="TRN20" s="5"/>
+      <c r="TRR20" s="5"/>
+      <c r="TRV20" s="5"/>
+      <c r="TRZ20" s="5"/>
+      <c r="TSD20" s="5"/>
+      <c r="TSH20" s="5"/>
+      <c r="TSL20" s="5"/>
+      <c r="TSP20" s="5"/>
+      <c r="TST20" s="5"/>
+      <c r="TSX20" s="5"/>
+      <c r="TTB20" s="5"/>
+      <c r="TTF20" s="5"/>
+      <c r="TTJ20" s="5"/>
+      <c r="TTN20" s="5"/>
+      <c r="TTR20" s="5"/>
+      <c r="TTV20" s="5"/>
+      <c r="TTZ20" s="5"/>
+      <c r="TUD20" s="5"/>
+      <c r="TUH20" s="5"/>
+      <c r="TUL20" s="5"/>
+      <c r="TUP20" s="5"/>
+      <c r="TUT20" s="5"/>
+      <c r="TUX20" s="5"/>
+      <c r="TVB20" s="5"/>
+      <c r="TVF20" s="5"/>
+      <c r="TVJ20" s="5"/>
+      <c r="TVN20" s="5"/>
+      <c r="TVR20" s="5"/>
+      <c r="TVV20" s="5"/>
+      <c r="TVZ20" s="5"/>
+      <c r="TWD20" s="5"/>
+      <c r="TWH20" s="5"/>
+      <c r="TWL20" s="5"/>
+      <c r="TWP20" s="5"/>
+      <c r="TWT20" s="5"/>
+      <c r="TWX20" s="5"/>
+      <c r="TXB20" s="5"/>
+      <c r="TXF20" s="5"/>
+      <c r="TXJ20" s="5"/>
+      <c r="TXN20" s="5"/>
+      <c r="TXR20" s="5"/>
+      <c r="TXV20" s="5"/>
+      <c r="TXZ20" s="5"/>
+      <c r="TYD20" s="5"/>
+      <c r="TYH20" s="5"/>
+      <c r="TYL20" s="5"/>
+      <c r="TYP20" s="5"/>
+      <c r="TYT20" s="5"/>
+      <c r="TYX20" s="5"/>
+      <c r="TZB20" s="5"/>
+      <c r="TZF20" s="5"/>
+      <c r="TZJ20" s="5"/>
+      <c r="TZN20" s="5"/>
+      <c r="TZR20" s="5"/>
+      <c r="TZV20" s="5"/>
+      <c r="TZZ20" s="5"/>
+      <c r="UAD20" s="5"/>
+      <c r="UAH20" s="5"/>
+      <c r="UAL20" s="5"/>
+      <c r="UAP20" s="5"/>
+      <c r="UAT20" s="5"/>
+      <c r="UAX20" s="5"/>
+      <c r="UBB20" s="5"/>
+      <c r="UBF20" s="5"/>
+      <c r="UBJ20" s="5"/>
+      <c r="UBN20" s="5"/>
+      <c r="UBR20" s="5"/>
+      <c r="UBV20" s="5"/>
+      <c r="UBZ20" s="5"/>
+      <c r="UCD20" s="5"/>
+      <c r="UCH20" s="5"/>
+      <c r="UCL20" s="5"/>
+      <c r="UCP20" s="5"/>
+      <c r="UCT20" s="5"/>
+      <c r="UCX20" s="5"/>
+      <c r="UDB20" s="5"/>
+      <c r="UDF20" s="5"/>
+      <c r="UDJ20" s="5"/>
+      <c r="UDN20" s="5"/>
+      <c r="UDR20" s="5"/>
+      <c r="UDV20" s="5"/>
+      <c r="UDZ20" s="5"/>
+      <c r="UED20" s="5"/>
+      <c r="UEH20" s="5"/>
+      <c r="UEL20" s="5"/>
+      <c r="UEP20" s="5"/>
+      <c r="UET20" s="5"/>
+      <c r="UEX20" s="5"/>
+      <c r="UFB20" s="5"/>
+      <c r="UFF20" s="5"/>
+      <c r="UFJ20" s="5"/>
+      <c r="UFN20" s="5"/>
+      <c r="UFR20" s="5"/>
+      <c r="UFV20" s="5"/>
+      <c r="UFZ20" s="5"/>
+      <c r="UGD20" s="5"/>
+      <c r="UGH20" s="5"/>
+      <c r="UGL20" s="5"/>
+      <c r="UGP20" s="5"/>
+      <c r="UGT20" s="5"/>
+      <c r="UGX20" s="5"/>
+      <c r="UHB20" s="5"/>
+      <c r="UHF20" s="5"/>
+      <c r="UHJ20" s="5"/>
+      <c r="UHN20" s="5"/>
+      <c r="UHR20" s="5"/>
+      <c r="UHV20" s="5"/>
+      <c r="UHZ20" s="5"/>
+      <c r="UID20" s="5"/>
+      <c r="UIH20" s="5"/>
+      <c r="UIL20" s="5"/>
+      <c r="UIP20" s="5"/>
+      <c r="UIT20" s="5"/>
+      <c r="UIX20" s="5"/>
+      <c r="UJB20" s="5"/>
+      <c r="UJF20" s="5"/>
+      <c r="UJJ20" s="5"/>
+      <c r="UJN20" s="5"/>
+      <c r="UJR20" s="5"/>
+      <c r="UJV20" s="5"/>
+      <c r="UJZ20" s="5"/>
+      <c r="UKD20" s="5"/>
+      <c r="UKH20" s="5"/>
+      <c r="UKL20" s="5"/>
+      <c r="UKP20" s="5"/>
+      <c r="UKT20" s="5"/>
+      <c r="UKX20" s="5"/>
+      <c r="ULB20" s="5"/>
+      <c r="ULF20" s="5"/>
+      <c r="ULJ20" s="5"/>
+      <c r="ULN20" s="5"/>
+      <c r="ULR20" s="5"/>
+      <c r="ULV20" s="5"/>
+      <c r="ULZ20" s="5"/>
+      <c r="UMD20" s="5"/>
+      <c r="UMH20" s="5"/>
+      <c r="UML20" s="5"/>
+      <c r="UMP20" s="5"/>
+      <c r="UMT20" s="5"/>
+      <c r="UMX20" s="5"/>
+      <c r="UNB20" s="5"/>
+      <c r="UNF20" s="5"/>
+      <c r="UNJ20" s="5"/>
+      <c r="UNN20" s="5"/>
+      <c r="UNR20" s="5"/>
+      <c r="UNV20" s="5"/>
+      <c r="UNZ20" s="5"/>
+      <c r="UOD20" s="5"/>
+      <c r="UOH20" s="5"/>
+      <c r="UOL20" s="5"/>
+      <c r="UOP20" s="5"/>
+      <c r="UOT20" s="5"/>
+      <c r="UOX20" s="5"/>
+      <c r="UPB20" s="5"/>
+      <c r="UPF20" s="5"/>
+      <c r="UPJ20" s="5"/>
+      <c r="UPN20" s="5"/>
+      <c r="UPR20" s="5"/>
+      <c r="UPV20" s="5"/>
+      <c r="UPZ20" s="5"/>
+      <c r="UQD20" s="5"/>
+      <c r="UQH20" s="5"/>
+      <c r="UQL20" s="5"/>
+      <c r="UQP20" s="5"/>
+      <c r="UQT20" s="5"/>
+      <c r="UQX20" s="5"/>
+      <c r="URB20" s="5"/>
+      <c r="URF20" s="5"/>
+      <c r="URJ20" s="5"/>
+      <c r="URN20" s="5"/>
+      <c r="URR20" s="5"/>
+      <c r="URV20" s="5"/>
+      <c r="URZ20" s="5"/>
+      <c r="USD20" s="5"/>
+      <c r="USH20" s="5"/>
+      <c r="USL20" s="5"/>
+      <c r="USP20" s="5"/>
+      <c r="UST20" s="5"/>
+      <c r="USX20" s="5"/>
+      <c r="UTB20" s="5"/>
+      <c r="UTF20" s="5"/>
+      <c r="UTJ20" s="5"/>
+      <c r="UTN20" s="5"/>
+      <c r="UTR20" s="5"/>
+      <c r="UTV20" s="5"/>
+      <c r="UTZ20" s="5"/>
+      <c r="UUD20" s="5"/>
+      <c r="UUH20" s="5"/>
+      <c r="UUL20" s="5"/>
+      <c r="UUP20" s="5"/>
+      <c r="UUT20" s="5"/>
+      <c r="UUX20" s="5"/>
+      <c r="UVB20" s="5"/>
+      <c r="UVF20" s="5"/>
+      <c r="UVJ20" s="5"/>
+      <c r="UVN20" s="5"/>
+      <c r="UVR20" s="5"/>
+      <c r="UVV20" s="5"/>
+      <c r="UVZ20" s="5"/>
+      <c r="UWD20" s="5"/>
+      <c r="UWH20" s="5"/>
+      <c r="UWL20" s="5"/>
+      <c r="UWP20" s="5"/>
+      <c r="UWT20" s="5"/>
+      <c r="UWX20" s="5"/>
+      <c r="UXB20" s="5"/>
+      <c r="UXF20" s="5"/>
+      <c r="UXJ20" s="5"/>
+      <c r="UXN20" s="5"/>
+      <c r="UXR20" s="5"/>
+      <c r="UXV20" s="5"/>
+      <c r="UXZ20" s="5"/>
+      <c r="UYD20" s="5"/>
+      <c r="UYH20" s="5"/>
+      <c r="UYL20" s="5"/>
+      <c r="UYP20" s="5"/>
+      <c r="UYT20" s="5"/>
+      <c r="UYX20" s="5"/>
+      <c r="UZB20" s="5"/>
+      <c r="UZF20" s="5"/>
+      <c r="UZJ20" s="5"/>
+      <c r="UZN20" s="5"/>
+      <c r="UZR20" s="5"/>
+      <c r="UZV20" s="5"/>
+      <c r="UZZ20" s="5"/>
+      <c r="VAD20" s="5"/>
+      <c r="VAH20" s="5"/>
+      <c r="VAL20" s="5"/>
+      <c r="VAP20" s="5"/>
+      <c r="VAT20" s="5"/>
+      <c r="VAX20" s="5"/>
+      <c r="VBB20" s="5"/>
+      <c r="VBF20" s="5"/>
+      <c r="VBJ20" s="5"/>
+      <c r="VBN20" s="5"/>
+      <c r="VBR20" s="5"/>
+      <c r="VBV20" s="5"/>
+      <c r="VBZ20" s="5"/>
+      <c r="VCD20" s="5"/>
+      <c r="VCH20" s="5"/>
+      <c r="VCL20" s="5"/>
+      <c r="VCP20" s="5"/>
+      <c r="VCT20" s="5"/>
+      <c r="VCX20" s="5"/>
+      <c r="VDB20" s="5"/>
+      <c r="VDF20" s="5"/>
+      <c r="VDJ20" s="5"/>
+      <c r="VDN20" s="5"/>
+      <c r="VDR20" s="5"/>
+      <c r="VDV20" s="5"/>
+      <c r="VDZ20" s="5"/>
+      <c r="VED20" s="5"/>
+      <c r="VEH20" s="5"/>
+      <c r="VEL20" s="5"/>
+      <c r="VEP20" s="5"/>
+      <c r="VET20" s="5"/>
+      <c r="VEX20" s="5"/>
+      <c r="VFB20" s="5"/>
+      <c r="VFF20" s="5"/>
+      <c r="VFJ20" s="5"/>
+      <c r="VFN20" s="5"/>
+      <c r="VFR20" s="5"/>
+      <c r="VFV20" s="5"/>
+      <c r="VFZ20" s="5"/>
+      <c r="VGD20" s="5"/>
+      <c r="VGH20" s="5"/>
+      <c r="VGL20" s="5"/>
+      <c r="VGP20" s="5"/>
+      <c r="VGT20" s="5"/>
+      <c r="VGX20" s="5"/>
+      <c r="VHB20" s="5"/>
+      <c r="VHF20" s="5"/>
+      <c r="VHJ20" s="5"/>
+      <c r="VHN20" s="5"/>
+      <c r="VHR20" s="5"/>
+      <c r="VHV20" s="5"/>
+      <c r="VHZ20" s="5"/>
+      <c r="VID20" s="5"/>
+      <c r="VIH20" s="5"/>
+      <c r="VIL20" s="5"/>
+      <c r="VIP20" s="5"/>
+      <c r="VIT20" s="5"/>
+      <c r="VIX20" s="5"/>
+      <c r="VJB20" s="5"/>
+      <c r="VJF20" s="5"/>
+      <c r="VJJ20" s="5"/>
+      <c r="VJN20" s="5"/>
+      <c r="VJR20" s="5"/>
+      <c r="VJV20" s="5"/>
+      <c r="VJZ20" s="5"/>
+      <c r="VKD20" s="5"/>
+      <c r="VKH20" s="5"/>
+      <c r="VKL20" s="5"/>
+      <c r="VKP20" s="5"/>
+      <c r="VKT20" s="5"/>
+      <c r="VKX20" s="5"/>
+      <c r="VLB20" s="5"/>
+      <c r="VLF20" s="5"/>
+      <c r="VLJ20" s="5"/>
+      <c r="VLN20" s="5"/>
+      <c r="VLR20" s="5"/>
+      <c r="VLV20" s="5"/>
+      <c r="VLZ20" s="5"/>
+      <c r="VMD20" s="5"/>
+      <c r="VMH20" s="5"/>
+      <c r="VML20" s="5"/>
+      <c r="VMP20" s="5"/>
+      <c r="VMT20" s="5"/>
+      <c r="VMX20" s="5"/>
+      <c r="VNB20" s="5"/>
+      <c r="VNF20" s="5"/>
+      <c r="VNJ20" s="5"/>
+      <c r="VNN20" s="5"/>
+      <c r="VNR20" s="5"/>
+      <c r="VNV20" s="5"/>
+      <c r="VNZ20" s="5"/>
+      <c r="VOD20" s="5"/>
+      <c r="VOH20" s="5"/>
+      <c r="VOL20" s="5"/>
+      <c r="VOP20" s="5"/>
+      <c r="VOT20" s="5"/>
+      <c r="VOX20" s="5"/>
+      <c r="VPB20" s="5"/>
+      <c r="VPF20" s="5"/>
+      <c r="VPJ20" s="5"/>
+      <c r="VPN20" s="5"/>
+      <c r="VPR20" s="5"/>
+      <c r="VPV20" s="5"/>
+      <c r="VPZ20" s="5"/>
+      <c r="VQD20" s="5"/>
+      <c r="VQH20" s="5"/>
+      <c r="VQL20" s="5"/>
+      <c r="VQP20" s="5"/>
+      <c r="VQT20" s="5"/>
+      <c r="VQX20" s="5"/>
+      <c r="VRB20" s="5"/>
+      <c r="VRF20" s="5"/>
+      <c r="VRJ20" s="5"/>
+      <c r="VRN20" s="5"/>
+      <c r="VRR20" s="5"/>
+      <c r="VRV20" s="5"/>
+      <c r="VRZ20" s="5"/>
+      <c r="VSD20" s="5"/>
+      <c r="VSH20" s="5"/>
+      <c r="VSL20" s="5"/>
+      <c r="VSP20" s="5"/>
+      <c r="VST20" s="5"/>
+      <c r="VSX20" s="5"/>
+      <c r="VTB20" s="5"/>
+      <c r="VTF20" s="5"/>
+      <c r="VTJ20" s="5"/>
+      <c r="VTN20" s="5"/>
+      <c r="VTR20" s="5"/>
+      <c r="VTV20" s="5"/>
+      <c r="VTZ20" s="5"/>
+      <c r="VUD20" s="5"/>
+      <c r="VUH20" s="5"/>
+      <c r="VUL20" s="5"/>
+      <c r="VUP20" s="5"/>
+      <c r="VUT20" s="5"/>
+      <c r="VUX20" s="5"/>
+      <c r="VVB20" s="5"/>
+      <c r="VVF20" s="5"/>
+      <c r="VVJ20" s="5"/>
+      <c r="VVN20" s="5"/>
+      <c r="VVR20" s="5"/>
+      <c r="VVV20" s="5"/>
+      <c r="VVZ20" s="5"/>
+      <c r="VWD20" s="5"/>
+      <c r="VWH20" s="5"/>
+      <c r="VWL20" s="5"/>
+      <c r="VWP20" s="5"/>
+      <c r="VWT20" s="5"/>
+      <c r="VWX20" s="5"/>
+      <c r="VXB20" s="5"/>
+      <c r="VXF20" s="5"/>
+      <c r="VXJ20" s="5"/>
+      <c r="VXN20" s="5"/>
+      <c r="VXR20" s="5"/>
+      <c r="VXV20" s="5"/>
+      <c r="VXZ20" s="5"/>
+      <c r="VYD20" s="5"/>
+      <c r="VYH20" s="5"/>
+      <c r="VYL20" s="5"/>
+      <c r="VYP20" s="5"/>
+      <c r="VYT20" s="5"/>
+      <c r="VYX20" s="5"/>
+      <c r="VZB20" s="5"/>
+      <c r="VZF20" s="5"/>
+      <c r="VZJ20" s="5"/>
+      <c r="VZN20" s="5"/>
+      <c r="VZR20" s="5"/>
+      <c r="VZV20" s="5"/>
+      <c r="VZZ20" s="5"/>
+      <c r="WAD20" s="5"/>
+      <c r="WAH20" s="5"/>
+      <c r="WAL20" s="5"/>
+      <c r="WAP20" s="5"/>
+      <c r="WAT20" s="5"/>
+      <c r="WAX20" s="5"/>
+      <c r="WBB20" s="5"/>
+      <c r="WBF20" s="5"/>
+      <c r="WBJ20" s="5"/>
+      <c r="WBN20" s="5"/>
+      <c r="WBR20" s="5"/>
+      <c r="WBV20" s="5"/>
+      <c r="WBZ20" s="5"/>
+      <c r="WCD20" s="5"/>
+      <c r="WCH20" s="5"/>
+      <c r="WCL20" s="5"/>
+      <c r="WCP20" s="5"/>
+      <c r="WCT20" s="5"/>
+      <c r="WCX20" s="5"/>
+      <c r="WDB20" s="5"/>
+      <c r="WDF20" s="5"/>
+      <c r="WDJ20" s="5"/>
+      <c r="WDN20" s="5"/>
+      <c r="WDR20" s="5"/>
+      <c r="WDV20" s="5"/>
+      <c r="WDZ20" s="5"/>
+      <c r="WED20" s="5"/>
+      <c r="WEH20" s="5"/>
+      <c r="WEL20" s="5"/>
+      <c r="WEP20" s="5"/>
+      <c r="WET20" s="5"/>
+      <c r="WEX20" s="5"/>
+      <c r="WFB20" s="5"/>
+      <c r="WFF20" s="5"/>
+      <c r="WFJ20" s="5"/>
+      <c r="WFN20" s="5"/>
+      <c r="WFR20" s="5"/>
+      <c r="WFV20" s="5"/>
+      <c r="WFZ20" s="5"/>
+      <c r="WGD20" s="5"/>
+      <c r="WGH20" s="5"/>
+      <c r="WGL20" s="5"/>
+      <c r="WGP20" s="5"/>
+      <c r="WGT20" s="5"/>
+      <c r="WGX20" s="5"/>
+      <c r="WHB20" s="5"/>
+      <c r="WHF20" s="5"/>
+      <c r="WHJ20" s="5"/>
+      <c r="WHN20" s="5"/>
+      <c r="WHR20" s="5"/>
+      <c r="WHV20" s="5"/>
+      <c r="WHZ20" s="5"/>
+      <c r="WID20" s="5"/>
+      <c r="WIH20" s="5"/>
+      <c r="WIL20" s="5"/>
+      <c r="WIP20" s="5"/>
+      <c r="WIT20" s="5"/>
+      <c r="WIX20" s="5"/>
+      <c r="WJB20" s="5"/>
+      <c r="WJF20" s="5"/>
+      <c r="WJJ20" s="5"/>
+      <c r="WJN20" s="5"/>
+      <c r="WJR20" s="5"/>
+      <c r="WJV20" s="5"/>
+      <c r="WJZ20" s="5"/>
+      <c r="WKD20" s="5"/>
+      <c r="WKH20" s="5"/>
+      <c r="WKL20" s="5"/>
+      <c r="WKP20" s="5"/>
+      <c r="WKT20" s="5"/>
+      <c r="WKX20" s="5"/>
+      <c r="WLB20" s="5"/>
+      <c r="WLF20" s="5"/>
+      <c r="WLJ20" s="5"/>
+      <c r="WLN20" s="5"/>
+      <c r="WLR20" s="5"/>
+      <c r="WLV20" s="5"/>
+      <c r="WLZ20" s="5"/>
+      <c r="WMD20" s="5"/>
+      <c r="WMH20" s="5"/>
+      <c r="WML20" s="5"/>
+      <c r="WMP20" s="5"/>
+      <c r="WMT20" s="5"/>
+      <c r="WMX20" s="5"/>
+      <c r="WNB20" s="5"/>
+      <c r="WNF20" s="5"/>
+      <c r="WNJ20" s="5"/>
+      <c r="WNN20" s="5"/>
+      <c r="WNR20" s="5"/>
+      <c r="WNV20" s="5"/>
+      <c r="WNZ20" s="5"/>
+      <c r="WOD20" s="5"/>
+      <c r="WOH20" s="5"/>
+      <c r="WOL20" s="5"/>
+      <c r="WOP20" s="5"/>
+      <c r="WOT20" s="5"/>
+      <c r="WOX20" s="5"/>
+      <c r="WPB20" s="5"/>
+      <c r="WPF20" s="5"/>
+      <c r="WPJ20" s="5"/>
+      <c r="WPN20" s="5"/>
+      <c r="WPR20" s="5"/>
+      <c r="WPV20" s="5"/>
+      <c r="WPZ20" s="5"/>
+      <c r="WQD20" s="5"/>
+      <c r="WQH20" s="5"/>
+      <c r="WQL20" s="5"/>
+      <c r="WQP20" s="5"/>
+      <c r="WQT20" s="5"/>
+      <c r="WQX20" s="5"/>
+      <c r="WRB20" s="5"/>
+      <c r="WRF20" s="5"/>
+      <c r="WRJ20" s="5"/>
+      <c r="WRN20" s="5"/>
+      <c r="WRR20" s="5"/>
+      <c r="WRV20" s="5"/>
+      <c r="WRZ20" s="5"/>
+      <c r="WSD20" s="5"/>
+      <c r="WSH20" s="5"/>
+      <c r="WSL20" s="5"/>
+      <c r="WSP20" s="5"/>
+      <c r="WST20" s="5"/>
+      <c r="WSX20" s="5"/>
+      <c r="WTB20" s="5"/>
+      <c r="WTF20" s="5"/>
+      <c r="WTJ20" s="5"/>
+      <c r="WTN20" s="5"/>
+      <c r="WTR20" s="5"/>
+      <c r="WTV20" s="5"/>
+      <c r="WTZ20" s="5"/>
+      <c r="WUD20" s="5"/>
+      <c r="WUH20" s="5"/>
+      <c r="WUL20" s="5"/>
+      <c r="WUP20" s="5"/>
+      <c r="WUT20" s="5"/>
+      <c r="WUX20" s="5"/>
+      <c r="WVB20" s="5"/>
+      <c r="WVF20" s="5"/>
+      <c r="WVJ20" s="5"/>
+      <c r="WVN20" s="5"/>
+      <c r="WVR20" s="5"/>
+      <c r="WVV20" s="5"/>
+      <c r="WVZ20" s="5"/>
+      <c r="WWD20" s="5"/>
+      <c r="WWH20" s="5"/>
+      <c r="WWL20" s="5"/>
+      <c r="WWP20" s="5"/>
+      <c r="WWT20" s="5"/>
+      <c r="WWX20" s="5"/>
+      <c r="WXB20" s="5"/>
+      <c r="WXF20" s="5"/>
+      <c r="WXJ20" s="5"/>
+      <c r="WXN20" s="5"/>
+      <c r="WXR20" s="5"/>
+      <c r="WXV20" s="5"/>
+      <c r="WXZ20" s="5"/>
+      <c r="WYD20" s="5"/>
+      <c r="WYH20" s="5"/>
+      <c r="WYL20" s="5"/>
+      <c r="WYP20" s="5"/>
+      <c r="WYT20" s="5"/>
+      <c r="WYX20" s="5"/>
+      <c r="WZB20" s="5"/>
+      <c r="WZF20" s="5"/>
+      <c r="WZJ20" s="5"/>
+      <c r="WZN20" s="5"/>
+      <c r="WZR20" s="5"/>
+      <c r="WZV20" s="5"/>
+      <c r="WZZ20" s="5"/>
+      <c r="XAD20" s="5"/>
+      <c r="XAH20" s="5"/>
+      <c r="XAL20" s="5"/>
+      <c r="XAP20" s="5"/>
+      <c r="XAT20" s="5"/>
+      <c r="XAX20" s="5"/>
+      <c r="XBB20" s="5"/>
+      <c r="XBF20" s="5"/>
+      <c r="XBJ20" s="5"/>
+      <c r="XBN20" s="5"/>
+      <c r="XBR20" s="5"/>
+      <c r="XBV20" s="5"/>
+      <c r="XBZ20" s="5"/>
+      <c r="XCD20" s="5"/>
+      <c r="XCH20" s="5"/>
+      <c r="XCL20" s="5"/>
+      <c r="XCP20" s="5"/>
+      <c r="XCT20" s="5"/>
+      <c r="XCX20" s="5"/>
+      <c r="XDB20" s="5"/>
+      <c r="XDF20" s="5"/>
+      <c r="XDJ20" s="5"/>
+      <c r="XDN20" s="5"/>
+      <c r="XDR20" s="5"/>
+      <c r="XDV20" s="5"/>
+      <c r="XDZ20" s="5"/>
+      <c r="XED20" s="5"/>
+      <c r="XEH20" s="5"/>
+      <c r="XEL20" s="5"/>
+      <c r="XEP20" s="5"/>
+      <c r="XET20" s="5"/>
+      <c r="XEX20" s="5"/>
+      <c r="XFB20" s="5"/>
     </row>
     <row r="21" spans="2:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
       <c r="B21" s="2" t="s">
@@ -42006,6 +42018,7 @@
         <v>25</v>
       </c>
     </row>
+    <row r="32" spans="2:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" s="7" customFormat="1"/>
     <row r="33" spans="2:12">
       <c r="B33" t="s">
         <v>38</v>
@@ -42033,6 +42046,40 @@
         <v>25</v>
       </c>
     </row>
+    <row r="42" spans="2:12" s="7" customFormat="1"/>
+    <row r="43" spans="2:12">
+      <c r="B43" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12">
+      <c r="B44" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12">
+      <c r="B45" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="J1:P1"/>

--- a/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0A8C6C-86C0-4DF8-9F2E-201F257CDEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD6625F-42F7-4E51-8B23-AD18D39CA04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,11 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -194,9 +199,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>(list#sep=;),int</t>
-  </si>
-  <si>
     <t>stacking</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -246,6 +248,10 @@
   </si>
   <si>
     <t>ALApplyEffect</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(array#sep=;),int</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -835,7 +841,7 @@
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="P8" s="2"/>
     </row>
@@ -859,11 +865,11 @@
     </row>
     <row r="11" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
       <c r="B11" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>43</v>
@@ -4966,7 +4972,7 @@
       <c r="B12" s="3"/>
       <c r="F12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>43</v>
@@ -9069,7 +9075,7 @@
       <c r="B13" s="3"/>
       <c r="F13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>43</v>
@@ -13172,7 +13178,7 @@
       <c r="B14" s="3"/>
       <c r="F14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>43</v>
@@ -17275,7 +17281,7 @@
       <c r="B15" s="3"/>
       <c r="F15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>43</v>
@@ -21378,7 +21384,7 @@
       <c r="B16" s="3"/>
       <c r="F16" s="2"/>
       <c r="J16" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>43</v>
@@ -25481,7 +25487,7 @@
       <c r="B17" s="3"/>
       <c r="F17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>26</v>
@@ -29584,7 +29590,7 @@
       <c r="B18" s="3"/>
       <c r="F18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>26</v>
@@ -33687,10 +33693,10 @@
       <c r="B19" s="3"/>
       <c r="F19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="N19" s="2"/>
       <c r="R19" s="2"/>
@@ -42049,15 +42055,15 @@
     <row r="42" spans="2:12" s="7" customFormat="1"/>
     <row r="43" spans="2:12">
       <c r="B43" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="44" spans="2:12">
       <c r="B44" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>24</v>
@@ -42068,16 +42074,16 @@
     </row>
     <row r="45" spans="2:12">
       <c r="B45" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A8BFEAC-3D71-48D4-BE49-617C98C89972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="66">
   <si>
     <t>##var</t>
   </si>
@@ -103,27 +104,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>value</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>float</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>bool</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>x</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>y</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>z</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -162,19 +147,7 @@
     <t>MmcLogic</t>
   </si>
   <si>
-    <t>k</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>b</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>MMCScalableFloat</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>timeUnit</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -182,59 +155,11 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>time</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>period</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>effects</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>firstTrigger</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>stacking</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>stackingType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>stackCode</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>limitCount</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>durationRefreshPolicy</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>periodResetPolicy</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>expirationPolicy</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>denyOverflowApplication</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>clearStackOnOverflow</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>overflowEffects</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -257,11 +182,99 @@
     <t>ResetStartTimeWhenActivated</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>ALMove</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RotationOffset</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Value</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>K</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Duration</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Y</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Z</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TimeUnit</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Time</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Effects</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FirstTrigger</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StackingType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StackCode</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>LimitCount</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DurationRefreshPolicy</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>PeriodResetPolicy</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DenyOverflowApplication</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExpirationPolicy</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClearStackOnOverflow</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>OverflowEffects</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="8">
     <font>
       <sz val="11"/>
@@ -675,18 +688,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:XFB46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:XFB47"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="2" max="2" width="20.625" customWidth="1"/>
-    <col min="3" max="3" width="14.625" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="6" width="12.25" customWidth="1"/>
+    <col min="5" max="6" width="12.21875" customWidth="1"/>
     <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="21.5" customWidth="1"/>
-    <col min="11" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="10.375" customWidth="1"/>
+    <col min="10" max="10" width="21.44140625" customWidth="1"/>
+    <col min="11" max="12" width="13.44140625" customWidth="1"/>
+    <col min="13" max="13" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
@@ -784,36 +797,36 @@
     </row>
     <row r="4" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
       <c r="B4" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="P4" s="2"/>
     </row>
     <row r="5" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
       <c r="B5" s="2"/>
       <c r="J5" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="P5" s="2"/>
     </row>
     <row r="6" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
       <c r="B6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P6" s="2"/>
     </row>
@@ -837,36 +850,36 @@
     </row>
     <row r="8" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
       <c r="B8" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="K8" s="2"/>
       <c r="L8" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="P8" s="2"/>
     </row>
     <row r="9" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
       <c r="B9" s="2"/>
       <c r="J9" s="2" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="K9" s="2"/>
       <c r="L9" s="2" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="P9" s="2"/>
     </row>
     <row r="10" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
       <c r="B10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P10" s="2"/>
     </row>
@@ -879,14 +892,14 @@
     </row>
     <row r="12" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
       <c r="B12" s="2" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="N12" s="2"/>
       <c r="R12" s="2"/>
@@ -4986,10 +4999,10 @@
       <c r="B13" s="3"/>
       <c r="F13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="N13" s="2"/>
       <c r="R13" s="2"/>
@@ -9089,10 +9102,10 @@
       <c r="B14" s="3"/>
       <c r="F14" s="2"/>
       <c r="J14" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="N14" s="2"/>
       <c r="R14" s="2"/>
@@ -13192,10 +13205,10 @@
       <c r="B15" s="3"/>
       <c r="F15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="N15" s="2"/>
       <c r="R15" s="2"/>
@@ -17295,10 +17308,10 @@
       <c r="B16" s="3"/>
       <c r="F16" s="2"/>
       <c r="J16" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="N16" s="2"/>
       <c r="R16" s="2"/>
@@ -21398,10 +21411,10 @@
       <c r="B17" s="3"/>
       <c r="F17" s="2"/>
       <c r="J17" s="2" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="N17" s="2"/>
       <c r="R17" s="2"/>
@@ -25501,10 +25514,10 @@
       <c r="B18" s="3"/>
       <c r="F18" s="2"/>
       <c r="J18" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N18" s="2"/>
       <c r="R18" s="2"/>
@@ -29604,10 +29617,10 @@
       <c r="B19" s="3"/>
       <c r="F19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N19" s="2"/>
       <c r="R19" s="2"/>
@@ -33707,10 +33720,10 @@
       <c r="B20" s="3"/>
       <c r="F20" s="2"/>
       <c r="J20" s="2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="N20" s="2"/>
       <c r="R20" s="2"/>
@@ -41907,7 +41920,7 @@
     </row>
     <row r="22" spans="2:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
       <c r="B22" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E22" s="2"/>
       <c r="J22" s="2"/>
@@ -41915,14 +41928,14 @@
     </row>
     <row r="23" spans="2:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
       <c r="B23" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E23" s="2"/>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>23</v>
@@ -41930,14 +41943,14 @@
     </row>
     <row r="24" spans="2:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
       <c r="B24" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E24" s="2"/>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>23</v>
@@ -41948,139 +41961,139 @@
       <c r="C25" s="2"/>
       <c r="E25" s="2"/>
       <c r="J25" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="2:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
       <c r="B26" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E26" s="2"/>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="2:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" ht="15" customHeight="1">
       <c r="B27" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E27" s="2"/>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28" spans="2:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" ht="15" customHeight="1">
       <c r="B28" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E28" s="2"/>
       <c r="J28" s="2" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="2:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
       <c r="J29" s="2" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="2:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E30" s="2"/>
       <c r="J30" s="2" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="2:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
       <c r="J31" s="2" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="2:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382">
       <c r="J32" s="2" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="2:12" s="7" customFormat="1"/>
     <row r="34" spans="2:12">
       <c r="B34" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="2:12">
       <c r="B35" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="C35" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="2:12">
       <c r="J36" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="2:12" s="7" customFormat="1"/>
     <row r="44" spans="2:12">
       <c r="B44" s="2" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
     </row>
     <row r="45" spans="2:12">
       <c r="B45" s="2" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>23</v>
@@ -42088,16 +42101,30 @@
     </row>
     <row r="46" spans="2:12">
       <c r="B46" s="2" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>61</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12">
+      <c r="B47" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED668CB5-8508-48AF-9A13-B35766196CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1A263E-708F-4F9B-B55B-D9C50935261A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1A263E-708F-4F9B-B55B-D9C50935261A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512DC72A-5691-4217-B5A1-CC2315303BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -196,6 +196,57 @@
   </si>
   <si>
     <t>Z</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ALTimeline</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ManualEndAbility</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FrameCount</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能时长</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否需要手动结束</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tracks</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(array#sep=;),Track</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AbilityTask</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TaskDoCost</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TaskDebug</t>
+  </si>
+  <si>
+    <t>Text</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -580,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.6640625" customWidth="1"/>
@@ -686,32 +737,18 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="L4" s="2"/>
-    </row>
+    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="J5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="J5" s="2"/>
+      <c r="L5" s="2"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>26</v>
@@ -725,34 +762,34 @@
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="E7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>26</v>
-      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
       <c r="E8" s="2"/>
       <c r="J8" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>26</v>
@@ -762,50 +799,57 @@
         <v>41</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="2"/>
       <c r="J10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="J11" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="J11" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="2"/>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="J12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>24</v>
@@ -813,63 +857,57 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="J14" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B16" t="s">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J15" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C18" t="s">
         <v>33</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="J18" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="J18" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B26" s="2" t="s">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>35</v>
@@ -878,21 +916,99 @@
         <v>41</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="L29" s="2" t="s">
+      <c r="L30" s="2" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J33" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B37" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B38" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>59</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512DC72A-5691-4217-B5A1-CC2315303BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06900F03-0842-46ED-91A6-DE716EB41DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="59">
   <si>
     <t>##var</t>
   </si>
@@ -203,38 +203,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>ManualEndAbility</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>bool</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>FrameCount</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能时长</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否需要手动结束</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tracks</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>(array#sep=;),Track</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>AbilityTask</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -243,10 +215,31 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>Text</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TimelineID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>TaskDebug</t>
-  </si>
-  <si>
-    <t>Text</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartTimePoint</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EndTimePoint</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>起始时间点</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>结束时间点</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -631,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P39"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.6640625" customWidth="1"/>
@@ -955,59 +948,68 @@
         <v>35</v>
       </c>
       <c r="J31" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N31" s="2"/>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="N32" s="2"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J33" s="2"/>
+      <c r="L33" s="2"/>
+    </row>
+    <row r="36" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B37" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B38" s="2"/>
+      <c r="J38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B39" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B40" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J40" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="L31" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J32" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="L32" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="J33" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="36" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B37" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B38" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
-        <v>59</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L39" s="2" t="s">
+      <c r="L40" s="2" t="s">
         <v>23</v>
       </c>
     </row>

--- a/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06900F03-0842-46ED-91A6-DE716EB41DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -224,29 +223,13 @@
   </si>
   <si>
     <t>TaskDebug</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>StartTimePoint</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>EndTimePoint</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>起始时间点</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>结束时间点</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -623,21 +606,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="20.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" customWidth="1"/>
+    <col min="2" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="14.625" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="6" width="12.21875" customWidth="1"/>
+    <col min="5" max="6" width="12.25" customWidth="1"/>
     <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="21.44140625" customWidth="1"/>
-    <col min="11" max="12" width="13.44140625" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" customWidth="1"/>
+    <col min="10" max="10" width="21.5" customWidth="1"/>
+    <col min="11" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="13" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -675,7 +658,7 @@
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -701,7 +684,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -730,8 +713,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>26</v>
       </c>
@@ -739,7 +722,7 @@
       <c r="J5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>27</v>
       </c>
@@ -754,7 +737,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
@@ -769,7 +752,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="E8" s="2"/>
@@ -780,7 +763,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
@@ -795,7 +778,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
@@ -810,7 +793,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>30</v>
       </c>
@@ -825,7 +808,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J12" s="2" t="s">
         <v>46</v>
       </c>
@@ -833,7 +816,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>31</v>
       </c>
@@ -848,7 +831,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J14" s="2" t="s">
         <v>46</v>
       </c>
@@ -856,7 +839,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J15" s="2" t="s">
         <v>47</v>
       </c>
@@ -864,13 +847,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>34</v>
       </c>
@@ -884,7 +867,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="J19" s="2" t="s">
         <v>43</v>
       </c>
@@ -892,13 +875,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>36</v>
       </c>
@@ -912,7 +895,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>37</v>
       </c>
@@ -926,7 +909,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>39</v>
       </c>
@@ -940,7 +923,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>48</v>
       </c>
@@ -955,61 +938,43 @@
       </c>
       <c r="N31" s="2"/>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="J32" s="2"/>
       <c r="L32" s="2"/>
       <c r="N32" s="2"/>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="J33" s="2"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="36" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J37" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B38" s="2"/>
-      <c r="J38" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="N37" s="2"/>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J40" s="2" t="s">
+      <c r="J39" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="L40" s="2" t="s">
+      <c r="L39" s="2" t="s">
         <v>23</v>
       </c>
     </row>

--- a/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E95E62-C440-43E0-8942-C11BF7BCB4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="54">
   <si>
     <t>##var</t>
   </si>
@@ -211,10 +212,6 @@
   </si>
   <si>
     <t>TaskDoCost</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Text</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -229,7 +226,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -606,21 +603,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.625" customWidth="1"/>
-    <col min="3" max="3" width="14.625" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="6" width="12.25" customWidth="1"/>
+    <col min="5" max="6" width="12.21875" customWidth="1"/>
     <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="21.5" customWidth="1"/>
-    <col min="11" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="10.375" customWidth="1"/>
+    <col min="10" max="10" width="21.44140625" customWidth="1"/>
+    <col min="11" max="12" width="13.44140625" customWidth="1"/>
+    <col min="13" max="13" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -658,7 +655,7 @@
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -684,7 +681,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -713,8 +710,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>26</v>
       </c>
@@ -722,7 +719,7 @@
       <c r="J5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>27</v>
       </c>
@@ -737,7 +734,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
@@ -752,7 +749,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="E8" s="2"/>
@@ -763,7 +760,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
@@ -778,7 +775,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
@@ -793,7 +790,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>30</v>
       </c>
@@ -808,7 +805,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="J12" s="2" t="s">
         <v>46</v>
       </c>
@@ -816,7 +813,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
         <v>31</v>
       </c>
@@ -831,7 +828,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="J14" s="2" t="s">
         <v>46</v>
       </c>
@@ -839,7 +836,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="J15" s="2" t="s">
         <v>47</v>
       </c>
@@ -847,13 +844,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>34</v>
       </c>
@@ -867,7 +864,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="J19" s="2" t="s">
         <v>43</v>
       </c>
@@ -875,13 +872,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
         <v>36</v>
       </c>
@@ -895,7 +892,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>37</v>
       </c>
@@ -909,7 +906,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
         <v>39</v>
       </c>
@@ -923,7 +920,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
         <v>48</v>
       </c>
@@ -931,24 +928,24 @@
         <v>35</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>49</v>
       </c>
       <c r="N31" s="2"/>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="J32" s="2"/>
       <c r="L32" s="2"/>
       <c r="N32" s="2"/>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="J33" s="2"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="36" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
         <v>50</v>
       </c>
@@ -956,7 +953,7 @@
       <c r="L37" s="2"/>
       <c r="N37" s="2"/>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
         <v>51</v>
       </c>
@@ -964,15 +961,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>50</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>23</v>

--- a/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E95E62-C440-43E0-8942-C11BF7BCB4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="56">
   <si>
     <t>##var</t>
   </si>
@@ -220,13 +219,21 @@
   </si>
   <si>
     <t>TaskDebug</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TaskPlayCue</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Cues</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -603,21 +610,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P40"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="20.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" customWidth="1"/>
+    <col min="2" max="2" width="20.625" customWidth="1"/>
+    <col min="3" max="3" width="14.625" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="6" width="12.21875" customWidth="1"/>
+    <col min="5" max="6" width="12.25" customWidth="1"/>
     <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="21.44140625" customWidth="1"/>
-    <col min="11" max="12" width="13.44140625" customWidth="1"/>
-    <col min="13" max="13" width="10.33203125" customWidth="1"/>
+    <col min="10" max="10" width="21.5" customWidth="1"/>
+    <col min="11" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="13" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -655,7 +662,7 @@
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -681,7 +688,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -710,8 +717,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>26</v>
       </c>
@@ -719,7 +726,7 @@
       <c r="J5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>27</v>
       </c>
@@ -734,7 +741,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
@@ -749,7 +756,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="E8" s="2"/>
@@ -760,7 +767,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
@@ -775,7 +782,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>29</v>
       </c>
@@ -790,7 +797,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>30</v>
       </c>
@@ -805,7 +812,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J12" s="2" t="s">
         <v>46</v>
       </c>
@@ -813,7 +820,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>31</v>
       </c>
@@ -828,7 +835,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J14" s="2" t="s">
         <v>46</v>
       </c>
@@ -836,7 +843,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="J15" s="2" t="s">
         <v>47</v>
       </c>
@@ -844,13 +851,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>34</v>
       </c>
@@ -864,7 +871,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="J19" s="2" t="s">
         <v>43</v>
       </c>
@@ -872,13 +879,13 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>36</v>
       </c>
@@ -892,7 +899,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>37</v>
       </c>
@@ -906,7 +913,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>39</v>
       </c>
@@ -920,7 +927,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>48</v>
       </c>
@@ -935,17 +942,17 @@
       </c>
       <c r="N31" s="2"/>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="J32" s="2"/>
       <c r="L32" s="2"/>
       <c r="N32" s="2"/>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="J33" s="2"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="36" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
         <v>50</v>
       </c>
@@ -953,7 +960,7 @@
       <c r="L37" s="2"/>
       <c r="N37" s="2"/>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
         <v>51</v>
       </c>
@@ -961,7 +968,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
         <v>53</v>
       </c>
@@ -973,6 +980,20 @@
       </c>
       <c r="L39" s="2" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B40" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\REPO\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E021A63F-619E-43FF-818D-8D48711E9A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="57">
   <si>
     <t>##var</t>
   </si>
@@ -115,10 +116,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>GameplayCueLog</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>GameplayCueLogFloat</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -227,13 +224,21 @@
   </si>
   <si>
     <t>Cues</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TaskPlayCuePreset</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CueLog</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -610,21 +615,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P40"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P43"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="20.625" customWidth="1"/>
-    <col min="3" max="3" width="14.625" customWidth="1"/>
+    <col min="2" max="2" width="20.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="6" width="12.25" customWidth="1"/>
+    <col min="5" max="6" width="12.21875" customWidth="1"/>
     <col min="7" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="21.5" customWidth="1"/>
-    <col min="11" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="10.375" customWidth="1"/>
+    <col min="10" max="10" width="21.44140625" customWidth="1"/>
+    <col min="11" max="12" width="13.44140625" customWidth="1"/>
+    <col min="13" max="13" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -662,7 +667,7 @@
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -688,7 +693,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -717,8 +722,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>26</v>
       </c>
@@ -726,274 +731,300 @@
       <c r="J5" s="2"/>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="E8" s="2"/>
       <c r="J8" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E9" s="2"/>
       <c r="J9" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="J12" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>26</v>
       </c>
       <c r="E13" s="2"/>
       <c r="J13" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="J14" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="J15" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B18" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="J19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B28" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="C28" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L29" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L29" s="2" t="s">
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B30" s="2" t="s">
+      <c r="C30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J30" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L31" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="N31" s="2"/>
     </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
       <c r="J32" s="2"/>
       <c r="L32" s="2"/>
       <c r="N32" s="2"/>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="J33" s="2"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="36" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B37" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J37" s="2"/>
       <c r="L37" s="2"/>
       <c r="N37" s="2"/>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B38" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J40" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C40" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J40" s="2" t="s">
+      <c r="L40" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="L41" s="2"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="L42" s="2"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B43" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L40" s="2" t="s">
-        <v>38</v>
+      <c r="C43" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E021A63F-619E-43FF-818D-8D48711E9A1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A87C6D-CED4-4C33-9A4E-2A28C68DE6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="71">
   <si>
     <t>##var</t>
   </si>
@@ -108,34 +108,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>bool</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>CueLogic</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>GameplayCueLogFloat</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>GameplayCueLogBool</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>GameplayCueLogVector2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>GameplayCueVector3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CueLoging</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>MmcLogic</t>
   </si>
   <si>
@@ -163,10 +139,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>RotationOffset</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>Value</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -183,18 +155,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>X</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Y</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Z</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>ALTimeline</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -211,10 +171,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>TimelineID</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>TaskDebug</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -223,15 +179,115 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Cues</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>TaskPlayCuePreset</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>CueLog</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RequiredTags</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ImmunityTags</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>XParamCue</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>XParamInt</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TaskDoNothing</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>XParam</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Param</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>XParamNone</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>XParamString</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>XParamFloat</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>XParamString</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>XParamCueIDs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>IDs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>XParamArrayInt</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>XParamArrayFloat</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(array#sep=;),float</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>XParamArrayString</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(array#sep=;),string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>XParamALTimelineID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CueLogic</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>XParamEffectIDs</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CueLogging</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>XParamMMCScalable</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>XParamLogging</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>EX-GAS内部通用的参数类型，所有自定义泛型类的参数都需要继承自XParam，以此来规范传参</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -277,7 +333,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -302,6 +358,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -323,7 +385,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -338,6 +400,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -616,14 +684,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.6640625" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="5" max="6" width="12.21875" customWidth="1"/>
-    <col min="7" max="9" width="15" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" customWidth="1"/>
+    <col min="6" max="6" width="7.109375" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" customWidth="1"/>
+    <col min="8" max="9" width="15" customWidth="1"/>
     <col min="10" max="10" width="21.44140625" customWidth="1"/>
     <col min="11" max="12" width="13.44140625" customWidth="1"/>
     <col min="13" max="13" width="10.33203125" customWidth="1"/>
@@ -722,310 +792,569 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="G4" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="2"/>
+    </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>52</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="L5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="P5" s="2"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E6" s="2"/>
       <c r="J6" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>23</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="P6" s="2"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E7" s="2"/>
       <c r="J7" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="K7" s="2"/>
       <c r="L7" s="2" t="s">
-        <v>23</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="P7" s="2"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="E8" s="2"/>
       <c r="J8" s="2" t="s">
-        <v>43</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="K8" s="2"/>
       <c r="L8" s="2" t="s">
-        <v>24</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="P8" s="2"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E9" s="2"/>
       <c r="J9" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="K9" s="2"/>
       <c r="L9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+      <c r="P9" s="2"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2"/>
       <c r="J10" s="2" t="s">
-        <v>40</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="K10" s="2"/>
       <c r="L10" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="P10" s="2"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="E11" s="2"/>
       <c r="J11" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="K11" s="2"/>
       <c r="L11" s="2" t="s">
-        <v>24</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="P11" s="2"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>45</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="K12" s="2"/>
       <c r="L12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>26</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="P12" s="2"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="J13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="P13" s="2"/>
+    </row>
+    <row r="14" spans="1:16" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="2"/>
       <c r="J14" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="K14" s="2"/>
       <c r="L14" s="2" t="s">
-        <v>24</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="P14" s="2"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="J15" s="2" t="s">
         <v>46</v>
       </c>
       <c r="L15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P15" s="2"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="J16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="P16" s="2"/>
+    </row>
+    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="J17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="P17" s="2"/>
+    </row>
+    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P18" s="2"/>
+    </row>
+    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B19" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P19" s="2"/>
+    </row>
+    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="P20" s="2"/>
+    </row>
+    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="L21" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B18" s="2" t="s">
+      <c r="P21" s="2"/>
+    </row>
+    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="J22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P22" s="2"/>
+    </row>
+    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="P23" s="2"/>
+    </row>
+    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J24" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L18" s="2" t="s">
+      <c r="L24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P24" s="2"/>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="J25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L25" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B27" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="P25" s="2"/>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K26" s="2"/>
+      <c r="P26" s="2"/>
+    </row>
+    <row r="27" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="L28" s="2"/>
+    </row>
+    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>34</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E29" s="2"/>
       <c r="J29" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B30" s="2" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>34</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E30" s="2"/>
       <c r="J30" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B31" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="N31" s="2"/>
-    </row>
-    <row r="32" spans="2:14" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="L31" s="2"/>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="E32" s="2"/>
       <c r="J32" s="2"/>
       <c r="L32" s="2"/>
-      <c r="N32" s="2"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="E33" s="2"/>
       <c r="J33" s="2"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="36" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B37" s="2" t="s">
-        <v>49</v>
-      </c>
+    <row r="34" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="L34" s="2"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J35" s="2"/>
+      <c r="L35" s="2"/>
+    </row>
+    <row r="36" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="L36" s="2"/>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="J37" s="2"/>
       <c r="L37" s="2"/>
-      <c r="N37" s="2"/>
-    </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B38" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" s="2" t="s">
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J38" s="2"/>
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" t="s">
+        <v>26</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="49" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B50" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B51" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B52" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="53" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="54" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B54" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="N54" s="2"/>
+    </row>
+    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J55" s="2"/>
+      <c r="L55" s="2"/>
+      <c r="N55" s="2"/>
+    </row>
+    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J56" s="2"/>
+      <c r="L56" s="2"/>
+    </row>
+    <row r="59" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B60" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J60" s="2"/>
+      <c r="L60" s="2"/>
+      <c r="N60" s="2"/>
+    </row>
+    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B61" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B39" s="2" t="s">
+      <c r="C61" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L61" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C39" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J39" s="2" t="s">
+    </row>
+    <row r="62" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B62" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="L39" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B40" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="L41" s="2"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="L42" s="2"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
+      <c r="C62" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="63" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B63" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L63" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>37</v>
-      </c>
+    </row>
+    <row r="64" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B64" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="65" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="J66" s="2"/>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="L67" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A87C6D-CED4-4C33-9A4E-2A28C68DE6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7334E1-32AA-473A-8CBE-4E7552D2D14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="76">
   <si>
     <t>##var</t>
   </si>
@@ -288,6 +288,25 @@
   </si>
   <si>
     <t>EX-GAS内部通用的参数类型，所有自定义泛型类的参数都需要继承自XParam，以此来规范传参</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>XParamAnimator</t>
+  </si>
+  <si>
+    <t>XParamAnimator</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AnimatorNodePath</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>AnimationName</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>CuePlayAnimator</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -398,14 +417,14 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -684,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P67"/>
+  <dimension ref="A1:P70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.6640625" customWidth="1"/>
@@ -727,15 +746,15 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -797,17 +816,17 @@
         <v>50</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
+      <c r="O4" s="5"/>
       <c r="P4" s="2"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -1086,87 +1105,114 @@
       <c r="P25" s="2"/>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="K26" s="2"/>
+      <c r="B26" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="P26" s="2"/>
     </row>
-    <row r="27" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="J27" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P27" s="2"/>
+    </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B28" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
       <c r="J28" s="2"/>
       <c r="L28" s="2"/>
+      <c r="P28" s="2"/>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B29" s="2" t="s">
+      <c r="K29" s="2"/>
+      <c r="P29" s="2"/>
+    </row>
+    <row r="30" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B31" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="L31" s="2"/>
+    </row>
+    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E29" s="2"/>
-      <c r="J29" s="2" t="s">
+      <c r="E32" s="2"/>
+      <c r="J32" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="L29" s="2" t="s">
+      <c r="L32" s="2" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B30" s="2" t="s">
+    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B33" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E30" s="2"/>
-      <c r="J30" s="2" t="s">
+      <c r="E33" s="2"/>
+      <c r="J33" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="L30" s="2" t="s">
+      <c r="L33" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="L31" s="2"/>
-    </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="L32" s="2"/>
-    </row>
-    <row r="33" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="L33" s="2"/>
-    </row>
-    <row r="34" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="E34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="L34" s="2"/>
+      <c r="J34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="E35" s="2"/>
       <c r="J35" s="2"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="E36" s="2"/>
       <c r="J36" s="2"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="E37" s="2"/>
       <c r="J37" s="2"/>
       <c r="L37" s="2"/>
     </row>
@@ -1174,77 +1220,50 @@
       <c r="J38" s="2"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="2:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="L39" s="2"/>
+    </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
+      <c r="J40" s="2"/>
+      <c r="L40" s="2"/>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="J41" s="2"/>
+      <c r="L41" s="2"/>
+    </row>
+    <row r="42" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B41" s="2" t="s">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C44" t="s">
         <v>26</v>
       </c>
-      <c r="J41" s="2" t="s">
+      <c r="J44" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="L41" s="2" t="s">
+      <c r="L44" s="2" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="49" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B50" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B51" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B52" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L52" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
+    <row r="52" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="53" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B53" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C53" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="54" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B54" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>28</v>
@@ -1253,73 +1272,73 @@
         <v>51</v>
       </c>
       <c r="L54" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B55" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B56" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B57" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L57" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="N54" s="2"/>
-    </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J55" s="2"/>
-      <c r="L55" s="2"/>
-      <c r="N55" s="2"/>
-    </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="J56" s="2"/>
-      <c r="L56" s="2"/>
-    </row>
-    <row r="59" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B60" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J60" s="2"/>
-      <c r="L60" s="2"/>
-      <c r="N60" s="2"/>
-    </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B61" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J61" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L61" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B62" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J62" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L62" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
+      <c r="N57" s="2"/>
+    </row>
+    <row r="58" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J58" s="2"/>
+      <c r="L58" s="2"/>
+      <c r="N58" s="2"/>
+    </row>
+    <row r="59" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="J59" s="2"/>
+      <c r="L59" s="2"/>
+    </row>
+    <row r="62" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="63" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B63" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C63" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J63" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L63" s="2" t="s">
-        <v>55</v>
-      </c>
+      <c r="J63" s="2"/>
+      <c r="L63" s="2"/>
+      <c r="N63" s="2"/>
     </row>
     <row r="64" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B64" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>39</v>
@@ -1328,12 +1347,12 @@
         <v>51</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B65" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>39</v>
@@ -1342,19 +1361,61 @@
         <v>51</v>
       </c>
       <c r="L65" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B66" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B67" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="68" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B68" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L68" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B66" s="2"/>
-      <c r="C66" s="2"/>
-      <c r="J66" s="2"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="L67" s="2"/>
+    <row r="69" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+      <c r="J69" s="2"/>
+    </row>
+    <row r="70" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="L70" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
+++ b/ProjectConfigTable/exgas_config/Datas/__beans__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MyRepo\gameplay-ability-system-for-unity\ProjectConfigTable\exgas_config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7334E1-32AA-473A-8CBE-4E7552D2D14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFED189-6474-4A12-96B4-D7115E687D30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -267,10 +267,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>CueLogic</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>XParamEffectIDs</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -307,6 +303,10 @@
   </si>
   <si>
     <t>CuePlayAnimator</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(array#sep=;),int#default={}</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -817,7 +817,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="G4" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
@@ -981,7 +981,7 @@
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="P14" s="2"/>
     </row>
@@ -996,10 +996,10 @@
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="J16" s="2" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="P16" s="2"/>
     </row>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>50</v>
@@ -1047,7 +1047,7 @@
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>50</v>
@@ -1080,7 +1080,7 @@
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -1106,13 +1106,13 @@
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>50</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>23</v>
@@ -1123,7 +1123,7 @@
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="J27" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>23</v>
@@ -1167,7 +1167,7 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B33" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>25</v>
@@ -1177,12 +1177,12 @@
         <v>51</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>25</v>
@@ -1192,7 +1192,7 @@
         <v>51</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.25">
@@ -1252,7 +1252,7 @@
         <v>51</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -1286,7 +1286,7 @@
         <v>51</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56" spans="2:14" x14ac:dyDescent="0.25">
